--- a/docs/data/jp/xlsx/6954.xlsx
+++ b/docs/data/jp/xlsx/6954.xlsx
@@ -228,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -350,6 +350,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -762,7 +765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC151"/>
+  <dimension ref="A1:AC158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4318,11 +4321,11 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 (2026.10.23)</t>
+          <t>현재 주가 (2026.10.26)</t>
         </is>
       </c>
       <c r="B47" s="29" t="n">
-        <v>5587</v>
+        <v>5639</v>
       </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
@@ -5559,7 +5562,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉 2026.10.23</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5811,3726 +5814,4190 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T79" s="17">
+        <f>IF(OR(T78="",S78=""),"",IF(S78&lt;=0,"",IFERROR(T78/S78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>123702</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>129976</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>127338</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>116307</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>128595</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>129964</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>119756</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>132204</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>137124</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>140281</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>139941</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>140073</v>
       </c>
-      <c r="T79" s="22" t="n">
+      <c r="T80" s="22" t="n">
         <v>117958</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>138938</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>129976</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>129964</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>140281</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>74128</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>68773</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>67762</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>76555</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>68457</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>82151</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>76607</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>79001</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>78620</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>94238</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>91094</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>102600</v>
       </c>
-      <c r="T80" s="12" t="n">
+      <c r="T81" s="12" t="n">
         <v>74800</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>76905</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>68773</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>82151</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>94238</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>33241</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>34277</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>34804</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>33925</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>33549</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>33801</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>34179</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>35465</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>36880</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>38179</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>37602</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>39430</v>
-      </c>
-      <c r="T81" s="22" t="n">
-        <v>31506</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>32704</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>34277</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>33801</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>38179</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>40887</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>34496</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>32958</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>42630</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>34908</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>48350</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>42428</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>43536</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>41740</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>56059</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>53492</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>63170</v>
-      </c>
-      <c r="T82" s="12" t="n">
-        <v>43294</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>44201</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>34496</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>48350</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>56059</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T82" s="17">
+        <f>IF(OR(T81="",S81=""),"",IF(S81&lt;=0,"",IFERROR(T81/S81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>1145</v>
+        <v>33241</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>1271</v>
+        <v>34277</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>1629</v>
+        <v>34804</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>1776</v>
+        <v>33925</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>1888</v>
+        <v>33549</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>1829</v>
+        <v>33801</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>1869</v>
+        <v>34179</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>1950</v>
+        <v>35465</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>1736</v>
+        <v>36880</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>1982</v>
+        <v>38179</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>2249</v>
+        <v>37602</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>2903</v>
+        <v>39430</v>
       </c>
       <c r="T83" s="22" t="n">
-        <v>621</v>
+        <v>31506</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>971</v>
+        <v>32704</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>1271</v>
+        <v>34277</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>1829</v>
+        <v>33801</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>1982</v>
+        <v>38179</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>배당금수익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>335</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>207</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>269</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>1477</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>398</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>206</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>296</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>2325</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>523</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>226</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>374</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>2114</v>
-      </c>
-      <c r="T84" s="22" t="n">
-        <v>190</v>
-      </c>
-      <c r="U84" s="22" t="n">
-        <v>197</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>207</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>206</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>226</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>40887</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>34496</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>32958</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>42630</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>34908</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>48350</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>42428</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>43536</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>41740</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>56059</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>53492</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>63170</v>
+      </c>
+      <c r="T84" s="12" t="n">
+        <v>43294</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>44201</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>34496</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>48350</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>56059</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>지분법이익</t>
-        </is>
-      </c>
-      <c r="C85" s="22" t="n">
-        <v>6302</v>
-      </c>
-      <c r="D85" s="22" t="n">
-        <v>6880</v>
-      </c>
-      <c r="E85" s="22" t="n">
-        <v>6186</v>
-      </c>
-      <c r="F85" s="22" t="n">
-        <v>7756</v>
-      </c>
-      <c r="G85" s="22" t="n">
-        <v>6840</v>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>7258</v>
-      </c>
-      <c r="I85" s="22" t="n">
-        <v>6688</v>
-      </c>
-      <c r="J85" s="22" t="n">
-        <v>8037</v>
-      </c>
-      <c r="K85" s="22" t="n">
-        <v>7332</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>8474</v>
-      </c>
-      <c r="M85" s="22" t="n">
-        <v>11371</v>
-      </c>
-      <c r="N85" s="22" t="n">
-        <v>11606</v>
-      </c>
-      <c r="T85" s="22" t="n">
-        <v>6813</v>
-      </c>
-      <c r="U85" s="22" t="n">
-        <v>7988</v>
-      </c>
-      <c r="V85" s="22" t="n">
-        <v>6880</v>
-      </c>
-      <c r="W85" s="22" t="n">
-        <v>7258</v>
-      </c>
-      <c r="X85" s="22" t="n">
-        <v>8474</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="T85" s="17">
+        <f>IF(OR(T84="",T78=""),"",IF(T78&lt;=0,"",IFERROR(T84/T78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>잡이익</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>1029</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>4513</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>769</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>1661</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>956</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>1442</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>1080</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>1591</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>859</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>2580</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>1284</v>
-      </c>
-      <c r="N86" s="22" t="n">
-        <v>2343</v>
-      </c>
-      <c r="T86" s="22" t="n">
-        <v>2011</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>1655</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>4513</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>1442</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>2580</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T86" s="17">
+        <f>IF(OR(T84="",S84=""),"",IF(S84&lt;=0,"",IFERROR(T84/S84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>이자수익</t>
         </is>
       </c>
       <c r="C87" s="22" t="n">
-        <v>8811</v>
+        <v>1145</v>
       </c>
       <c r="D87" s="22" t="n">
-        <v>12871</v>
+        <v>1271</v>
       </c>
       <c r="E87" s="22" t="n">
-        <v>8853</v>
+        <v>1629</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>12670</v>
+        <v>1776</v>
       </c>
       <c r="G87" s="22" t="n">
-        <v>10082</v>
+        <v>1888</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>10735</v>
+        <v>1829</v>
       </c>
       <c r="I87" s="22" t="n">
-        <v>9933</v>
+        <v>1869</v>
       </c>
       <c r="J87" s="22" t="n">
-        <v>13903</v>
+        <v>1950</v>
       </c>
       <c r="K87" s="22" t="n">
-        <v>10450</v>
+        <v>1736</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>13262</v>
+        <v>1982</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>15278</v>
+        <v>2249</v>
       </c>
       <c r="N87" s="22" t="n">
-        <v>18966</v>
+        <v>2903</v>
       </c>
       <c r="T87" s="22" t="n">
-        <v>9635</v>
+        <v>621</v>
       </c>
       <c r="U87" s="22" t="n">
-        <v>10811</v>
+        <v>971</v>
       </c>
       <c r="V87" s="22" t="n">
-        <v>12871</v>
+        <v>1271</v>
       </c>
       <c r="W87" s="22" t="n">
-        <v>10735</v>
+        <v>1829</v>
       </c>
       <c r="X87" s="22" t="n">
-        <v>13262</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>고정자산 철거비용</t>
+          <t>배당금수익</t>
         </is>
       </c>
       <c r="C88" s="22" t="n">
-        <v>287</v>
+        <v>335</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>36</v>
+        <v>207</v>
       </c>
       <c r="E88" s="22" t="n">
-        <v>125</v>
+        <v>269</v>
+      </c>
+      <c r="F88" s="22" t="n">
+        <v>1477</v>
+      </c>
+      <c r="G88" s="22" t="n">
+        <v>398</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="I88" s="22" t="n">
-        <v>178</v>
+        <v>296</v>
+      </c>
+      <c r="J88" s="22" t="n">
+        <v>2325</v>
+      </c>
+      <c r="K88" s="22" t="n">
+        <v>523</v>
       </c>
       <c r="L88" s="22" t="n">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>132</v>
+        <v>374</v>
+      </c>
+      <c r="N88" s="22" t="n">
+        <v>2114</v>
       </c>
       <c r="T88" s="22" t="n">
-        <v>395</v>
+        <v>190</v>
       </c>
       <c r="U88" s="22" t="n">
-        <v>675</v>
+        <v>197</v>
       </c>
       <c r="V88" s="22" t="n">
-        <v>36</v>
+        <v>207</v>
       </c>
       <c r="W88" s="22" t="n">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="X88" s="22" t="n">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>순화폐성 포지션 손실</t>
+          <t>지분법이익</t>
         </is>
       </c>
       <c r="C89" s="22" t="n">
-        <v>197</v>
+        <v>6302</v>
+      </c>
+      <c r="D89" s="22" t="n">
+        <v>6880</v>
+      </c>
+      <c r="E89" s="22" t="n">
+        <v>6186</v>
+      </c>
+      <c r="F89" s="22" t="n">
+        <v>7756</v>
+      </c>
+      <c r="G89" s="22" t="n">
+        <v>6840</v>
+      </c>
+      <c r="H89" s="22" t="n">
+        <v>7258</v>
+      </c>
+      <c r="I89" s="22" t="n">
+        <v>6688</v>
+      </c>
+      <c r="J89" s="22" t="n">
+        <v>8037</v>
+      </c>
+      <c r="K89" s="22" t="n">
+        <v>7332</v>
+      </c>
+      <c r="L89" s="22" t="n">
+        <v>8474</v>
+      </c>
+      <c r="M89" s="22" t="n">
+        <v>11371</v>
+      </c>
+      <c r="N89" s="22" t="n">
+        <v>11606</v>
+      </c>
+      <c r="T89" s="22" t="n">
+        <v>6813</v>
+      </c>
+      <c r="U89" s="22" t="n">
+        <v>7988</v>
+      </c>
+      <c r="V89" s="22" t="n">
+        <v>6880</v>
+      </c>
+      <c r="W89" s="22" t="n">
+        <v>7258</v>
+      </c>
+      <c r="X89" s="22" t="n">
+        <v>8474</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>기부금</t>
-        </is>
+          <t>잡이익</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D90" s="22" t="n">
+        <v>4513</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>242</v>
+        <v>769</v>
+      </c>
+      <c r="F90" s="22" t="n">
+        <v>1661</v>
+      </c>
+      <c r="G90" s="22" t="n">
+        <v>956</v>
+      </c>
+      <c r="H90" s="22" t="n">
+        <v>1442</v>
+      </c>
+      <c r="I90" s="22" t="n">
+        <v>1080</v>
+      </c>
+      <c r="J90" s="22" t="n">
+        <v>1591</v>
+      </c>
+      <c r="K90" s="22" t="n">
+        <v>859</v>
+      </c>
+      <c r="L90" s="22" t="n">
+        <v>2580</v>
+      </c>
+      <c r="M90" s="22" t="n">
+        <v>1284</v>
+      </c>
+      <c r="N90" s="22" t="n">
+        <v>2343</v>
       </c>
       <c r="T90" s="22" t="n">
-        <v>192</v>
+        <v>2011</v>
       </c>
       <c r="U90" s="22" t="n">
-        <v>71</v>
+        <v>1655</v>
+      </c>
+      <c r="V90" s="22" t="n">
+        <v>4513</v>
+      </c>
+      <c r="W90" s="22" t="n">
+        <v>1442</v>
+      </c>
+      <c r="X90" s="22" t="n">
+        <v>2580</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>소송 화해금</t>
-        </is>
+          <t>영업외수익 합계</t>
+        </is>
+      </c>
+      <c r="C91" s="22" t="n">
+        <v>8811</v>
+      </c>
+      <c r="D91" s="22" t="n">
+        <v>12871</v>
+      </c>
+      <c r="E91" s="22" t="n">
+        <v>8853</v>
+      </c>
+      <c r="F91" s="22" t="n">
+        <v>12670</v>
+      </c>
+      <c r="G91" s="22" t="n">
+        <v>10082</v>
+      </c>
+      <c r="H91" s="22" t="n">
+        <v>10735</v>
+      </c>
+      <c r="I91" s="22" t="n">
+        <v>9933</v>
+      </c>
+      <c r="J91" s="22" t="n">
+        <v>13903</v>
+      </c>
+      <c r="K91" s="22" t="n">
+        <v>10450</v>
+      </c>
+      <c r="L91" s="22" t="n">
+        <v>13262</v>
+      </c>
+      <c r="M91" s="22" t="n">
+        <v>15278</v>
+      </c>
+      <c r="N91" s="22" t="n">
+        <v>18966</v>
       </c>
       <c r="T91" s="22" t="n">
-        <v>0</v>
+        <v>9635</v>
       </c>
       <c r="U91" s="22" t="n">
-        <v>0</v>
+        <v>10811</v>
+      </c>
+      <c r="V91" s="22" t="n">
+        <v>12871</v>
+      </c>
+      <c r="W91" s="22" t="n">
+        <v>10735</v>
+      </c>
+      <c r="X91" s="22" t="n">
+        <v>13262</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>고정자산 제각·매각손실</t>
-        </is>
-      </c>
-      <c r="G92" s="22" t="n">
-        <v>130</v>
+          <t>고정자산 철거비용</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="n">
+        <v>287</v>
+      </c>
+      <c r="D92" s="22" t="n">
+        <v>36</v>
+      </c>
+      <c r="E92" s="22" t="n">
+        <v>125</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>85</v>
-      </c>
-      <c r="K92" s="22" t="n">
-        <v>11</v>
+        <v>25</v>
+      </c>
+      <c r="I92" s="22" t="n">
+        <v>178</v>
       </c>
       <c r="L92" s="22" t="n">
-        <v>61</v>
+        <v>217</v>
+      </c>
+      <c r="M92" s="22" t="n">
+        <v>132</v>
       </c>
       <c r="T92" s="22" t="n">
-        <v>355</v>
+        <v>395</v>
       </c>
       <c r="U92" s="22" t="n">
-        <v>526</v>
+        <v>675</v>
+      </c>
+      <c r="V92" s="22" t="n">
+        <v>36</v>
       </c>
       <c r="W92" s="22" t="n">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="X92" s="22" t="n">
-        <v>61</v>
+        <v>217</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
-        </is>
-      </c>
-      <c r="E93" s="22" t="n">
-        <v>84</v>
-      </c>
-      <c r="F93" s="22" t="n">
-        <v>620</v>
-      </c>
-      <c r="I93" s="22" t="n">
-        <v>397</v>
-      </c>
-      <c r="J93" s="22" t="n">
-        <v>-75</v>
+          <t>순화폐성 포지션 손실</t>
+        </is>
+      </c>
+      <c r="C93" s="22" t="n">
+        <v>197</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>잡손실</t>
-        </is>
-      </c>
-      <c r="C94" s="22" t="n">
-        <v>-190</v>
-      </c>
-      <c r="D94" s="22" t="n">
-        <v>387</v>
+          <t>기부금</t>
+        </is>
       </c>
       <c r="E94" s="22" t="n">
-        <v>473</v>
-      </c>
-      <c r="F94" s="22" t="n">
-        <v>1003</v>
-      </c>
-      <c r="G94" s="22" t="n">
-        <v>64</v>
-      </c>
-      <c r="H94" s="22" t="n">
-        <v>121</v>
-      </c>
-      <c r="I94" s="22" t="n">
-        <v>631</v>
-      </c>
-      <c r="J94" s="22" t="n">
-        <v>428</v>
-      </c>
-      <c r="K94" s="22" t="n">
-        <v>87</v>
-      </c>
-      <c r="L94" s="22" t="n">
-        <v>-38</v>
-      </c>
-      <c r="M94" s="22" t="n">
-        <v>445</v>
-      </c>
-      <c r="N94" s="22" t="n">
-        <v>1015</v>
+        <v>242</v>
       </c>
       <c r="T94" s="22" t="n">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="U94" s="22" t="n">
-        <v>-377</v>
-      </c>
-      <c r="V94" s="22" t="n">
-        <v>387</v>
-      </c>
-      <c r="W94" s="22" t="n">
-        <v>121</v>
-      </c>
-      <c r="X94" s="22" t="n">
-        <v>-38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
-        </is>
-      </c>
-      <c r="C95" s="22" t="n">
-        <v>705</v>
-      </c>
-      <c r="D95" s="22" t="n">
-        <v>758</v>
-      </c>
-      <c r="E95" s="22" t="n">
-        <v>682</v>
-      </c>
-      <c r="F95" s="22" t="n">
-        <v>1649</v>
-      </c>
-      <c r="G95" s="22" t="n">
-        <v>285</v>
-      </c>
-      <c r="H95" s="22" t="n">
-        <v>1832</v>
-      </c>
-      <c r="I95" s="22" t="n">
-        <v>809</v>
-      </c>
-      <c r="J95" s="22" t="n">
-        <v>1086</v>
-      </c>
-      <c r="K95" s="22" t="n">
-        <v>776</v>
-      </c>
-      <c r="L95" s="22" t="n">
-        <v>1155</v>
-      </c>
-      <c r="M95" s="22" t="n">
-        <v>577</v>
-      </c>
-      <c r="N95" s="22" t="n">
-        <v>1284</v>
+          <t>소송 화해금</t>
+        </is>
       </c>
       <c r="T95" s="22" t="n">
-        <v>1068</v>
+        <v>0</v>
       </c>
       <c r="U95" s="22" t="n">
-        <v>1480</v>
-      </c>
-      <c r="V95" s="22" t="n">
-        <v>758</v>
-      </c>
-      <c r="W95" s="22" t="n">
-        <v>1832</v>
-      </c>
-      <c r="X95" s="22" t="n">
-        <v>1155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="n">
-        <v>48993</v>
-      </c>
-      <c r="D96" s="12" t="n">
-        <v>46609</v>
-      </c>
-      <c r="E96" s="12" t="n">
-        <v>41129</v>
-      </c>
-      <c r="F96" s="12" t="n">
-        <v>53651</v>
-      </c>
-      <c r="G96" s="12" t="n">
-        <v>44705</v>
-      </c>
-      <c r="H96" s="12" t="n">
-        <v>57253</v>
-      </c>
-      <c r="I96" s="12" t="n">
-        <v>51552</v>
-      </c>
-      <c r="J96" s="12" t="n">
-        <v>56353</v>
-      </c>
-      <c r="K96" s="12" t="n">
-        <v>51414</v>
-      </c>
-      <c r="L96" s="12" t="n">
-        <v>68166</v>
-      </c>
-      <c r="M96" s="12" t="n">
-        <v>68193</v>
-      </c>
-      <c r="N96" s="12" t="n">
-        <v>80852</v>
-      </c>
-      <c r="T96" s="12" t="n">
-        <v>51861</v>
-      </c>
-      <c r="U96" s="12" t="n">
-        <v>53532</v>
-      </c>
-      <c r="V96" s="12" t="n">
-        <v>46609</v>
-      </c>
-      <c r="W96" s="12" t="n">
-        <v>57253</v>
-      </c>
-      <c r="X96" s="12" t="n">
-        <v>68166</v>
+      <c r="A96" s="20" t="inlineStr">
+        <is>
+          <t>고정자산 제각·매각손실</t>
+        </is>
+      </c>
+      <c r="G96" s="22" t="n">
+        <v>130</v>
+      </c>
+      <c r="H96" s="22" t="n">
+        <v>85</v>
+      </c>
+      <c r="K96" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="L96" s="22" t="n">
+        <v>61</v>
+      </c>
+      <c r="T96" s="22" t="n">
+        <v>355</v>
+      </c>
+      <c r="U96" s="22" t="n">
+        <v>526</v>
+      </c>
+      <c r="W96" s="22" t="n">
+        <v>85</v>
+      </c>
+      <c r="X96" s="22" t="n">
+        <v>61</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>해외 자회사 송금사기 손실</t>
-        </is>
-      </c>
-      <c r="T97" s="22" t="n">
-        <v>-59</v>
-      </c>
-      <c r="U97" s="22" t="n">
-        <v>0</v>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="E97" s="22" t="n">
+        <v>84</v>
+      </c>
+      <c r="F97" s="22" t="n">
+        <v>620</v>
+      </c>
+      <c r="I97" s="22" t="n">
+        <v>397</v>
+      </c>
+      <c r="J97" s="22" t="n">
+        <v>-75</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
-        </is>
+          <t>잡손실</t>
+        </is>
+      </c>
+      <c r="C98" s="22" t="n">
+        <v>-190</v>
+      </c>
+      <c r="D98" s="22" t="n">
+        <v>387</v>
+      </c>
+      <c r="E98" s="22" t="n">
+        <v>473</v>
+      </c>
+      <c r="F98" s="22" t="n">
+        <v>1003</v>
+      </c>
+      <c r="G98" s="22" t="n">
+        <v>64</v>
+      </c>
+      <c r="H98" s="22" t="n">
+        <v>121</v>
+      </c>
+      <c r="I98" s="22" t="n">
+        <v>631</v>
+      </c>
+      <c r="J98" s="22" t="n">
+        <v>428</v>
+      </c>
+      <c r="K98" s="22" t="n">
+        <v>87</v>
+      </c>
+      <c r="L98" s="22" t="n">
+        <v>-38</v>
+      </c>
+      <c r="M98" s="22" t="n">
+        <v>445</v>
+      </c>
+      <c r="N98" s="22" t="n">
+        <v>1015</v>
       </c>
       <c r="T98" s="22" t="n">
-        <v>-59</v>
+        <v>126</v>
       </c>
       <c r="U98" s="22" t="n">
-        <v>1224</v>
+        <v>-377</v>
+      </c>
+      <c r="V98" s="22" t="n">
+        <v>387</v>
+      </c>
+      <c r="W98" s="22" t="n">
+        <v>121</v>
+      </c>
+      <c r="X98" s="22" t="n">
+        <v>-38</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="n">
+      <c r="A99" s="20" t="inlineStr">
+        <is>
+          <t>영업외비용 합계</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="n">
+        <v>705</v>
+      </c>
+      <c r="D99" s="22" t="n">
+        <v>758</v>
+      </c>
+      <c r="E99" s="22" t="n">
+        <v>682</v>
+      </c>
+      <c r="F99" s="22" t="n">
+        <v>1649</v>
+      </c>
+      <c r="G99" s="22" t="n">
+        <v>285</v>
+      </c>
+      <c r="H99" s="22" t="n">
+        <v>1832</v>
+      </c>
+      <c r="I99" s="22" t="n">
+        <v>809</v>
+      </c>
+      <c r="J99" s="22" t="n">
+        <v>1086</v>
+      </c>
+      <c r="K99" s="22" t="n">
+        <v>776</v>
+      </c>
+      <c r="L99" s="22" t="n">
+        <v>1155</v>
+      </c>
+      <c r="M99" s="22" t="n">
+        <v>577</v>
+      </c>
+      <c r="N99" s="22" t="n">
+        <v>1284</v>
+      </c>
+      <c r="T99" s="22" t="n">
+        <v>1068</v>
+      </c>
+      <c r="U99" s="22" t="n">
+        <v>1480</v>
+      </c>
+      <c r="V99" s="22" t="n">
+        <v>758</v>
+      </c>
+      <c r="W99" s="22" t="n">
+        <v>1832</v>
+      </c>
+      <c r="X99" s="22" t="n">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="n">
         <v>48993</v>
       </c>
-      <c r="D99" s="12" t="n">
+      <c r="D100" s="12" t="n">
         <v>46609</v>
       </c>
-      <c r="E99" s="12" t="n">
+      <c r="E100" s="12" t="n">
         <v>41129</v>
       </c>
-      <c r="F99" s="12" t="n">
+      <c r="F100" s="12" t="n">
         <v>53651</v>
       </c>
-      <c r="G99" s="12" t="n">
+      <c r="G100" s="12" t="n">
         <v>44705</v>
       </c>
-      <c r="H99" s="12" t="n">
+      <c r="H100" s="12" t="n">
         <v>57253</v>
       </c>
-      <c r="I99" s="12" t="n">
+      <c r="I100" s="12" t="n">
         <v>51552</v>
       </c>
-      <c r="J99" s="12" t="n">
+      <c r="J100" s="12" t="n">
         <v>56353</v>
       </c>
-      <c r="K99" s="12" t="n">
+      <c r="K100" s="12" t="n">
         <v>51414</v>
       </c>
-      <c r="L99" s="12" t="n">
+      <c r="L100" s="12" t="n">
         <v>68166</v>
       </c>
-      <c r="M99" s="12" t="n">
+      <c r="M100" s="12" t="n">
         <v>68193</v>
       </c>
-      <c r="N99" s="12" t="n">
+      <c r="N100" s="12" t="n">
         <v>80852</v>
       </c>
-      <c r="T99" s="12" t="n">
-        <v>51920</v>
-      </c>
-      <c r="U99" s="12" t="n">
-        <v>52308</v>
-      </c>
-      <c r="V99" s="12" t="n">
+      <c r="T100" s="12" t="n">
+        <v>51861</v>
+      </c>
+      <c r="U100" s="12" t="n">
+        <v>53532</v>
+      </c>
+      <c r="V100" s="12" t="n">
         <v>46609</v>
       </c>
-      <c r="W99" s="12" t="n">
+      <c r="W100" s="12" t="n">
         <v>57253</v>
       </c>
-      <c r="X99" s="12" t="n">
+      <c r="X100" s="12" t="n">
         <v>68166</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="20" t="inlineStr">
-        <is>
-          <t>법인세·주민세·사업세</t>
-        </is>
-      </c>
-      <c r="C100" s="22" t="n">
-        <v>6675</v>
-      </c>
-      <c r="D100" s="22" t="n">
-        <v>10838</v>
-      </c>
-      <c r="E100" s="22" t="n">
-        <v>9275</v>
-      </c>
-      <c r="F100" s="22" t="n">
-        <v>14787</v>
-      </c>
-      <c r="G100" s="22" t="n">
-        <v>11422</v>
-      </c>
-      <c r="H100" s="22" t="n">
-        <v>10435</v>
-      </c>
-      <c r="I100" s="22" t="n">
-        <v>12426</v>
-      </c>
-      <c r="J100" s="22" t="n">
-        <v>16736</v>
-      </c>
-      <c r="K100" s="22" t="n">
-        <v>11768</v>
-      </c>
-      <c r="L100" s="22" t="n">
-        <v>11029</v>
-      </c>
-      <c r="M100" s="22" t="n">
-        <v>13981</v>
-      </c>
-      <c r="N100" s="22" t="n">
-        <v>19051</v>
-      </c>
-      <c r="T100" s="22" t="n">
-        <v>17413</v>
-      </c>
-      <c r="U100" s="22" t="n">
-        <v>14015</v>
-      </c>
-      <c r="V100" s="22" t="n">
-        <v>10838</v>
-      </c>
-      <c r="W100" s="22" t="n">
-        <v>10435</v>
-      </c>
-      <c r="X100" s="22" t="n">
-        <v>11029</v>
-      </c>
-    </row>
     <row r="101">
-      <c r="A101" s="20" t="inlineStr">
-        <is>
-          <t>과년도 법인세</t>
-        </is>
-      </c>
-      <c r="D101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W101" s="22" t="n">
-        <v>0</v>
+      <c r="A101" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G101" s="17">
+        <f>IF(OR(G100="",C100=""),"",IF(C100&lt;=0,"",IFERROR(G100/C100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H101" s="17">
+        <f>IF(OR(H100="",D100=""),"",IF(D100&lt;=0,"",IFERROR(H100/D100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I101" s="17">
+        <f>IF(OR(I100="",E100=""),"",IF(E100&lt;=0,"",IFERROR(I100/E100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J101" s="17">
+        <f>IF(OR(J100="",F100=""),"",IF(F100&lt;=0,"",IFERROR(J100/F100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K101" s="17">
+        <f>IF(OR(K100="",G100=""),"",IF(G100&lt;=0,"",IFERROR(K100/G100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L101" s="17">
+        <f>IF(OR(L100="",H100=""),"",IF(H100&lt;=0,"",IFERROR(L100/H100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M101" s="17">
+        <f>IF(OR(M100="",I100=""),"",IF(I100&lt;=0,"",IFERROR(M100/I100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N101" s="17">
+        <f>IF(OR(N100="",J100=""),"",IF(J100&lt;=0,"",IFERROR(N100/J100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T101" s="17">
+        <f>IF(OR(T100="",S100=""),"",IF(S100&lt;=0,"",IFERROR(T100/S100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U101" s="17">
+        <f>IF(OR(U100="",T100=""),"",IF(T100&lt;=0,"",IFERROR(U100/T100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V101" s="17">
+        <f>IF(OR(V100="",U100=""),"",IF(U100&lt;=0,"",IFERROR(V100/U100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W101" s="17">
+        <f>IF(OR(W100="",V100=""),"",IF(V100&lt;=0,"",IFERROR(W100/V100-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X101" s="17">
+        <f>IF(OR(X100="",W100=""),"",IF(W100&lt;=0,"",IFERROR(X100/W100-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C102" s="22" t="n">
-        <v>4070</v>
-      </c>
-      <c r="D102" s="22" t="n">
-        <v>367</v>
-      </c>
-      <c r="E102" s="22" t="n">
-        <v>2074</v>
-      </c>
-      <c r="F102" s="22" t="n">
-        <v>-3147</v>
-      </c>
-      <c r="G102" s="22" t="n">
-        <v>-541</v>
-      </c>
-      <c r="H102" s="22" t="n">
-        <v>1086</v>
-      </c>
-      <c r="I102" s="22" t="n">
-        <v>513</v>
-      </c>
-      <c r="J102" s="22" t="n">
-        <v>-3122</v>
-      </c>
-      <c r="K102" s="22" t="n">
-        <v>2044</v>
-      </c>
-      <c r="L102" s="22" t="n">
-        <v>6694</v>
-      </c>
-      <c r="M102" s="22" t="n">
-        <v>2303</v>
-      </c>
-      <c r="N102" s="22" t="n">
-        <v>-1029</v>
+          <t>해외 자회사 송금사기 손실</t>
+        </is>
       </c>
       <c r="T102" s="22" t="n">
-        <v>-2769</v>
+        <v>-59</v>
       </c>
       <c r="U102" s="22" t="n">
-        <v>-3118</v>
-      </c>
-      <c r="V102" s="22" t="n">
-        <v>367</v>
-      </c>
-      <c r="W102" s="22" t="n">
-        <v>1086</v>
-      </c>
-      <c r="X102" s="22" t="n">
-        <v>6694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="20" t="inlineStr">
         <is>
-          <t>법인세 등 합계</t>
-        </is>
-      </c>
-      <c r="C103" s="22" t="n">
-        <v>13957</v>
-      </c>
-      <c r="D103" s="22" t="n">
-        <v>11205</v>
-      </c>
-      <c r="E103" s="22" t="n">
-        <v>11349</v>
-      </c>
-      <c r="F103" s="22" t="n">
-        <v>11640</v>
-      </c>
-      <c r="G103" s="22" t="n">
-        <v>10881</v>
-      </c>
-      <c r="H103" s="22" t="n">
-        <v>11521</v>
-      </c>
-      <c r="I103" s="22" t="n">
-        <v>12939</v>
-      </c>
-      <c r="J103" s="22" t="n">
-        <v>13614</v>
-      </c>
-      <c r="K103" s="22" t="n">
-        <v>13812</v>
-      </c>
-      <c r="L103" s="22" t="n">
-        <v>17723</v>
-      </c>
-      <c r="M103" s="22" t="n">
-        <v>16284</v>
-      </c>
-      <c r="N103" s="22" t="n">
-        <v>18022</v>
+          <t>특별손실 합계</t>
+        </is>
       </c>
       <c r="T103" s="22" t="n">
-        <v>14644</v>
+        <v>-59</v>
       </c>
       <c r="U103" s="22" t="n">
-        <v>10897</v>
-      </c>
-      <c r="V103" s="22" t="n">
-        <v>11205</v>
-      </c>
-      <c r="W103" s="22" t="n">
-        <v>11521</v>
-      </c>
-      <c r="X103" s="22" t="n">
-        <v>17723</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="n">
+        <v>48993</v>
+      </c>
+      <c r="D104" s="12" t="n">
+        <v>46609</v>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>41129</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>53651</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>44705</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>57253</v>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>51552</v>
+      </c>
+      <c r="J104" s="12" t="n">
+        <v>56353</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>51414</v>
+      </c>
+      <c r="L104" s="12" t="n">
+        <v>68166</v>
+      </c>
+      <c r="M104" s="12" t="n">
+        <v>68193</v>
+      </c>
+      <c r="N104" s="12" t="n">
+        <v>80852</v>
+      </c>
+      <c r="T104" s="12" t="n">
+        <v>51920</v>
+      </c>
+      <c r="U104" s="12" t="n">
+        <v>52308</v>
+      </c>
+      <c r="V104" s="12" t="n">
+        <v>46609</v>
+      </c>
+      <c r="W104" s="12" t="n">
+        <v>57253</v>
+      </c>
+      <c r="X104" s="12" t="n">
+        <v>68166</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="n">
+        <v>6675</v>
+      </c>
+      <c r="D105" s="22" t="n">
+        <v>10838</v>
+      </c>
+      <c r="E105" s="22" t="n">
+        <v>9275</v>
+      </c>
+      <c r="F105" s="22" t="n">
+        <v>14787</v>
+      </c>
+      <c r="G105" s="22" t="n">
+        <v>11422</v>
+      </c>
+      <c r="H105" s="22" t="n">
+        <v>10435</v>
+      </c>
+      <c r="I105" s="22" t="n">
+        <v>12426</v>
+      </c>
+      <c r="J105" s="22" t="n">
+        <v>16736</v>
+      </c>
+      <c r="K105" s="22" t="n">
+        <v>11768</v>
+      </c>
+      <c r="L105" s="22" t="n">
+        <v>11029</v>
+      </c>
+      <c r="M105" s="22" t="n">
+        <v>13981</v>
+      </c>
+      <c r="N105" s="22" t="n">
+        <v>19051</v>
+      </c>
+      <c r="T105" s="22" t="n">
+        <v>17413</v>
+      </c>
+      <c r="U105" s="22" t="n">
+        <v>14015</v>
+      </c>
+      <c r="V105" s="22" t="n">
+        <v>10838</v>
+      </c>
+      <c r="W105" s="22" t="n">
+        <v>10435</v>
+      </c>
+      <c r="X105" s="22" t="n">
+        <v>11029</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>과년도 법인세</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C107" s="22" t="n">
+        <v>4070</v>
+      </c>
+      <c r="D107" s="22" t="n">
+        <v>367</v>
+      </c>
+      <c r="E107" s="22" t="n">
+        <v>2074</v>
+      </c>
+      <c r="F107" s="22" t="n">
+        <v>-3147</v>
+      </c>
+      <c r="G107" s="22" t="n">
+        <v>-541</v>
+      </c>
+      <c r="H107" s="22" t="n">
+        <v>1086</v>
+      </c>
+      <c r="I107" s="22" t="n">
+        <v>513</v>
+      </c>
+      <c r="J107" s="22" t="n">
+        <v>-3122</v>
+      </c>
+      <c r="K107" s="22" t="n">
+        <v>2044</v>
+      </c>
+      <c r="L107" s="22" t="n">
+        <v>6694</v>
+      </c>
+      <c r="M107" s="22" t="n">
+        <v>2303</v>
+      </c>
+      <c r="N107" s="22" t="n">
+        <v>-1029</v>
+      </c>
+      <c r="T107" s="22" t="n">
+        <v>-2769</v>
+      </c>
+      <c r="U107" s="22" t="n">
+        <v>-3118</v>
+      </c>
+      <c r="V107" s="22" t="n">
+        <v>367</v>
+      </c>
+      <c r="W107" s="22" t="n">
+        <v>1086</v>
+      </c>
+      <c r="X107" s="22" t="n">
+        <v>6694</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="20" t="inlineStr">
+        <is>
+          <t>법인세 등 합계</t>
+        </is>
+      </c>
+      <c r="C108" s="22" t="n">
+        <v>13957</v>
+      </c>
+      <c r="D108" s="22" t="n">
+        <v>11205</v>
+      </c>
+      <c r="E108" s="22" t="n">
+        <v>11349</v>
+      </c>
+      <c r="F108" s="22" t="n">
+        <v>11640</v>
+      </c>
+      <c r="G108" s="22" t="n">
+        <v>10881</v>
+      </c>
+      <c r="H108" s="22" t="n">
+        <v>11521</v>
+      </c>
+      <c r="I108" s="22" t="n">
+        <v>12939</v>
+      </c>
+      <c r="J108" s="22" t="n">
+        <v>13614</v>
+      </c>
+      <c r="K108" s="22" t="n">
+        <v>13812</v>
+      </c>
+      <c r="L108" s="22" t="n">
+        <v>17723</v>
+      </c>
+      <c r="M108" s="22" t="n">
+        <v>16284</v>
+      </c>
+      <c r="N108" s="22" t="n">
+        <v>18022</v>
+      </c>
+      <c r="T108" s="22" t="n">
+        <v>14644</v>
+      </c>
+      <c r="U108" s="22" t="n">
+        <v>10897</v>
+      </c>
+      <c r="V108" s="22" t="n">
+        <v>11205</v>
+      </c>
+      <c r="W108" s="22" t="n">
+        <v>11521</v>
+      </c>
+      <c r="X108" s="22" t="n">
+        <v>17723</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C104" s="12" t="n">
+      <c r="C109" s="12" t="n">
         <v>35036</v>
       </c>
-      <c r="D104" s="12" t="n">
+      <c r="D109" s="12" t="n">
         <v>35404</v>
       </c>
-      <c r="E104" s="12" t="n">
+      <c r="E109" s="12" t="n">
         <v>29780</v>
       </c>
-      <c r="F104" s="12" t="n">
+      <c r="F109" s="12" t="n">
         <v>42011</v>
       </c>
-      <c r="G104" s="12" t="n">
+      <c r="G109" s="12" t="n">
         <v>33824</v>
       </c>
-      <c r="H104" s="12" t="n">
+      <c r="H109" s="12" t="n">
         <v>45732</v>
       </c>
-      <c r="I104" s="12" t="n">
+      <c r="I109" s="12" t="n">
         <v>38613</v>
       </c>
-      <c r="J104" s="12" t="n">
+      <c r="J109" s="12" t="n">
         <v>42739</v>
       </c>
-      <c r="K104" s="12" t="n">
+      <c r="K109" s="12" t="n">
         <v>37602</v>
       </c>
-      <c r="L104" s="12" t="n">
+      <c r="L109" s="12" t="n">
         <v>50443</v>
       </c>
-      <c r="M104" s="12" t="n">
+      <c r="M109" s="12" t="n">
         <v>51909</v>
       </c>
-      <c r="N104" s="12" t="n">
+      <c r="N109" s="12" t="n">
         <v>62830</v>
       </c>
-      <c r="T104" s="12" t="n">
+      <c r="T109" s="12" t="n">
         <v>37276</v>
       </c>
-      <c r="U104" s="12" t="n">
+      <c r="U109" s="12" t="n">
         <v>41411</v>
       </c>
-      <c r="V104" s="12" t="n">
+      <c r="V109" s="12" t="n">
         <v>35404</v>
       </c>
-      <c r="W104" s="12" t="n">
+      <c r="W109" s="12" t="n">
         <v>45732</v>
       </c>
-      <c r="X104" s="12" t="n">
+      <c r="X109" s="12" t="n">
         <v>50443</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="9" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G110" s="17">
+        <f>IF(OR(G109="",C109=""),"",IF(C109&lt;=0,"",IFERROR(G109/C109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H110" s="17">
+        <f>IF(OR(H109="",D109=""),"",IF(D109&lt;=0,"",IFERROR(H109/D109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I110" s="17">
+        <f>IF(OR(I109="",E109=""),"",IF(E109&lt;=0,"",IFERROR(I109/E109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J110" s="17">
+        <f>IF(OR(J109="",F109=""),"",IF(F109&lt;=0,"",IFERROR(J109/F109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K110" s="17">
+        <f>IF(OR(K109="",G109=""),"",IF(G109&lt;=0,"",IFERROR(K109/G109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L110" s="17">
+        <f>IF(OR(L109="",H109=""),"",IF(H109&lt;=0,"",IFERROR(L109/H109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M110" s="17">
+        <f>IF(OR(M109="",I109=""),"",IF(I109&lt;=0,"",IFERROR(M109/I109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N110" s="17">
+        <f>IF(OR(N109="",J109=""),"",IF(J109&lt;=0,"",IFERROR(N109/J109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T110" s="17">
+        <f>IF(OR(T109="",S109=""),"",IF(S109&lt;=0,"",IFERROR(T109/S109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U110" s="17">
+        <f>IF(OR(U109="",T109=""),"",IF(T109&lt;=0,"",IFERROR(U109/T109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V110" s="17">
+        <f>IF(OR(V109="",U109=""),"",IF(U109&lt;=0,"",IFERROR(V109/U109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W110" s="17">
+        <f>IF(OR(W109="",V109=""),"",IF(V109&lt;=0,"",IFERROR(W109/V109-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X110" s="17">
+        <f>IF(OR(X109="",W109=""),"",IF(W109&lt;=0,"",IFERROR(X109/W109-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
         <is>
           <t>비지배주주 순이익</t>
         </is>
       </c>
-      <c r="C105" s="12" t="n">
+      <c r="C111" s="12" t="n">
         <v>633</v>
       </c>
-      <c r="D105" s="12" t="n">
+      <c r="D111" s="12" t="n">
         <v>585</v>
       </c>
-      <c r="E105" s="12" t="n">
+      <c r="E111" s="12" t="n">
         <v>977</v>
       </c>
-      <c r="F105" s="12" t="n">
+      <c r="F111" s="12" t="n">
         <v>892</v>
       </c>
-      <c r="G105" s="12" t="n">
+      <c r="G111" s="12" t="n">
         <v>962</v>
       </c>
-      <c r="H105" s="12" t="n">
+      <c r="H111" s="12" t="n">
         <v>959</v>
       </c>
-      <c r="I105" s="12" t="n">
+      <c r="I111" s="12" t="n">
         <v>769</v>
       </c>
-      <c r="J105" s="12" t="n">
+      <c r="J111" s="12" t="n">
         <v>763</v>
       </c>
-      <c r="K105" s="12" t="n">
+      <c r="K111" s="12" t="n">
         <v>560</v>
       </c>
-      <c r="L105" s="12" t="n">
+      <c r="L111" s="12" t="n">
         <v>762</v>
       </c>
-      <c r="M105" s="12" t="n">
+      <c r="M111" s="12" t="n">
         <v>928</v>
       </c>
-      <c r="N105" s="12" t="n">
+      <c r="N111" s="12" t="n">
         <v>1235</v>
       </c>
-      <c r="T105" s="12" t="n">
+      <c r="T111" s="12" t="n">
         <v>775</v>
       </c>
-      <c r="U105" s="12" t="n">
+      <c r="U111" s="12" t="n">
         <v>631</v>
       </c>
-      <c r="V105" s="12" t="n">
+      <c r="V111" s="12" t="n">
         <v>585</v>
       </c>
-      <c r="W105" s="12" t="n">
+      <c r="W111" s="12" t="n">
         <v>959</v>
       </c>
-      <c r="X105" s="12" t="n">
+      <c r="X111" s="12" t="n">
         <v>762</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="9" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
         <is>
           <t>지배주주 순이익</t>
         </is>
       </c>
-      <c r="C106" s="12" t="n">
+      <c r="C112" s="12" t="n">
         <v>34403</v>
       </c>
-      <c r="D106" s="12" t="n">
+      <c r="D112" s="12" t="n">
         <v>34819</v>
       </c>
-      <c r="E106" s="12" t="n">
+      <c r="E112" s="12" t="n">
         <v>28803</v>
       </c>
-      <c r="F106" s="12" t="n">
+      <c r="F112" s="12" t="n">
         <v>41119</v>
       </c>
-      <c r="G106" s="12" t="n">
+      <c r="G112" s="12" t="n">
         <v>32862</v>
       </c>
-      <c r="H106" s="12" t="n">
+      <c r="H112" s="12" t="n">
         <v>44773</v>
       </c>
-      <c r="I106" s="12" t="n">
+      <c r="I112" s="12" t="n">
         <v>37844</v>
       </c>
-      <c r="J106" s="12" t="n">
+      <c r="J112" s="12" t="n">
         <v>41976</v>
       </c>
-      <c r="K106" s="12" t="n">
+      <c r="K112" s="12" t="n">
         <v>37042</v>
       </c>
-      <c r="L106" s="12" t="n">
+      <c r="L112" s="12" t="n">
         <v>49681</v>
       </c>
-      <c r="M106" s="12" t="n">
+      <c r="M112" s="12" t="n">
         <v>50981</v>
       </c>
-      <c r="N106" s="12" t="n">
+      <c r="N112" s="12" t="n">
         <v>61595</v>
       </c>
-      <c r="T106" s="12" t="n">
+      <c r="T112" s="12" t="n">
         <v>36501</v>
       </c>
-      <c r="U106" s="12" t="n">
+      <c r="U112" s="12" t="n">
         <v>40780</v>
       </c>
-      <c r="V106" s="12" t="n">
+      <c r="V112" s="12" t="n">
         <v>34819</v>
       </c>
-      <c r="W106" s="12" t="n">
+      <c r="W112" s="12" t="n">
         <v>44773</v>
       </c>
-      <c r="X106" s="12" t="n">
+      <c r="X112" s="12" t="n">
         <v>49681</v>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="18" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G113" s="17">
+        <f>IF(OR(G112="",C112=""),"",IF(C112&lt;=0,"",IFERROR(G112/C112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H113" s="17">
+        <f>IF(OR(H112="",D112=""),"",IF(D112&lt;=0,"",IFERROR(H112/D112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I113" s="17">
+        <f>IF(OR(I112="",E112=""),"",IF(E112&lt;=0,"",IFERROR(I112/E112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J113" s="17">
+        <f>IF(OR(J112="",F112=""),"",IF(F112&lt;=0,"",IFERROR(J112/F112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K113" s="17">
+        <f>IF(OR(K112="",G112=""),"",IF(G112&lt;=0,"",IFERROR(K112/G112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L113" s="17">
+        <f>IF(OR(L112="",H112=""),"",IF(H112&lt;=0,"",IFERROR(L112/H112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M113" s="17">
+        <f>IF(OR(M112="",I112=""),"",IF(I112&lt;=0,"",IFERROR(M112/I112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N113" s="17">
+        <f>IF(OR(N112="",J112=""),"",IF(J112&lt;=0,"",IFERROR(N112/J112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="T113" s="17">
+        <f>IF(OR(T112="",S112=""),"",IF(S112&lt;=0,"",IFERROR(T112/S112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U113" s="17">
+        <f>IF(OR(U112="",T112=""),"",IF(T112&lt;=0,"",IFERROR(U112/T112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V113" s="17">
+        <f>IF(OR(V112="",U112=""),"",IF(U112&lt;=0,"",IFERROR(V112/U112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W113" s="17">
+        <f>IF(OR(W112="",V112=""),"",IF(V112&lt;=0,"",IFERROR(W112/V112-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X113" s="17">
+        <f>IF(OR(X112="",W112=""),"",IF(W112&lt;=0,"",IFERROR(X112/W112-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="18" t="inlineStr">
         <is>
           <t>포괄손익 · 전 항목</t>
         </is>
       </c>
-      <c r="B108" s="44" t="inlineStr">
+      <c r="B115" s="44" t="inlineStr">
         <is>
           <t>분기 = 3개월 단독</t>
         </is>
       </c>
-      <c r="C108" s="18" t="n"/>
-      <c r="D108" s="18" t="n"/>
-      <c r="E108" s="18" t="n"/>
-      <c r="F108" s="18" t="n"/>
-      <c r="G108" s="18" t="n"/>
-      <c r="H108" s="18" t="n"/>
-      <c r="I108" s="18" t="n"/>
-      <c r="J108" s="18" t="n"/>
-      <c r="K108" s="18" t="n"/>
-      <c r="L108" s="18" t="n"/>
-      <c r="M108" s="18" t="n"/>
-      <c r="N108" s="18" t="n"/>
-      <c r="O108" s="18" t="n"/>
-      <c r="P108" s="18" t="n"/>
-      <c r="Q108" s="18" t="n"/>
-      <c r="R108" s="18" t="n"/>
-      <c r="S108" s="18" t="n"/>
-      <c r="T108" s="18" t="n"/>
-      <c r="U108" s="18" t="n"/>
-      <c r="V108" s="18" t="n"/>
-      <c r="W108" s="18" t="n"/>
-      <c r="X108" s="18" t="n"/>
-      <c r="Y108" s="18" t="n"/>
-      <c r="Z108" s="18" t="n"/>
-      <c r="AA108" s="18" t="n"/>
-      <c r="AB108" s="18" t="n"/>
-      <c r="AC108" s="18" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="inlineStr">
+      <c r="C115" s="18" t="n"/>
+      <c r="D115" s="18" t="n"/>
+      <c r="E115" s="18" t="n"/>
+      <c r="F115" s="18" t="n"/>
+      <c r="G115" s="18" t="n"/>
+      <c r="H115" s="18" t="n"/>
+      <c r="I115" s="18" t="n"/>
+      <c r="J115" s="18" t="n"/>
+      <c r="K115" s="18" t="n"/>
+      <c r="L115" s="18" t="n"/>
+      <c r="M115" s="18" t="n"/>
+      <c r="N115" s="18" t="n"/>
+      <c r="O115" s="18" t="n"/>
+      <c r="P115" s="18" t="n"/>
+      <c r="Q115" s="18" t="n"/>
+      <c r="R115" s="18" t="n"/>
+      <c r="S115" s="18" t="n"/>
+      <c r="T115" s="18" t="n"/>
+      <c r="U115" s="18" t="n"/>
+      <c r="V115" s="18" t="n"/>
+      <c r="W115" s="18" t="n"/>
+      <c r="X115" s="18" t="n"/>
+      <c r="Y115" s="18" t="n"/>
+      <c r="Z115" s="18" t="n"/>
+      <c r="AA115" s="18" t="n"/>
+      <c r="AB115" s="18" t="n"/>
+      <c r="AC115" s="18" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="B116" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C109" s="5" t="inlineStr">
+      <c r="C116" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="D109" s="5" t="inlineStr">
+      <c r="D116" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="E109" s="5" t="inlineStr">
+      <c r="E116" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="F109" s="5" t="inlineStr">
+      <c r="F116" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="G109" s="5" t="inlineStr">
+      <c r="G116" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="H109" s="5" t="inlineStr">
+      <c r="H116" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="I109" s="5" t="inlineStr">
+      <c r="I116" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="J109" s="5" t="inlineStr">
+      <c r="J116" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="K109" s="5" t="inlineStr">
+      <c r="K116" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="L109" s="5" t="inlineStr">
+      <c r="L116" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="M109" s="5" t="inlineStr">
+      <c r="M116" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="N109" s="5" t="inlineStr">
+      <c r="N116" s="5" t="inlineStr">
         <is>
           <t>2027.2Q</t>
         </is>
       </c>
-      <c r="O109" s="5" t="inlineStr">
+      <c r="O116" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P109" s="5" t="inlineStr">
+      <c r="P116" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q109" s="5" t="inlineStr">
+      <c r="Q116" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R109" s="5" t="inlineStr">
+      <c r="R116" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S109" s="5" t="inlineStr">
+      <c r="S116" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T109" s="5" t="inlineStr">
+      <c r="T116" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U109" s="5" t="inlineStr">
+      <c r="U116" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V109" s="5" t="inlineStr">
+      <c r="V116" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W109" s="5" t="inlineStr">
+      <c r="W116" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X109" s="5" t="inlineStr">
+      <c r="X116" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y109" s="5" t="inlineStr">
+      <c r="Y116" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z109" s="5" t="inlineStr">
+      <c r="Z116" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA109" s="5" t="inlineStr">
+      <c r="AA116" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB109" s="5" t="inlineStr">
+      <c r="AB116" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC109" s="5" t="inlineStr">
+      <c r="AC116" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="9" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="C110" s="12" t="n">
-        <v>35036</v>
-      </c>
-      <c r="D110" s="12" t="n">
-        <v>35404</v>
-      </c>
-      <c r="E110" s="12" t="n">
-        <v>29780</v>
-      </c>
-      <c r="F110" s="12" t="n">
-        <v>42011</v>
-      </c>
-      <c r="G110" s="12" t="n">
-        <v>33824</v>
-      </c>
-      <c r="H110" s="12" t="n">
-        <v>45732</v>
-      </c>
-      <c r="I110" s="12" t="n">
-        <v>38613</v>
-      </c>
-      <c r="J110" s="12" t="n">
-        <v>42739</v>
-      </c>
-      <c r="K110" s="12" t="n">
-        <v>37602</v>
-      </c>
-      <c r="L110" s="12" t="n">
-        <v>50443</v>
-      </c>
-      <c r="M110" s="12" t="n">
-        <v>51909</v>
-      </c>
-      <c r="N110" s="12" t="n">
-        <v>62830</v>
-      </c>
-      <c r="T110" s="12" t="n">
-        <v>37276</v>
-      </c>
-      <c r="U110" s="12" t="n">
-        <v>41411</v>
-      </c>
-      <c r="V110" s="12" t="n">
-        <v>35404</v>
-      </c>
-      <c r="W110" s="12" t="n">
-        <v>45732</v>
-      </c>
-      <c r="X110" s="12" t="n">
-        <v>50443</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="20" t="inlineStr">
-        <is>
-          <t>기타유가증권 평가차액</t>
-        </is>
-      </c>
-      <c r="C111" s="22" t="n">
-        <v>-1285</v>
-      </c>
-      <c r="D111" s="22" t="n">
-        <v>7042</v>
-      </c>
-      <c r="E111" s="22" t="n">
-        <v>-1227</v>
-      </c>
-      <c r="F111" s="22" t="n">
-        <v>-2125</v>
-      </c>
-      <c r="G111" s="22" t="n">
-        <v>1294</v>
-      </c>
-      <c r="H111" s="22" t="n">
-        <v>-4888</v>
-      </c>
-      <c r="I111" s="22" t="n">
-        <v>1134</v>
-      </c>
-      <c r="J111" s="22" t="n">
-        <v>9402</v>
-      </c>
-      <c r="K111" s="22" t="n">
-        <v>5228</v>
-      </c>
-      <c r="L111" s="22" t="n">
-        <v>-1742</v>
-      </c>
-      <c r="M111" s="22" t="n">
-        <v>14128</v>
-      </c>
-      <c r="N111" s="22" t="n">
-        <v>-3039</v>
-      </c>
-      <c r="T111" s="22" t="n">
-        <v>-921</v>
-      </c>
-      <c r="U111" s="22" t="n">
-        <v>494</v>
-      </c>
-      <c r="V111" s="22" t="n">
-        <v>7042</v>
-      </c>
-      <c r="W111" s="22" t="n">
-        <v>-4888</v>
-      </c>
-      <c r="X111" s="22" t="n">
-        <v>-1742</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="20" t="inlineStr">
-        <is>
-          <t>해외사업환산조정</t>
-        </is>
-      </c>
-      <c r="C112" s="22" t="n">
-        <v>-14503</v>
-      </c>
-      <c r="D112" s="22" t="n">
-        <v>25123</v>
-      </c>
-      <c r="E112" s="22" t="n">
-        <v>30983</v>
-      </c>
-      <c r="F112" s="22" t="n">
-        <v>-54700</v>
-      </c>
-      <c r="G112" s="22" t="n">
-        <v>33513</v>
-      </c>
-      <c r="H112" s="22" t="n">
-        <v>-24074</v>
-      </c>
-      <c r="I112" s="22" t="n">
-        <v>3386</v>
-      </c>
-      <c r="J112" s="22" t="n">
-        <v>10891</v>
-      </c>
-      <c r="K112" s="22" t="n">
-        <v>26417</v>
-      </c>
-      <c r="L112" s="22" t="n">
-        <v>2755</v>
-      </c>
-      <c r="M112" s="22" t="n">
-        <v>8524</v>
-      </c>
-      <c r="N112" s="22" t="n">
-        <v>-12477</v>
-      </c>
-      <c r="T112" s="22" t="n">
-        <v>22148</v>
-      </c>
-      <c r="U112" s="22" t="n">
-        <v>5004</v>
-      </c>
-      <c r="V112" s="22" t="n">
-        <v>25123</v>
-      </c>
-      <c r="W112" s="22" t="n">
-        <v>-24074</v>
-      </c>
-      <c r="X112" s="22" t="n">
-        <v>2755</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여 조정액</t>
-        </is>
-      </c>
-      <c r="C113" s="22" t="n">
-        <v>1161</v>
-      </c>
-      <c r="D113" s="22" t="n">
-        <v>8782</v>
-      </c>
-      <c r="E113" s="22" t="n">
-        <v>-97</v>
-      </c>
-      <c r="F113" s="22" t="n">
-        <v>1538</v>
-      </c>
-      <c r="G113" s="22" t="n">
-        <v>-426</v>
-      </c>
-      <c r="H113" s="22" t="n">
-        <v>9670</v>
-      </c>
-      <c r="I113" s="22" t="n">
-        <v>427</v>
-      </c>
-      <c r="J113" s="22" t="n">
-        <v>-17</v>
-      </c>
-      <c r="K113" s="22" t="n">
-        <v>-183</v>
-      </c>
-      <c r="L113" s="22" t="n">
-        <v>8770</v>
-      </c>
-      <c r="M113" s="22" t="n">
-        <v>-497</v>
-      </c>
-      <c r="N113" s="22" t="n">
-        <v>-136</v>
-      </c>
-      <c r="T113" s="22" t="n">
-        <v>660</v>
-      </c>
-      <c r="U113" s="22" t="n">
-        <v>-2338</v>
-      </c>
-      <c r="V113" s="22" t="n">
-        <v>8782</v>
-      </c>
-      <c r="W113" s="22" t="n">
-        <v>9670</v>
-      </c>
-      <c r="X113" s="22" t="n">
-        <v>8770</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="20" t="inlineStr">
-        <is>
-          <t>지분법 적용회사 지분 해당액</t>
-        </is>
-      </c>
-      <c r="C114" s="22" t="n">
-        <v>4696</v>
-      </c>
-      <c r="D114" s="22" t="n">
-        <v>-5231</v>
-      </c>
-      <c r="E114" s="22" t="n">
-        <v>9897</v>
-      </c>
-      <c r="F114" s="22" t="n">
-        <v>7399</v>
-      </c>
-      <c r="G114" s="22" t="n">
-        <v>-13258</v>
-      </c>
-      <c r="H114" s="22" t="n">
-        <v>9794</v>
-      </c>
-      <c r="I114" s="22" t="n">
-        <v>-8634</v>
-      </c>
-      <c r="J114" s="22" t="n">
-        <v>-3361</v>
-      </c>
-      <c r="K114" s="22" t="n">
-        <v>5175</v>
-      </c>
-      <c r="L114" s="22" t="n">
-        <v>10487</v>
-      </c>
-      <c r="M114" s="22" t="n">
-        <v>6979</v>
-      </c>
-      <c r="N114" s="22" t="n">
-        <v>4826</v>
-      </c>
-      <c r="T114" s="22" t="n">
-        <v>4202</v>
-      </c>
-      <c r="U114" s="22" t="n">
-        <v>-7749</v>
-      </c>
-      <c r="V114" s="22" t="n">
-        <v>-5231</v>
-      </c>
-      <c r="W114" s="22" t="n">
-        <v>9794</v>
-      </c>
-      <c r="X114" s="22" t="n">
-        <v>10487</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="20" t="inlineStr">
-        <is>
-          <t>기타포괄손익 합계</t>
-        </is>
-      </c>
-      <c r="C115" s="22" t="n">
-        <v>-9931</v>
-      </c>
-      <c r="D115" s="22" t="n">
-        <v>35716</v>
-      </c>
-      <c r="E115" s="22" t="n">
-        <v>39556</v>
-      </c>
-      <c r="F115" s="22" t="n">
-        <v>-47888</v>
-      </c>
-      <c r="G115" s="22" t="n">
-        <v>21123</v>
-      </c>
-      <c r="H115" s="22" t="n">
-        <v>-9498</v>
-      </c>
-      <c r="I115" s="22" t="n">
-        <v>-3687</v>
-      </c>
-      <c r="J115" s="22" t="n">
-        <v>16915</v>
-      </c>
-      <c r="K115" s="22" t="n">
-        <v>36637</v>
-      </c>
-      <c r="L115" s="22" t="n">
-        <v>20270</v>
-      </c>
-      <c r="M115" s="22" t="n">
-        <v>29134</v>
-      </c>
-      <c r="N115" s="22" t="n">
-        <v>-10826</v>
-      </c>
-      <c r="T115" s="22" t="n">
-        <v>26089</v>
-      </c>
-      <c r="U115" s="22" t="n">
-        <v>-4589</v>
-      </c>
-      <c r="V115" s="22" t="n">
-        <v>35716</v>
-      </c>
-      <c r="W115" s="22" t="n">
-        <v>-9498</v>
-      </c>
-      <c r="X115" s="22" t="n">
-        <v>20270</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="9" t="inlineStr">
-        <is>
-          <t>포괄이익</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="n">
-        <v>25105</v>
-      </c>
-      <c r="D116" s="12" t="n">
-        <v>71120</v>
-      </c>
-      <c r="E116" s="12" t="n">
-        <v>69336</v>
-      </c>
-      <c r="F116" s="12" t="n">
-        <v>-5877</v>
-      </c>
-      <c r="G116" s="12" t="n">
-        <v>54947</v>
-      </c>
-      <c r="H116" s="12" t="n">
-        <v>36234</v>
-      </c>
-      <c r="I116" s="12" t="n">
-        <v>34926</v>
-      </c>
-      <c r="J116" s="12" t="n">
-        <v>59654</v>
-      </c>
-      <c r="K116" s="12" t="n">
-        <v>74239</v>
-      </c>
-      <c r="L116" s="12" t="n">
-        <v>70713</v>
-      </c>
-      <c r="M116" s="12" t="n">
-        <v>81043</v>
-      </c>
-      <c r="N116" s="12" t="n">
-        <v>52004</v>
-      </c>
-      <c r="T116" s="12" t="n">
-        <v>63365</v>
-      </c>
-      <c r="U116" s="12" t="n">
-        <v>36822</v>
-      </c>
-      <c r="V116" s="12" t="n">
-        <v>71120</v>
-      </c>
-      <c r="W116" s="12" t="n">
-        <v>36234</v>
-      </c>
-      <c r="X116" s="12" t="n">
-        <v>70713</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="n">
+        <v>35036</v>
+      </c>
+      <c r="D117" s="12" t="n">
+        <v>35404</v>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>29780</v>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>42011</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>33824</v>
+      </c>
+      <c r="H117" s="12" t="n">
+        <v>45732</v>
+      </c>
+      <c r="I117" s="12" t="n">
+        <v>38613</v>
+      </c>
+      <c r="J117" s="12" t="n">
+        <v>42739</v>
+      </c>
+      <c r="K117" s="12" t="n">
+        <v>37602</v>
+      </c>
+      <c r="L117" s="12" t="n">
+        <v>50443</v>
+      </c>
+      <c r="M117" s="12" t="n">
+        <v>51909</v>
+      </c>
+      <c r="N117" s="12" t="n">
+        <v>62830</v>
+      </c>
+      <c r="T117" s="12" t="n">
+        <v>37276</v>
+      </c>
+      <c r="U117" s="12" t="n">
+        <v>41411</v>
+      </c>
+      <c r="V117" s="12" t="n">
+        <v>35404</v>
+      </c>
+      <c r="W117" s="12" t="n">
+        <v>45732</v>
+      </c>
+      <c r="X117" s="12" t="n">
+        <v>50443</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="20" t="inlineStr">
+        <is>
+          <t>기타유가증권 평가차액</t>
+        </is>
+      </c>
+      <c r="C118" s="22" t="n">
+        <v>-1285</v>
+      </c>
+      <c r="D118" s="22" t="n">
+        <v>7042</v>
+      </c>
+      <c r="E118" s="22" t="n">
+        <v>-1227</v>
+      </c>
+      <c r="F118" s="22" t="n">
+        <v>-2125</v>
+      </c>
+      <c r="G118" s="22" t="n">
+        <v>1294</v>
+      </c>
+      <c r="H118" s="22" t="n">
+        <v>-4888</v>
+      </c>
+      <c r="I118" s="22" t="n">
+        <v>1134</v>
+      </c>
+      <c r="J118" s="22" t="n">
+        <v>9402</v>
+      </c>
+      <c r="K118" s="22" t="n">
+        <v>5228</v>
+      </c>
+      <c r="L118" s="22" t="n">
+        <v>-1742</v>
+      </c>
+      <c r="M118" s="22" t="n">
+        <v>14128</v>
+      </c>
+      <c r="N118" s="22" t="n">
+        <v>-3039</v>
+      </c>
+      <c r="T118" s="22" t="n">
+        <v>-921</v>
+      </c>
+      <c r="U118" s="22" t="n">
+        <v>494</v>
+      </c>
+      <c r="V118" s="22" t="n">
+        <v>7042</v>
+      </c>
+      <c r="W118" s="22" t="n">
+        <v>-4888</v>
+      </c>
+      <c r="X118" s="22" t="n">
+        <v>-1742</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="20" t="inlineStr">
+        <is>
+          <t>해외사업환산조정</t>
+        </is>
+      </c>
+      <c r="C119" s="22" t="n">
+        <v>-14503</v>
+      </c>
+      <c r="D119" s="22" t="n">
+        <v>25123</v>
+      </c>
+      <c r="E119" s="22" t="n">
+        <v>30983</v>
+      </c>
+      <c r="F119" s="22" t="n">
+        <v>-54700</v>
+      </c>
+      <c r="G119" s="22" t="n">
+        <v>33513</v>
+      </c>
+      <c r="H119" s="22" t="n">
+        <v>-24074</v>
+      </c>
+      <c r="I119" s="22" t="n">
+        <v>3386</v>
+      </c>
+      <c r="J119" s="22" t="n">
+        <v>10891</v>
+      </c>
+      <c r="K119" s="22" t="n">
+        <v>26417</v>
+      </c>
+      <c r="L119" s="22" t="n">
+        <v>2755</v>
+      </c>
+      <c r="M119" s="22" t="n">
+        <v>8524</v>
+      </c>
+      <c r="N119" s="22" t="n">
+        <v>-12477</v>
+      </c>
+      <c r="T119" s="22" t="n">
+        <v>22148</v>
+      </c>
+      <c r="U119" s="22" t="n">
+        <v>5004</v>
+      </c>
+      <c r="V119" s="22" t="n">
+        <v>25123</v>
+      </c>
+      <c r="W119" s="22" t="n">
+        <v>-24074</v>
+      </c>
+      <c r="X119" s="22" t="n">
+        <v>2755</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="20" t="inlineStr">
+        <is>
+          <t>퇴직급여 조정액</t>
+        </is>
+      </c>
+      <c r="C120" s="22" t="n">
+        <v>1161</v>
+      </c>
+      <c r="D120" s="22" t="n">
+        <v>8782</v>
+      </c>
+      <c r="E120" s="22" t="n">
+        <v>-97</v>
+      </c>
+      <c r="F120" s="22" t="n">
+        <v>1538</v>
+      </c>
+      <c r="G120" s="22" t="n">
+        <v>-426</v>
+      </c>
+      <c r="H120" s="22" t="n">
+        <v>9670</v>
+      </c>
+      <c r="I120" s="22" t="n">
+        <v>427</v>
+      </c>
+      <c r="J120" s="22" t="n">
+        <v>-17</v>
+      </c>
+      <c r="K120" s="22" t="n">
+        <v>-183</v>
+      </c>
+      <c r="L120" s="22" t="n">
+        <v>8770</v>
+      </c>
+      <c r="M120" s="22" t="n">
+        <v>-497</v>
+      </c>
+      <c r="N120" s="22" t="n">
+        <v>-136</v>
+      </c>
+      <c r="T120" s="22" t="n">
+        <v>660</v>
+      </c>
+      <c r="U120" s="22" t="n">
+        <v>-2338</v>
+      </c>
+      <c r="V120" s="22" t="n">
+        <v>8782</v>
+      </c>
+      <c r="W120" s="22" t="n">
+        <v>9670</v>
+      </c>
+      <c r="X120" s="22" t="n">
+        <v>8770</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="20" t="inlineStr">
+        <is>
+          <t>지분법 적용회사 지분 해당액</t>
+        </is>
+      </c>
+      <c r="C121" s="22" t="n">
+        <v>4696</v>
+      </c>
+      <c r="D121" s="22" t="n">
+        <v>-5231</v>
+      </c>
+      <c r="E121" s="22" t="n">
+        <v>9897</v>
+      </c>
+      <c r="F121" s="22" t="n">
+        <v>7399</v>
+      </c>
+      <c r="G121" s="22" t="n">
+        <v>-13258</v>
+      </c>
+      <c r="H121" s="22" t="n">
+        <v>9794</v>
+      </c>
+      <c r="I121" s="22" t="n">
+        <v>-8634</v>
+      </c>
+      <c r="J121" s="22" t="n">
+        <v>-3361</v>
+      </c>
+      <c r="K121" s="22" t="n">
+        <v>5175</v>
+      </c>
+      <c r="L121" s="22" t="n">
+        <v>10487</v>
+      </c>
+      <c r="M121" s="22" t="n">
+        <v>6979</v>
+      </c>
+      <c r="N121" s="22" t="n">
+        <v>4826</v>
+      </c>
+      <c r="T121" s="22" t="n">
+        <v>4202</v>
+      </c>
+      <c r="U121" s="22" t="n">
+        <v>-7749</v>
+      </c>
+      <c r="V121" s="22" t="n">
+        <v>-5231</v>
+      </c>
+      <c r="W121" s="22" t="n">
+        <v>9794</v>
+      </c>
+      <c r="X121" s="22" t="n">
+        <v>10487</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="20" t="inlineStr">
+        <is>
+          <t>기타포괄손익 합계</t>
+        </is>
+      </c>
+      <c r="C122" s="22" t="n">
+        <v>-9931</v>
+      </c>
+      <c r="D122" s="22" t="n">
+        <v>35716</v>
+      </c>
+      <c r="E122" s="22" t="n">
+        <v>39556</v>
+      </c>
+      <c r="F122" s="22" t="n">
+        <v>-47888</v>
+      </c>
+      <c r="G122" s="22" t="n">
+        <v>21123</v>
+      </c>
+      <c r="H122" s="22" t="n">
+        <v>-9498</v>
+      </c>
+      <c r="I122" s="22" t="n">
+        <v>-3687</v>
+      </c>
+      <c r="J122" s="22" t="n">
+        <v>16915</v>
+      </c>
+      <c r="K122" s="22" t="n">
+        <v>36637</v>
+      </c>
+      <c r="L122" s="22" t="n">
+        <v>20270</v>
+      </c>
+      <c r="M122" s="22" t="n">
+        <v>29134</v>
+      </c>
+      <c r="N122" s="22" t="n">
+        <v>-10826</v>
+      </c>
+      <c r="T122" s="22" t="n">
+        <v>26089</v>
+      </c>
+      <c r="U122" s="22" t="n">
+        <v>-4589</v>
+      </c>
+      <c r="V122" s="22" t="n">
+        <v>35716</v>
+      </c>
+      <c r="W122" s="22" t="n">
+        <v>-9498</v>
+      </c>
+      <c r="X122" s="22" t="n">
+        <v>20270</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
+        <is>
+          <t>포괄이익</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="n">
+        <v>25105</v>
+      </c>
+      <c r="D123" s="12" t="n">
+        <v>71120</v>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v>69336</v>
+      </c>
+      <c r="F123" s="12" t="n">
+        <v>-5877</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>54947</v>
+      </c>
+      <c r="H123" s="12" t="n">
+        <v>36234</v>
+      </c>
+      <c r="I123" s="12" t="n">
+        <v>34926</v>
+      </c>
+      <c r="J123" s="12" t="n">
+        <v>59654</v>
+      </c>
+      <c r="K123" s="12" t="n">
+        <v>74239</v>
+      </c>
+      <c r="L123" s="12" t="n">
+        <v>70713</v>
+      </c>
+      <c r="M123" s="12" t="n">
+        <v>81043</v>
+      </c>
+      <c r="N123" s="12" t="n">
+        <v>52004</v>
+      </c>
+      <c r="T123" s="12" t="n">
+        <v>63365</v>
+      </c>
+      <c r="U123" s="12" t="n">
+        <v>36822</v>
+      </c>
+      <c r="V123" s="12" t="n">
+        <v>71120</v>
+      </c>
+      <c r="W123" s="12" t="n">
+        <v>36234</v>
+      </c>
+      <c r="X123" s="12" t="n">
+        <v>70713</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
           <t>지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C117" s="12" t="n">
+      <c r="C124" s="12" t="n">
         <v>24822</v>
       </c>
-      <c r="D117" s="12" t="n">
+      <c r="D124" s="12" t="n">
         <v>69882</v>
       </c>
-      <c r="E117" s="12" t="n">
+      <c r="E124" s="12" t="n">
         <v>67694</v>
       </c>
-      <c r="F117" s="12" t="n">
+      <c r="F124" s="12" t="n">
         <v>-5626</v>
       </c>
-      <c r="G117" s="12" t="n">
+      <c r="G124" s="12" t="n">
         <v>54944</v>
       </c>
-      <c r="H117" s="12" t="n">
+      <c r="H124" s="12" t="n">
         <v>34439</v>
       </c>
-      <c r="I117" s="12" t="n">
+      <c r="I124" s="12" t="n">
         <v>34308</v>
       </c>
-      <c r="J117" s="12" t="n">
+      <c r="J124" s="12" t="n">
         <v>58484</v>
       </c>
-      <c r="K117" s="12" t="n">
+      <c r="K124" s="12" t="n">
         <v>72749</v>
       </c>
-      <c r="L117" s="12" t="n">
+      <c r="L124" s="12" t="n">
         <v>69600</v>
       </c>
-      <c r="M117" s="12" t="n">
+      <c r="M124" s="12" t="n">
         <v>79669</v>
       </c>
-      <c r="N117" s="12" t="n">
+      <c r="N124" s="12" t="n">
         <v>50673</v>
       </c>
-      <c r="T117" s="12" t="n">
+      <c r="T124" s="12" t="n">
         <v>61867</v>
       </c>
-      <c r="U117" s="12" t="n">
+      <c r="U124" s="12" t="n">
         <v>36156</v>
       </c>
-      <c r="V117" s="12" t="n">
+      <c r="V124" s="12" t="n">
         <v>69882</v>
       </c>
-      <c r="W117" s="12" t="n">
+      <c r="W124" s="12" t="n">
         <v>34439</v>
       </c>
-      <c r="X117" s="12" t="n">
+      <c r="X124" s="12" t="n">
         <v>69600</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>비지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C118" s="12" t="n">
+      <c r="C125" s="12" t="n">
         <v>283</v>
       </c>
-      <c r="D118" s="12" t="n">
+      <c r="D125" s="12" t="n">
         <v>1238</v>
       </c>
-      <c r="E118" s="12" t="n">
+      <c r="E125" s="12" t="n">
         <v>1642</v>
       </c>
-      <c r="F118" s="12" t="n">
+      <c r="F125" s="12" t="n">
         <v>-251</v>
       </c>
-      <c r="G118" s="12" t="n">
+      <c r="G125" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H118" s="12" t="n">
+      <c r="H125" s="12" t="n">
         <v>1795</v>
       </c>
-      <c r="I118" s="12" t="n">
+      <c r="I125" s="12" t="n">
         <v>618</v>
       </c>
-      <c r="J118" s="12" t="n">
+      <c r="J125" s="12" t="n">
         <v>1170</v>
       </c>
-      <c r="K118" s="12" t="n">
+      <c r="K125" s="12" t="n">
         <v>1490</v>
       </c>
-      <c r="L118" s="12" t="n">
+      <c r="L125" s="12" t="n">
         <v>1113</v>
       </c>
-      <c r="M118" s="12" t="n">
+      <c r="M125" s="12" t="n">
         <v>1374</v>
       </c>
-      <c r="N118" s="12" t="n">
+      <c r="N125" s="12" t="n">
         <v>1331</v>
       </c>
-      <c r="T118" s="12" t="n">
+      <c r="T125" s="12" t="n">
         <v>1498</v>
       </c>
-      <c r="U118" s="12" t="n">
+      <c r="U125" s="12" t="n">
         <v>666</v>
       </c>
-      <c r="V118" s="12" t="n">
+      <c r="V125" s="12" t="n">
         <v>1238</v>
       </c>
-      <c r="W118" s="12" t="n">
+      <c r="W125" s="12" t="n">
         <v>1795</v>
       </c>
-      <c r="X118" s="12" t="n">
+      <c r="X125" s="12" t="n">
         <v>1113</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="18" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B120" s="44" t="inlineStr">
+      <c r="B127" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C120" s="18" t="n"/>
-      <c r="D120" s="18" t="n"/>
-      <c r="E120" s="18" t="n"/>
-      <c r="F120" s="18" t="n"/>
-      <c r="G120" s="18" t="n"/>
-      <c r="H120" s="18" t="n"/>
-      <c r="I120" s="18" t="n"/>
-      <c r="J120" s="18" t="n"/>
-      <c r="K120" s="18" t="n"/>
-      <c r="L120" s="18" t="n"/>
-      <c r="M120" s="18" t="n"/>
-      <c r="N120" s="18" t="n"/>
-      <c r="O120" s="18" t="n"/>
-      <c r="P120" s="18" t="n"/>
-      <c r="Q120" s="18" t="n"/>
-      <c r="R120" s="18" t="n"/>
-      <c r="S120" s="18" t="n"/>
-      <c r="T120" s="18" t="n"/>
-      <c r="U120" s="18" t="n"/>
-      <c r="V120" s="18" t="n"/>
-      <c r="W120" s="18" t="n"/>
-      <c r="X120" s="18" t="n"/>
-      <c r="Y120" s="18" t="n"/>
-      <c r="Z120" s="18" t="n"/>
-      <c r="AA120" s="18" t="n"/>
-      <c r="AB120" s="18" t="n"/>
-      <c r="AC120" s="18" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="inlineStr">
+      <c r="C127" s="18" t="n"/>
+      <c r="D127" s="18" t="n"/>
+      <c r="E127" s="18" t="n"/>
+      <c r="F127" s="18" t="n"/>
+      <c r="G127" s="18" t="n"/>
+      <c r="H127" s="18" t="n"/>
+      <c r="I127" s="18" t="n"/>
+      <c r="J127" s="18" t="n"/>
+      <c r="K127" s="18" t="n"/>
+      <c r="L127" s="18" t="n"/>
+      <c r="M127" s="18" t="n"/>
+      <c r="N127" s="18" t="n"/>
+      <c r="O127" s="18" t="n"/>
+      <c r="P127" s="18" t="n"/>
+      <c r="Q127" s="18" t="n"/>
+      <c r="R127" s="18" t="n"/>
+      <c r="S127" s="18" t="n"/>
+      <c r="T127" s="18" t="n"/>
+      <c r="U127" s="18" t="n"/>
+      <c r="V127" s="18" t="n"/>
+      <c r="W127" s="18" t="n"/>
+      <c r="X127" s="18" t="n"/>
+      <c r="Y127" s="18" t="n"/>
+      <c r="Z127" s="18" t="n"/>
+      <c r="AA127" s="18" t="n"/>
+      <c r="AB127" s="18" t="n"/>
+      <c r="AC127" s="18" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="B128" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C121" s="5" t="inlineStr">
+      <c r="C128" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="D121" s="5" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="E121" s="5" t="inlineStr">
+      <c r="E128" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="F121" s="5" t="inlineStr">
+      <c r="F128" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="G121" s="5" t="inlineStr">
+      <c r="G128" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="H121" s="5" t="inlineStr">
+      <c r="H128" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="I121" s="5" t="inlineStr">
+      <c r="I128" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="J121" s="5" t="inlineStr">
+      <c r="J128" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="K121" s="5" t="inlineStr">
+      <c r="K128" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="L121" s="5" t="inlineStr">
+      <c r="L128" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="M121" s="5" t="inlineStr">
+      <c r="M128" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="N121" s="5" t="inlineStr">
+      <c r="N128" s="5" t="inlineStr">
         <is>
           <t>2027.2Q</t>
         </is>
       </c>
-      <c r="O121" s="5" t="inlineStr">
+      <c r="O128" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P121" s="5" t="inlineStr">
+      <c r="P128" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q121" s="5" t="inlineStr">
+      <c r="Q128" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R121" s="5" t="inlineStr">
+      <c r="R128" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S121" s="5" t="inlineStr">
+      <c r="S128" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T121" s="5" t="inlineStr">
+      <c r="T128" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U121" s="5" t="inlineStr">
+      <c r="U128" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V121" s="5" t="inlineStr">
+      <c r="V128" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W121" s="5" t="inlineStr">
+      <c r="W128" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X121" s="5" t="inlineStr">
+      <c r="X128" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y121" s="5" t="inlineStr">
+      <c r="Y128" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z121" s="5" t="inlineStr">
+      <c r="Z128" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA121" s="5" t="inlineStr">
+      <c r="AA128" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB121" s="5" t="inlineStr">
+      <c r="AB128" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC121" s="5" t="inlineStr">
+      <c r="AC128" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="9" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="D122" s="12" t="n">
+      <c r="D129" s="12" t="n">
         <v>181755</v>
       </c>
-      <c r="F122" s="12" t="n">
+      <c r="F129" s="12" t="n">
         <v>94780</v>
       </c>
-      <c r="H122" s="12" t="n">
+      <c r="H129" s="12" t="n">
         <v>196738</v>
       </c>
-      <c r="J122" s="12" t="n">
+      <c r="J129" s="12" t="n">
         <v>107905</v>
       </c>
-      <c r="L122" s="12" t="n">
+      <c r="L129" s="12" t="n">
         <v>227485</v>
       </c>
-      <c r="N122" s="12" t="n">
+      <c r="N129" s="12" t="n">
         <v>149045</v>
       </c>
-      <c r="O122" s="12" t="n">
+      <c r="O129" s="12" t="n">
         <v>168829</v>
       </c>
-      <c r="P122" s="12" t="n">
+      <c r="P129" s="12" t="n">
         <v>249525</v>
       </c>
-      <c r="Q122" s="12" t="n">
+      <c r="Q129" s="12" t="n">
         <v>208540</v>
       </c>
-      <c r="R122" s="12" t="n">
+      <c r="R129" s="12" t="n">
         <v>100843</v>
       </c>
-      <c r="S122" s="12" t="n">
+      <c r="S129" s="12" t="n">
         <v>128744</v>
       </c>
-      <c r="T122" s="12" t="n">
+      <c r="T129" s="12" t="n">
         <v>212917</v>
       </c>
-      <c r="U122" s="12" t="n">
+      <c r="U129" s="12" t="n">
         <v>230103</v>
       </c>
-      <c r="V122" s="12" t="n">
+      <c r="V129" s="12" t="n">
         <v>181755</v>
       </c>
-      <c r="W122" s="12" t="n">
+      <c r="W129" s="12" t="n">
         <v>196738</v>
       </c>
-      <c r="X122" s="12" t="n">
+      <c r="X129" s="12" t="n">
         <v>227485</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="D123" s="22" t="n">
-        <v>49001</v>
-      </c>
-      <c r="F123" s="22" t="n">
-        <v>22655</v>
-      </c>
-      <c r="H123" s="22" t="n">
-        <v>46448</v>
-      </c>
-      <c r="J123" s="22" t="n">
-        <v>22601</v>
-      </c>
-      <c r="L123" s="22" t="n">
-        <v>47782</v>
-      </c>
-      <c r="N123" s="22" t="n">
-        <v>23147</v>
-      </c>
-      <c r="O123" s="22" t="n">
-        <v>26530</v>
-      </c>
-      <c r="P123" s="22" t="n">
-        <v>34190</v>
-      </c>
-      <c r="Q123" s="22" t="n">
-        <v>39709</v>
-      </c>
-      <c r="R123" s="22" t="n">
-        <v>45913</v>
-      </c>
-      <c r="S123" s="22" t="n">
-        <v>45102</v>
-      </c>
-      <c r="T123" s="22" t="n">
-        <v>47077</v>
-      </c>
-      <c r="U123" s="22" t="n">
-        <v>49189</v>
-      </c>
-      <c r="V123" s="22" t="n">
-        <v>49001</v>
-      </c>
-      <c r="W123" s="22" t="n">
-        <v>46448</v>
-      </c>
-      <c r="X123" s="22" t="n">
-        <v>47782</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="D124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" s="22" t="n">
-        <v>1973</v>
-      </c>
-      <c r="S124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U124" s="22" t="n">
-        <v>1224</v>
-      </c>
-      <c r="V124" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="D125" s="22" t="n">
-        <v>-410</v>
-      </c>
-      <c r="F125" s="22" t="n">
-        <v>227</v>
-      </c>
-      <c r="H125" s="22" t="n">
-        <v>522</v>
-      </c>
-      <c r="J125" s="22" t="n">
-        <v>-112</v>
-      </c>
-      <c r="L125" s="22" t="n">
-        <v>30</v>
-      </c>
-      <c r="N125" s="22" t="n">
-        <v>129</v>
-      </c>
-      <c r="O125" s="22" t="n">
-        <v>-239</v>
-      </c>
-      <c r="P125" s="22" t="n">
-        <v>462</v>
-      </c>
-      <c r="Q125" s="22" t="n">
-        <v>-200</v>
-      </c>
-      <c r="R125" s="22" t="n">
-        <v>-261</v>
-      </c>
-      <c r="S125" s="22" t="n">
-        <v>-121</v>
-      </c>
-      <c r="T125" s="22" t="n">
-        <v>195</v>
-      </c>
-      <c r="U125" s="22" t="n">
-        <v>355</v>
-      </c>
-      <c r="V125" s="22" t="n">
-        <v>-410</v>
-      </c>
-      <c r="W125" s="22" t="n">
-        <v>522</v>
-      </c>
-      <c r="X125" s="22" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여부채 증감</t>
-        </is>
-      </c>
-      <c r="D126" s="22" t="n">
-        <v>-13496</v>
-      </c>
-      <c r="F126" s="22" t="n">
-        <v>165</v>
-      </c>
-      <c r="H126" s="22" t="n">
-        <v>-11159</v>
-      </c>
-      <c r="J126" s="22" t="n">
-        <v>1016</v>
-      </c>
-      <c r="L126" s="22" t="n">
-        <v>-11838</v>
-      </c>
-      <c r="N126" s="22" t="n">
-        <v>-624</v>
-      </c>
-      <c r="O126" s="22" t="n">
-        <v>3178</v>
-      </c>
-      <c r="P126" s="22" t="n">
-        <v>-3840</v>
-      </c>
-      <c r="Q126" s="22" t="n">
-        <v>-25320</v>
-      </c>
-      <c r="R126" s="22" t="n">
-        <v>2762</v>
-      </c>
-      <c r="S126" s="22" t="n">
-        <v>4252</v>
-      </c>
-      <c r="T126" s="22" t="n">
-        <v>1851</v>
-      </c>
-      <c r="U126" s="22" t="n">
-        <v>3053</v>
-      </c>
-      <c r="V126" s="22" t="n">
-        <v>-13496</v>
-      </c>
-      <c r="W126" s="22" t="n">
-        <v>-11159</v>
-      </c>
-      <c r="X126" s="22" t="n">
-        <v>-11838</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여자산 증감</t>
-        </is>
-      </c>
-      <c r="D127" s="22" t="n">
-        <v>4175</v>
-      </c>
-      <c r="F127" s="22" t="n">
-        <v>1054</v>
-      </c>
-      <c r="H127" s="22" t="n">
-        <v>544</v>
-      </c>
-      <c r="J127" s="22" t="n">
-        <v>282</v>
-      </c>
-      <c r="L127" s="22" t="n">
-        <v>652</v>
-      </c>
-      <c r="N127" s="22" t="n">
-        <v>628</v>
-      </c>
-      <c r="P127" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" s="22" t="n">
-        <v>-6732</v>
-      </c>
-      <c r="R127" s="22" t="n">
-        <v>-7456</v>
-      </c>
-      <c r="S127" s="22" t="n">
-        <v>9040</v>
-      </c>
-      <c r="T127" s="22" t="n">
-        <v>-2232</v>
-      </c>
-      <c r="U127" s="22" t="n">
-        <v>3105</v>
-      </c>
-      <c r="V127" s="22" t="n">
-        <v>4175</v>
-      </c>
-      <c r="W127" s="22" t="n">
-        <v>544</v>
-      </c>
-      <c r="X127" s="22" t="n">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="20" t="inlineStr">
-        <is>
-          <t>이자·배당금 수익</t>
-        </is>
-      </c>
-      <c r="D128" s="22" t="n">
-        <v>-6822</v>
-      </c>
-      <c r="F128" s="22" t="n">
-        <v>-5151</v>
-      </c>
-      <c r="H128" s="22" t="n">
-        <v>-9472</v>
-      </c>
-      <c r="J128" s="22" t="n">
-        <v>-6440</v>
-      </c>
-      <c r="L128" s="22" t="n">
-        <v>-10907</v>
-      </c>
-      <c r="N128" s="22" t="n">
-        <v>-7640</v>
-      </c>
-      <c r="O128" s="22" t="n">
-        <v>-3789</v>
-      </c>
-      <c r="P128" s="22" t="n">
-        <v>-4793</v>
-      </c>
-      <c r="Q128" s="22" t="n">
-        <v>-5705</v>
-      </c>
-      <c r="R128" s="22" t="n">
-        <v>-5305</v>
-      </c>
-      <c r="S128" s="22" t="n">
-        <v>-3427</v>
-      </c>
-      <c r="T128" s="22" t="n">
-        <v>-3192</v>
-      </c>
-      <c r="U128" s="22" t="n">
-        <v>-5761</v>
-      </c>
-      <c r="V128" s="22" t="n">
-        <v>-6822</v>
-      </c>
-      <c r="W128" s="22" t="n">
-        <v>-9472</v>
-      </c>
-      <c r="X128" s="22" t="n">
-        <v>-10907</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="20" t="inlineStr">
-        <is>
-          <t>지분법손익</t>
-        </is>
-      </c>
-      <c r="D129" s="22" t="n">
-        <v>-27540</v>
-      </c>
-      <c r="F129" s="22" t="n">
-        <v>-13942</v>
-      </c>
-      <c r="H129" s="22" t="n">
-        <v>-28040</v>
-      </c>
-      <c r="J129" s="22" t="n">
-        <v>-14725</v>
-      </c>
-      <c r="L129" s="22" t="n">
-        <v>-30531</v>
-      </c>
-      <c r="N129" s="22" t="n">
-        <v>-22977</v>
-      </c>
-      <c r="O129" s="22" t="n">
-        <v>-10022</v>
-      </c>
-      <c r="P129" s="22" t="n">
-        <v>-16307</v>
-      </c>
-      <c r="Q129" s="22" t="n">
-        <v>-14243</v>
-      </c>
-      <c r="R129" s="22" t="n">
-        <v>-8752</v>
-      </c>
-      <c r="S129" s="22" t="n">
-        <v>-11640</v>
-      </c>
-      <c r="T129" s="22" t="n">
-        <v>-23126</v>
-      </c>
-      <c r="U129" s="22" t="n">
-        <v>-32371</v>
-      </c>
-      <c r="V129" s="22" t="n">
-        <v>-27540</v>
-      </c>
-      <c r="W129" s="22" t="n">
-        <v>-28040</v>
-      </c>
-      <c r="X129" s="22" t="n">
-        <v>-30531</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="D130" s="22" t="n">
-        <v>24798</v>
+        <v>49001</v>
       </c>
       <c r="F130" s="22" t="n">
-        <v>24618</v>
+        <v>22655</v>
       </c>
       <c r="H130" s="22" t="n">
-        <v>-4613</v>
+        <v>46448</v>
       </c>
       <c r="J130" s="22" t="n">
-        <v>4002</v>
+        <v>22601</v>
       </c>
       <c r="L130" s="22" t="n">
-        <v>-658</v>
+        <v>47782</v>
       </c>
       <c r="N130" s="22" t="n">
-        <v>11172</v>
+        <v>23147</v>
       </c>
       <c r="O130" s="22" t="n">
-        <v>-17386</v>
+        <v>26530</v>
       </c>
       <c r="P130" s="22" t="n">
-        <v>-51908</v>
+        <v>34190</v>
       </c>
       <c r="Q130" s="22" t="n">
-        <v>67500</v>
+        <v>39709</v>
       </c>
       <c r="R130" s="22" t="n">
-        <v>18358</v>
+        <v>45913</v>
       </c>
       <c r="S130" s="22" t="n">
-        <v>-37122</v>
+        <v>45102</v>
       </c>
       <c r="T130" s="22" t="n">
-        <v>-14498</v>
+        <v>47077</v>
       </c>
       <c r="U130" s="22" t="n">
-        <v>-3375</v>
+        <v>49189</v>
       </c>
       <c r="V130" s="22" t="n">
-        <v>24798</v>
+        <v>49001</v>
       </c>
       <c r="W130" s="22" t="n">
-        <v>-4613</v>
+        <v>46448</v>
       </c>
       <c r="X130" s="22" t="n">
-        <v>-658</v>
+        <v>47782</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>재고자산 증감</t>
+          <t>손상차손</t>
         </is>
       </c>
       <c r="D131" s="22" t="n">
-        <v>12556</v>
-      </c>
-      <c r="F131" s="22" t="n">
-        <v>21561</v>
-      </c>
-      <c r="H131" s="22" t="n">
-        <v>52489</v>
-      </c>
-      <c r="J131" s="22" t="n">
-        <v>17597</v>
-      </c>
-      <c r="L131" s="22" t="n">
-        <v>27869</v>
-      </c>
-      <c r="N131" s="22" t="n">
-        <v>-11059</v>
-      </c>
-      <c r="O131" s="22" t="n">
-        <v>-16519</v>
-      </c>
-      <c r="P131" s="22" t="n">
-        <v>-31527</v>
+        <v>0</v>
       </c>
       <c r="Q131" s="22" t="n">
-        <v>-6249</v>
+        <v>0</v>
       </c>
       <c r="R131" s="22" t="n">
-        <v>10288</v>
+        <v>1973</v>
       </c>
       <c r="S131" s="22" t="n">
-        <v>-16828</v>
+        <v>0</v>
       </c>
       <c r="T131" s="22" t="n">
-        <v>-74740</v>
+        <v>0</v>
       </c>
       <c r="U131" s="22" t="n">
-        <v>-91119</v>
+        <v>1224</v>
       </c>
       <c r="V131" s="22" t="n">
-        <v>12556</v>
-      </c>
-      <c r="W131" s="22" t="n">
-        <v>52489</v>
-      </c>
-      <c r="X131" s="22" t="n">
-        <v>27869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>매입채무 증감</t>
+          <t>대손충당금 증감</t>
         </is>
       </c>
       <c r="D132" s="22" t="n">
-        <v>-18812</v>
+        <v>-410</v>
       </c>
       <c r="F132" s="22" t="n">
-        <v>-6785</v>
+        <v>227</v>
       </c>
       <c r="H132" s="22" t="n">
-        <v>-4480</v>
+        <v>522</v>
       </c>
       <c r="J132" s="22" t="n">
-        <v>8</v>
+        <v>-112</v>
       </c>
       <c r="L132" s="22" t="n">
-        <v>5468</v>
+        <v>30</v>
       </c>
       <c r="N132" s="22" t="n">
-        <v>10067</v>
+        <v>129</v>
       </c>
       <c r="O132" s="22" t="n">
-        <v>11292</v>
+        <v>-239</v>
       </c>
       <c r="P132" s="22" t="n">
-        <v>16875</v>
+        <v>462</v>
       </c>
       <c r="Q132" s="22" t="n">
-        <v>-16393</v>
+        <v>-200</v>
       </c>
       <c r="R132" s="22" t="n">
-        <v>-8646</v>
+        <v>-261</v>
       </c>
       <c r="S132" s="22" t="n">
-        <v>15239</v>
+        <v>-121</v>
       </c>
       <c r="T132" s="22" t="n">
-        <v>2758</v>
+        <v>195</v>
       </c>
       <c r="U132" s="22" t="n">
-        <v>4632</v>
+        <v>355</v>
       </c>
       <c r="V132" s="22" t="n">
-        <v>-18812</v>
+        <v>-410</v>
       </c>
       <c r="W132" s="22" t="n">
-        <v>-4480</v>
+        <v>522</v>
       </c>
       <c r="X132" s="22" t="n">
-        <v>5468</v>
+        <v>30</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>퇴직급여부채 증감</t>
         </is>
       </c>
       <c r="D133" s="22" t="n">
-        <v>10761</v>
+        <v>-13496</v>
       </c>
       <c r="F133" s="22" t="n">
-        <v>-8859</v>
+        <v>165</v>
       </c>
       <c r="H133" s="22" t="n">
-        <v>13859</v>
+        <v>-11159</v>
       </c>
       <c r="J133" s="22" t="n">
-        <v>-8623</v>
+        <v>1016</v>
       </c>
       <c r="L133" s="22" t="n">
-        <v>3890</v>
+        <v>-11838</v>
       </c>
       <c r="N133" s="22" t="n">
-        <v>-1521</v>
+        <v>-624</v>
       </c>
       <c r="O133" s="22" t="n">
-        <v>-6470</v>
+        <v>3178</v>
       </c>
       <c r="P133" s="22" t="n">
-        <v>18369</v>
+        <v>-3840</v>
       </c>
       <c r="Q133" s="22" t="n">
-        <v>3855</v>
+        <v>-25320</v>
       </c>
       <c r="R133" s="22" t="n">
-        <v>14118</v>
+        <v>2762</v>
       </c>
       <c r="S133" s="22" t="n">
-        <v>-2985</v>
+        <v>4252</v>
       </c>
       <c r="T133" s="22" t="n">
-        <v>12445</v>
+        <v>1851</v>
       </c>
       <c r="U133" s="22" t="n">
-        <v>1027</v>
+        <v>3053</v>
       </c>
       <c r="V133" s="22" t="n">
-        <v>10761</v>
+        <v>-13496</v>
       </c>
       <c r="W133" s="22" t="n">
-        <v>13859</v>
+        <v>-11159</v>
       </c>
       <c r="X133" s="22" t="n">
-        <v>3890</v>
+        <v>-11838</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>퇴직급여자산 증감</t>
         </is>
       </c>
       <c r="D134" s="22" t="n">
-        <v>215966</v>
+        <v>4175</v>
       </c>
       <c r="F134" s="22" t="n">
-        <v>130323</v>
+        <v>1054</v>
       </c>
       <c r="H134" s="22" t="n">
-        <v>252836</v>
+        <v>544</v>
       </c>
       <c r="J134" s="22" t="n">
-        <v>123511</v>
+        <v>282</v>
       </c>
       <c r="L134" s="22" t="n">
-        <v>259242</v>
+        <v>652</v>
       </c>
       <c r="N134" s="22" t="n">
-        <v>150367</v>
-      </c>
-      <c r="O134" s="22" t="n">
-        <v>155404</v>
+        <v>628</v>
       </c>
       <c r="P134" s="22" t="n">
-        <v>211046</v>
+        <v>0</v>
       </c>
       <c r="Q134" s="22" t="n">
-        <v>244762</v>
+        <v>-6732</v>
       </c>
       <c r="R134" s="22" t="n">
-        <v>163835</v>
+        <v>-7456</v>
       </c>
       <c r="S134" s="22" t="n">
-        <v>130254</v>
+        <v>9040</v>
       </c>
       <c r="T134" s="22" t="n">
-        <v>159455</v>
+        <v>-2232</v>
       </c>
       <c r="U134" s="22" t="n">
-        <v>160062</v>
+        <v>3105</v>
       </c>
       <c r="V134" s="22" t="n">
-        <v>215966</v>
+        <v>4175</v>
       </c>
       <c r="W134" s="22" t="n">
-        <v>252836</v>
+        <v>544</v>
       </c>
       <c r="X134" s="22" t="n">
-        <v>259242</v>
+        <v>652</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="D135" s="22" t="n">
-        <v>25227</v>
+        <v>-6822</v>
       </c>
       <c r="F135" s="22" t="n">
-        <v>28878</v>
+        <v>-5151</v>
       </c>
       <c r="H135" s="22" t="n">
-        <v>33198</v>
+        <v>-9472</v>
       </c>
       <c r="J135" s="22" t="n">
-        <v>29780</v>
+        <v>-6440</v>
       </c>
       <c r="L135" s="22" t="n">
-        <v>34318</v>
+        <v>-10907</v>
       </c>
       <c r="N135" s="22" t="n">
-        <v>38898</v>
+        <v>-7640</v>
       </c>
       <c r="O135" s="22" t="n">
-        <v>8562</v>
+        <v>-3789</v>
       </c>
       <c r="P135" s="22" t="n">
-        <v>9818</v>
+        <v>-4793</v>
       </c>
       <c r="Q135" s="22" t="n">
-        <v>13662</v>
+        <v>-5705</v>
       </c>
       <c r="R135" s="22" t="n">
-        <v>11965</v>
+        <v>-5305</v>
       </c>
       <c r="S135" s="22" t="n">
-        <v>7082</v>
+        <v>-3427</v>
       </c>
       <c r="T135" s="22" t="n">
-        <v>8056</v>
+        <v>-3192</v>
       </c>
       <c r="U135" s="22" t="n">
-        <v>17546</v>
+        <v>-5761</v>
       </c>
       <c r="V135" s="22" t="n">
-        <v>25227</v>
+        <v>-6822</v>
       </c>
       <c r="W135" s="22" t="n">
-        <v>33198</v>
+        <v>-9472</v>
       </c>
       <c r="X135" s="22" t="n">
-        <v>34318</v>
+        <v>-10907</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>지분법손익</t>
         </is>
       </c>
       <c r="D136" s="22" t="n">
-        <v>-71503</v>
+        <v>-27540</v>
       </c>
       <c r="F136" s="22" t="n">
-        <v>-12528</v>
+        <v>-13942</v>
       </c>
       <c r="H136" s="22" t="n">
-        <v>-32363</v>
+        <v>-28040</v>
       </c>
       <c r="J136" s="22" t="n">
-        <v>-27025</v>
+        <v>-14725</v>
       </c>
       <c r="L136" s="22" t="n">
-        <v>-46095</v>
+        <v>-30531</v>
       </c>
       <c r="N136" s="22" t="n">
-        <v>-35039</v>
+        <v>-22977</v>
       </c>
       <c r="O136" s="22" t="n">
-        <v>-43039</v>
+        <v>-10022</v>
       </c>
       <c r="P136" s="22" t="n">
-        <v>-44983</v>
+        <v>-16307</v>
       </c>
       <c r="Q136" s="22" t="n">
-        <v>-79985</v>
+        <v>-14243</v>
       </c>
       <c r="R136" s="22" t="n">
-        <v>-29655</v>
+        <v>-8752</v>
       </c>
       <c r="S136" s="22" t="n">
-        <v>-20153</v>
+        <v>-11640</v>
       </c>
       <c r="T136" s="22" t="n">
-        <v>-43332</v>
+        <v>-23126</v>
       </c>
       <c r="U136" s="22" t="n">
-        <v>-78480</v>
+        <v>-32371</v>
       </c>
       <c r="V136" s="22" t="n">
-        <v>-71503</v>
+        <v>-27540</v>
       </c>
       <c r="W136" s="22" t="n">
-        <v>-32363</v>
+        <v>-28040</v>
       </c>
       <c r="X136" s="22" t="n">
-        <v>-46095</v>
+        <v>-30531</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="D137" s="22" t="n">
-        <v>2074</v>
+        <v>24798</v>
       </c>
       <c r="F137" s="22" t="n">
-        <v>621</v>
+        <v>24618</v>
       </c>
       <c r="H137" s="22" t="n">
-        <v>1602</v>
+        <v>-4613</v>
       </c>
       <c r="J137" s="22" t="n">
-        <v>1652</v>
+        <v>4002</v>
       </c>
       <c r="L137" s="22" t="n">
-        <v>3431</v>
+        <v>-658</v>
       </c>
       <c r="N137" s="22" t="n">
-        <v>1632</v>
+        <v>11172</v>
       </c>
       <c r="O137" s="22" t="n">
-        <v>786</v>
+        <v>-17386</v>
       </c>
       <c r="P137" s="22" t="n">
-        <v>109</v>
+        <v>-51908</v>
       </c>
       <c r="Q137" s="22" t="n">
-        <v>-701</v>
+        <v>67500</v>
       </c>
       <c r="R137" s="22" t="n">
-        <v>-1273</v>
+        <v>18358</v>
       </c>
       <c r="S137" s="22" t="n">
-        <v>813</v>
+        <v>-37122</v>
       </c>
       <c r="T137" s="22" t="n">
-        <v>1402</v>
+        <v>-14498</v>
       </c>
       <c r="U137" s="22" t="n">
-        <v>377</v>
+        <v>-3375</v>
       </c>
       <c r="V137" s="22" t="n">
-        <v>2074</v>
+        <v>24798</v>
       </c>
       <c r="W137" s="22" t="n">
-        <v>1602</v>
+        <v>-4613</v>
       </c>
       <c r="X137" s="22" t="n">
-        <v>3431</v>
+        <v>-658</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D138" s="12" t="n">
-        <v>171764</v>
-      </c>
-      <c r="F138" s="12" t="n">
-        <v>147294</v>
-      </c>
-      <c r="H138" s="12" t="n">
-        <v>255273</v>
-      </c>
-      <c r="J138" s="12" t="n">
-        <v>127918</v>
-      </c>
-      <c r="L138" s="12" t="n">
-        <v>250896</v>
-      </c>
-      <c r="N138" s="12" t="n">
-        <v>155858</v>
-      </c>
-      <c r="O138" s="12" t="n">
-        <v>121713</v>
-      </c>
-      <c r="P138" s="12" t="n">
-        <v>175990</v>
-      </c>
-      <c r="Q138" s="12" t="n">
-        <v>177738</v>
-      </c>
-      <c r="R138" s="12" t="n">
-        <v>144872</v>
-      </c>
-      <c r="S138" s="12" t="n">
-        <v>117996</v>
-      </c>
-      <c r="T138" s="12" t="n">
-        <v>125581</v>
-      </c>
-      <c r="U138" s="12" t="n">
-        <v>99505</v>
-      </c>
-      <c r="V138" s="12" t="n">
-        <v>171764</v>
-      </c>
-      <c r="W138" s="12" t="n">
-        <v>255273</v>
-      </c>
-      <c r="X138" s="12" t="n">
-        <v>250896</v>
+      <c r="A138" s="20" t="inlineStr">
+        <is>
+          <t>재고자산 증감</t>
+        </is>
+      </c>
+      <c r="D138" s="22" t="n">
+        <v>12556</v>
+      </c>
+      <c r="F138" s="22" t="n">
+        <v>21561</v>
+      </c>
+      <c r="H138" s="22" t="n">
+        <v>52489</v>
+      </c>
+      <c r="J138" s="22" t="n">
+        <v>17597</v>
+      </c>
+      <c r="L138" s="22" t="n">
+        <v>27869</v>
+      </c>
+      <c r="N138" s="22" t="n">
+        <v>-11059</v>
+      </c>
+      <c r="O138" s="22" t="n">
+        <v>-16519</v>
+      </c>
+      <c r="P138" s="22" t="n">
+        <v>-31527</v>
+      </c>
+      <c r="Q138" s="22" t="n">
+        <v>-6249</v>
+      </c>
+      <c r="R138" s="22" t="n">
+        <v>10288</v>
+      </c>
+      <c r="S138" s="22" t="n">
+        <v>-16828</v>
+      </c>
+      <c r="T138" s="22" t="n">
+        <v>-74740</v>
+      </c>
+      <c r="U138" s="22" t="n">
+        <v>-91119</v>
+      </c>
+      <c r="V138" s="22" t="n">
+        <v>12556</v>
+      </c>
+      <c r="W138" s="22" t="n">
+        <v>52489</v>
+      </c>
+      <c r="X138" s="22" t="n">
+        <v>27869</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>정기예금 예입</t>
+          <t>매입채무 증감</t>
         </is>
       </c>
       <c r="D139" s="22" t="n">
-        <v>-9290</v>
+        <v>-18812</v>
       </c>
       <c r="F139" s="22" t="n">
-        <v>-80000</v>
+        <v>-6785</v>
       </c>
       <c r="H139" s="22" t="n">
-        <v>-120000</v>
+        <v>-4480</v>
       </c>
       <c r="J139" s="22" t="n">
-        <v>-125855</v>
+        <v>8</v>
       </c>
       <c r="L139" s="22" t="n">
-        <v>-321477</v>
+        <v>5468</v>
       </c>
       <c r="N139" s="22" t="n">
-        <v>-239563</v>
+        <v>10067</v>
       </c>
       <c r="O139" s="22" t="n">
-        <v>0</v>
+        <v>11292</v>
       </c>
       <c r="P139" s="22" t="n">
-        <v>-21426</v>
+        <v>16875</v>
       </c>
       <c r="Q139" s="22" t="n">
-        <v>-60142</v>
+        <v>-16393</v>
       </c>
       <c r="R139" s="22" t="n">
-        <v>-32248</v>
+        <v>-8646</v>
       </c>
       <c r="S139" s="22" t="n">
-        <v>-31849</v>
+        <v>15239</v>
       </c>
       <c r="T139" s="22" t="n">
-        <v>-29199</v>
+        <v>2758</v>
       </c>
       <c r="U139" s="22" t="n">
-        <v>-70000</v>
+        <v>4632</v>
       </c>
       <c r="V139" s="22" t="n">
-        <v>-9290</v>
+        <v>-18812</v>
       </c>
       <c r="W139" s="22" t="n">
-        <v>-120000</v>
+        <v>-4480</v>
       </c>
       <c r="X139" s="22" t="n">
-        <v>-321477</v>
+        <v>5468</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>정기예금 인출</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="D140" s="22" t="n">
-        <v>50000</v>
+        <v>10761</v>
       </c>
       <c r="F140" s="22" t="n">
-        <v>3462</v>
+        <v>-8859</v>
       </c>
       <c r="H140" s="22" t="n">
-        <v>27526</v>
+        <v>13859</v>
       </c>
       <c r="J140" s="22" t="n">
-        <v>90000</v>
+        <v>-8623</v>
       </c>
       <c r="L140" s="22" t="n">
-        <v>286914</v>
+        <v>3890</v>
       </c>
       <c r="N140" s="22" t="n">
-        <v>141702</v>
+        <v>-1521</v>
+      </c>
+      <c r="O140" s="22" t="n">
+        <v>-6470</v>
       </c>
       <c r="P140" s="22" t="n">
-        <v>0</v>
+        <v>18369</v>
       </c>
       <c r="Q140" s="22" t="n">
-        <v>67357</v>
+        <v>3855</v>
       </c>
       <c r="R140" s="22" t="n">
-        <v>28672</v>
+        <v>14118</v>
       </c>
       <c r="S140" s="22" t="n">
-        <v>40021</v>
+        <v>-2985</v>
       </c>
       <c r="T140" s="22" t="n">
-        <v>12012</v>
+        <v>12445</v>
       </c>
       <c r="U140" s="22" t="n">
-        <v>44483</v>
+        <v>1027</v>
       </c>
       <c r="V140" s="22" t="n">
-        <v>50000</v>
+        <v>10761</v>
       </c>
       <c r="W140" s="22" t="n">
-        <v>27526</v>
+        <v>13859</v>
       </c>
       <c r="X140" s="22" t="n">
-        <v>286914</v>
+        <v>3890</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="D141" s="22" t="n">
-        <v>-53884</v>
+        <v>215966</v>
       </c>
       <c r="F141" s="22" t="n">
-        <v>-21361</v>
+        <v>130323</v>
       </c>
       <c r="H141" s="22" t="n">
-        <v>-40805</v>
+        <v>252836</v>
       </c>
       <c r="J141" s="22" t="n">
-        <v>-10151</v>
+        <v>123511</v>
       </c>
       <c r="L141" s="22" t="n">
-        <v>-21181</v>
+        <v>259242</v>
       </c>
       <c r="N141" s="22" t="n">
-        <v>-16603</v>
+        <v>150367</v>
       </c>
       <c r="O141" s="22" t="n">
-        <v>-87509</v>
+        <v>155404</v>
       </c>
       <c r="P141" s="22" t="n">
-        <v>-103016</v>
+        <v>211046</v>
       </c>
       <c r="Q141" s="22" t="n">
-        <v>-125324</v>
+        <v>244762</v>
       </c>
       <c r="R141" s="22" t="n">
-        <v>-75429</v>
+        <v>163835</v>
       </c>
       <c r="S141" s="22" t="n">
-        <v>-21768</v>
+        <v>130254</v>
       </c>
       <c r="T141" s="22" t="n">
-        <v>-34363</v>
+        <v>159455</v>
       </c>
       <c r="U141" s="22" t="n">
-        <v>-47066</v>
+        <v>160062</v>
       </c>
       <c r="V141" s="22" t="n">
-        <v>-53884</v>
+        <v>215966</v>
       </c>
       <c r="W141" s="22" t="n">
-        <v>-40805</v>
+        <v>252836</v>
       </c>
       <c r="X141" s="22" t="n">
-        <v>-21181</v>
+        <v>259242</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>이자·배당금 수취</t>
         </is>
       </c>
       <c r="D142" s="22" t="n">
-        <v>-389</v>
+        <v>25227</v>
       </c>
       <c r="F142" s="22" t="n">
-        <v>-1157</v>
+        <v>28878</v>
       </c>
       <c r="H142" s="22" t="n">
-        <v>-805</v>
+        <v>33198</v>
       </c>
       <c r="J142" s="22" t="n">
-        <v>-717</v>
+        <v>29780</v>
       </c>
       <c r="L142" s="22" t="n">
-        <v>-693</v>
+        <v>34318</v>
       </c>
       <c r="N142" s="22" t="n">
-        <v>-1259</v>
+        <v>38898</v>
       </c>
       <c r="O142" s="22" t="n">
-        <v>-1053</v>
+        <v>8562</v>
       </c>
       <c r="P142" s="22" t="n">
-        <v>-5815</v>
+        <v>9818</v>
       </c>
       <c r="Q142" s="22" t="n">
-        <v>-5234</v>
+        <v>13662</v>
       </c>
       <c r="R142" s="22" t="n">
-        <v>-5314</v>
+        <v>11965</v>
       </c>
       <c r="S142" s="22" t="n">
-        <v>-3174</v>
+        <v>7082</v>
       </c>
       <c r="T142" s="22" t="n">
-        <v>-2379</v>
+        <v>8056</v>
       </c>
       <c r="U142" s="22" t="n">
-        <v>-5415</v>
+        <v>17546</v>
       </c>
       <c r="V142" s="22" t="n">
-        <v>-389</v>
+        <v>25227</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>-805</v>
+        <v>33198</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>-693</v>
+        <v>34318</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D143" s="12" t="n">
-        <v>-13563</v>
-      </c>
-      <c r="F143" s="12" t="n">
-        <v>-99056</v>
-      </c>
-      <c r="H143" s="12" t="n">
-        <v>-134084</v>
-      </c>
-      <c r="J143" s="12" t="n">
-        <v>-46723</v>
-      </c>
-      <c r="L143" s="12" t="n">
-        <v>-56437</v>
-      </c>
-      <c r="N143" s="12" t="n">
-        <v>-115723</v>
-      </c>
-      <c r="O143" s="12" t="n">
-        <v>-88562</v>
-      </c>
-      <c r="P143" s="12" t="n">
-        <v>-130257</v>
-      </c>
-      <c r="Q143" s="12" t="n">
-        <v>-123343</v>
-      </c>
-      <c r="R143" s="12" t="n">
-        <v>-84319</v>
-      </c>
-      <c r="S143" s="12" t="n">
-        <v>-16770</v>
-      </c>
-      <c r="T143" s="12" t="n">
-        <v>-53929</v>
-      </c>
-      <c r="U143" s="12" t="n">
-        <v>-77998</v>
-      </c>
-      <c r="V143" s="12" t="n">
-        <v>-13563</v>
-      </c>
-      <c r="W143" s="12" t="n">
-        <v>-134084</v>
-      </c>
-      <c r="X143" s="12" t="n">
-        <v>-56437</v>
+      <c r="A143" s="20" t="inlineStr">
+        <is>
+          <t>법인세 납부</t>
+        </is>
+      </c>
+      <c r="D143" s="22" t="n">
+        <v>-71503</v>
+      </c>
+      <c r="F143" s="22" t="n">
+        <v>-12528</v>
+      </c>
+      <c r="H143" s="22" t="n">
+        <v>-32363</v>
+      </c>
+      <c r="J143" s="22" t="n">
+        <v>-27025</v>
+      </c>
+      <c r="L143" s="22" t="n">
+        <v>-46095</v>
+      </c>
+      <c r="N143" s="22" t="n">
+        <v>-35039</v>
+      </c>
+      <c r="O143" s="22" t="n">
+        <v>-43039</v>
+      </c>
+      <c r="P143" s="22" t="n">
+        <v>-44983</v>
+      </c>
+      <c r="Q143" s="22" t="n">
+        <v>-79985</v>
+      </c>
+      <c r="R143" s="22" t="n">
+        <v>-29655</v>
+      </c>
+      <c r="S143" s="22" t="n">
+        <v>-20153</v>
+      </c>
+      <c r="T143" s="22" t="n">
+        <v>-43332</v>
+      </c>
+      <c r="U143" s="22" t="n">
+        <v>-78480</v>
+      </c>
+      <c r="V143" s="22" t="n">
+        <v>-71503</v>
+      </c>
+      <c r="W143" s="22" t="n">
+        <v>-32363</v>
+      </c>
+      <c r="X143" s="22" t="n">
+        <v>-46095</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="D144" s="22" t="n">
-        <v>-28391</v>
+        <v>2074</v>
       </c>
       <c r="F144" s="22" t="n">
-        <v>-40261</v>
+        <v>621</v>
       </c>
       <c r="H144" s="22" t="n">
-        <v>-49555</v>
+        <v>1602</v>
       </c>
       <c r="J144" s="22" t="n">
-        <v>-665</v>
+        <v>1652</v>
       </c>
       <c r="L144" s="22" t="n">
-        <v>-553</v>
+        <v>3431</v>
       </c>
       <c r="N144" s="22" t="n">
-        <v>-50011</v>
+        <v>1632</v>
       </c>
       <c r="O144" s="22" t="n">
-        <v>-13481</v>
+        <v>786</v>
       </c>
       <c r="P144" s="22" t="n">
-        <v>-442</v>
+        <v>109</v>
       </c>
       <c r="Q144" s="22" t="n">
-        <v>-183</v>
+        <v>-701</v>
       </c>
       <c r="R144" s="22" t="n">
-        <v>-36870</v>
+        <v>-1273</v>
       </c>
       <c r="S144" s="22" t="n">
-        <v>-283</v>
+        <v>813</v>
       </c>
       <c r="T144" s="22" t="n">
-        <v>-234</v>
+        <v>1402</v>
       </c>
       <c r="U144" s="22" t="n">
-        <v>-24436</v>
+        <v>377</v>
       </c>
       <c r="V144" s="22" t="n">
-        <v>-28391</v>
+        <v>2074</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>-49555</v>
+        <v>1602</v>
       </c>
       <c r="X144" s="22" t="n">
-        <v>-553</v>
+        <v>3431</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="20" t="inlineStr">
-        <is>
-          <t>배당금 지급</t>
-        </is>
-      </c>
-      <c r="D145" s="22" t="n">
-        <v>-90096</v>
-      </c>
-      <c r="F145" s="22" t="n">
-        <v>-41493</v>
-      </c>
-      <c r="H145" s="22" t="n">
-        <v>-83133</v>
-      </c>
-      <c r="J145" s="22" t="n">
-        <v>-46554</v>
-      </c>
-      <c r="L145" s="22" t="n">
-        <v>-94459</v>
-      </c>
-      <c r="N145" s="22" t="n">
-        <v>-52018</v>
-      </c>
-      <c r="O145" s="22" t="n">
-        <v>-76505</v>
-      </c>
-      <c r="P145" s="22" t="n">
-        <v>-92003</v>
-      </c>
-      <c r="Q145" s="22" t="n">
-        <v>-173571</v>
-      </c>
-      <c r="R145" s="22" t="n">
-        <v>-102546</v>
-      </c>
-      <c r="S145" s="22" t="n">
-        <v>-50484</v>
-      </c>
-      <c r="T145" s="22" t="n">
-        <v>-86799</v>
-      </c>
-      <c r="U145" s="22" t="n">
-        <v>-96485</v>
-      </c>
-      <c r="V145" s="22" t="n">
-        <v>-90096</v>
-      </c>
-      <c r="W145" s="22" t="n">
-        <v>-83133</v>
-      </c>
-      <c r="X145" s="22" t="n">
-        <v>-94459</v>
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D145" s="12" t="n">
+        <v>171764</v>
+      </c>
+      <c r="F145" s="12" t="n">
+        <v>147294</v>
+      </c>
+      <c r="H145" s="12" t="n">
+        <v>255273</v>
+      </c>
+      <c r="J145" s="12" t="n">
+        <v>127918</v>
+      </c>
+      <c r="L145" s="12" t="n">
+        <v>250896</v>
+      </c>
+      <c r="N145" s="12" t="n">
+        <v>155858</v>
+      </c>
+      <c r="O145" s="12" t="n">
+        <v>121713</v>
+      </c>
+      <c r="P145" s="12" t="n">
+        <v>175990</v>
+      </c>
+      <c r="Q145" s="12" t="n">
+        <v>177738</v>
+      </c>
+      <c r="R145" s="12" t="n">
+        <v>144872</v>
+      </c>
+      <c r="S145" s="12" t="n">
+        <v>117996</v>
+      </c>
+      <c r="T145" s="12" t="n">
+        <v>125581</v>
+      </c>
+      <c r="U145" s="12" t="n">
+        <v>99505</v>
+      </c>
+      <c r="V145" s="12" t="n">
+        <v>171764</v>
+      </c>
+      <c r="W145" s="12" t="n">
+        <v>255273</v>
+      </c>
+      <c r="X145" s="12" t="n">
+        <v>250896</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득 예탁금 증감</t>
-        </is>
+          <t>정기예금 예입</t>
+        </is>
+      </c>
+      <c r="D146" s="22" t="n">
+        <v>-9290</v>
       </c>
       <c r="F146" s="22" t="n">
+        <v>-80000</v>
+      </c>
+      <c r="H146" s="22" t="n">
+        <v>-120000</v>
+      </c>
+      <c r="J146" s="22" t="n">
+        <v>-125855</v>
+      </c>
+      <c r="L146" s="22" t="n">
+        <v>-321477</v>
+      </c>
+      <c r="N146" s="22" t="n">
+        <v>-239563</v>
+      </c>
+      <c r="O146" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="J146" s="22" t="n">
-        <v>-10000</v>
-      </c>
-      <c r="N146" s="22" t="n">
-        <v>0</v>
+      <c r="P146" s="22" t="n">
+        <v>-21426</v>
+      </c>
+      <c r="Q146" s="22" t="n">
+        <v>-60142</v>
+      </c>
+      <c r="R146" s="22" t="n">
+        <v>-32248</v>
+      </c>
+      <c r="S146" s="22" t="n">
+        <v>-31849</v>
+      </c>
+      <c r="T146" s="22" t="n">
+        <v>-29199</v>
+      </c>
+      <c r="U146" s="22" t="n">
+        <v>-70000</v>
+      </c>
+      <c r="V146" s="22" t="n">
+        <v>-9290</v>
+      </c>
+      <c r="W146" s="22" t="n">
+        <v>-120000</v>
+      </c>
+      <c r="X146" s="22" t="n">
+        <v>-321477</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>정기예금 인출</t>
         </is>
       </c>
       <c r="D147" s="22" t="n">
-        <v>-4027</v>
+        <v>50000</v>
       </c>
       <c r="F147" s="22" t="n">
-        <v>-2737</v>
+        <v>3462</v>
       </c>
       <c r="H147" s="22" t="n">
-        <v>-3930</v>
+        <v>27526</v>
       </c>
       <c r="J147" s="22" t="n">
-        <v>-2528</v>
+        <v>90000</v>
       </c>
       <c r="L147" s="22" t="n">
-        <v>-3586</v>
+        <v>286914</v>
       </c>
       <c r="N147" s="22" t="n">
-        <v>-3683</v>
-      </c>
-      <c r="O147" s="22" t="n">
-        <v>-281</v>
+        <v>141702</v>
       </c>
       <c r="P147" s="22" t="n">
-        <v>-652</v>
+        <v>0</v>
       </c>
       <c r="Q147" s="22" t="n">
-        <v>886</v>
+        <v>67357</v>
       </c>
       <c r="R147" s="22" t="n">
-        <v>-1310</v>
+        <v>28672</v>
       </c>
       <c r="S147" s="22" t="n">
-        <v>-2365</v>
+        <v>40021</v>
       </c>
       <c r="T147" s="22" t="n">
-        <v>-2121</v>
+        <v>12012</v>
       </c>
       <c r="U147" s="22" t="n">
-        <v>-7003</v>
+        <v>44483</v>
       </c>
       <c r="V147" s="22" t="n">
-        <v>-4027</v>
+        <v>50000</v>
       </c>
       <c r="W147" s="22" t="n">
-        <v>-3930</v>
+        <v>27526</v>
       </c>
       <c r="X147" s="22" t="n">
-        <v>-3586</v>
+        <v>286914</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="D148" s="12" t="n">
-        <v>-122514</v>
-      </c>
-      <c r="F148" s="12" t="n">
-        <v>-84491</v>
-      </c>
-      <c r="H148" s="12" t="n">
-        <v>-136618</v>
-      </c>
-      <c r="J148" s="12" t="n">
-        <v>-59747</v>
-      </c>
-      <c r="L148" s="12" t="n">
-        <v>-98598</v>
-      </c>
-      <c r="N148" s="12" t="n">
-        <v>-105712</v>
-      </c>
-      <c r="O148" s="12" t="n">
-        <v>-90267</v>
-      </c>
-      <c r="P148" s="12" t="n">
-        <v>-93097</v>
-      </c>
-      <c r="Q148" s="12" t="n">
-        <v>-172868</v>
-      </c>
-      <c r="R148" s="12" t="n">
-        <v>-140726</v>
-      </c>
-      <c r="S148" s="12" t="n">
-        <v>-53132</v>
-      </c>
-      <c r="T148" s="12" t="n">
-        <v>-89154</v>
-      </c>
-      <c r="U148" s="12" t="n">
-        <v>-127924</v>
-      </c>
-      <c r="V148" s="12" t="n">
-        <v>-122514</v>
-      </c>
-      <c r="W148" s="12" t="n">
-        <v>-136618</v>
-      </c>
-      <c r="X148" s="12" t="n">
-        <v>-98598</v>
+      <c r="A148" s="20" t="inlineStr">
+        <is>
+          <t>유형자산 취득(설비투자)</t>
+        </is>
+      </c>
+      <c r="D148" s="22" t="n">
+        <v>-53884</v>
+      </c>
+      <c r="F148" s="22" t="n">
+        <v>-21361</v>
+      </c>
+      <c r="H148" s="22" t="n">
+        <v>-40805</v>
+      </c>
+      <c r="J148" s="22" t="n">
+        <v>-10151</v>
+      </c>
+      <c r="L148" s="22" t="n">
+        <v>-21181</v>
+      </c>
+      <c r="N148" s="22" t="n">
+        <v>-16603</v>
+      </c>
+      <c r="O148" s="22" t="n">
+        <v>-87509</v>
+      </c>
+      <c r="P148" s="22" t="n">
+        <v>-103016</v>
+      </c>
+      <c r="Q148" s="22" t="n">
+        <v>-125324</v>
+      </c>
+      <c r="R148" s="22" t="n">
+        <v>-75429</v>
+      </c>
+      <c r="S148" s="22" t="n">
+        <v>-21768</v>
+      </c>
+      <c r="T148" s="22" t="n">
+        <v>-34363</v>
+      </c>
+      <c r="U148" s="22" t="n">
+        <v>-47066</v>
+      </c>
+      <c r="V148" s="22" t="n">
+        <v>-53884</v>
+      </c>
+      <c r="W148" s="22" t="n">
+        <v>-40805</v>
+      </c>
+      <c r="X148" s="22" t="n">
+        <v>-21181</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="D149" s="22" t="n">
-        <v>14241</v>
+        <v>-389</v>
       </c>
       <c r="F149" s="22" t="n">
-        <v>-9489</v>
+        <v>-1157</v>
       </c>
       <c r="H149" s="22" t="n">
-        <v>-9361</v>
+        <v>-805</v>
       </c>
       <c r="J149" s="22" t="n">
-        <v>5835</v>
+        <v>-717</v>
       </c>
       <c r="L149" s="22" t="n">
-        <v>17123</v>
+        <v>-693</v>
       </c>
       <c r="N149" s="22" t="n">
-        <v>1687</v>
+        <v>-1259</v>
       </c>
       <c r="O149" s="22" t="n">
-        <v>215</v>
+        <v>-1053</v>
       </c>
       <c r="P149" s="22" t="n">
-        <v>-2283</v>
+        <v>-5815</v>
       </c>
       <c r="Q149" s="22" t="n">
-        <v>-580</v>
+        <v>-5234</v>
       </c>
       <c r="R149" s="22" t="n">
-        <v>-12533</v>
+        <v>-5314</v>
       </c>
       <c r="S149" s="22" t="n">
-        <v>14465</v>
+        <v>-3174</v>
       </c>
       <c r="T149" s="22" t="n">
-        <v>14238</v>
+        <v>-2379</v>
       </c>
       <c r="U149" s="22" t="n">
-        <v>8715</v>
+        <v>-5415</v>
       </c>
       <c r="V149" s="22" t="n">
-        <v>14241</v>
+        <v>-389</v>
       </c>
       <c r="W149" s="22" t="n">
-        <v>-9361</v>
+        <v>-805</v>
       </c>
       <c r="X149" s="22" t="n">
-        <v>17123</v>
+        <v>-693</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="20" t="inlineStr">
-        <is>
-          <t>현금성자산 증감</t>
-        </is>
-      </c>
-      <c r="D150" s="22" t="n">
-        <v>49928</v>
-      </c>
-      <c r="F150" s="22" t="n">
-        <v>-45742</v>
-      </c>
-      <c r="H150" s="22" t="n">
-        <v>-24790</v>
-      </c>
-      <c r="J150" s="22" t="n">
-        <v>27283</v>
-      </c>
-      <c r="L150" s="22" t="n">
-        <v>112984</v>
-      </c>
-      <c r="N150" s="22" t="n">
-        <v>-63890</v>
-      </c>
-      <c r="O150" s="22" t="n">
-        <v>-56901</v>
-      </c>
-      <c r="P150" s="22" t="n">
-        <v>-49647</v>
-      </c>
-      <c r="Q150" s="22" t="n">
-        <v>-119053</v>
-      </c>
-      <c r="R150" s="22" t="n">
-        <v>-92706</v>
-      </c>
-      <c r="S150" s="22" t="n">
-        <v>62559</v>
-      </c>
-      <c r="T150" s="22" t="n">
-        <v>-3264</v>
-      </c>
-      <c r="U150" s="22" t="n">
-        <v>-97702</v>
-      </c>
-      <c r="V150" s="22" t="n">
-        <v>49928</v>
-      </c>
-      <c r="W150" s="22" t="n">
-        <v>-24790</v>
-      </c>
-      <c r="X150" s="22" t="n">
-        <v>112984</v>
+      <c r="A150" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D150" s="12" t="n">
+        <v>-13563</v>
+      </c>
+      <c r="F150" s="12" t="n">
+        <v>-99056</v>
+      </c>
+      <c r="H150" s="12" t="n">
+        <v>-134084</v>
+      </c>
+      <c r="J150" s="12" t="n">
+        <v>-46723</v>
+      </c>
+      <c r="L150" s="12" t="n">
+        <v>-56437</v>
+      </c>
+      <c r="N150" s="12" t="n">
+        <v>-115723</v>
+      </c>
+      <c r="O150" s="12" t="n">
+        <v>-88562</v>
+      </c>
+      <c r="P150" s="12" t="n">
+        <v>-130257</v>
+      </c>
+      <c r="Q150" s="12" t="n">
+        <v>-123343</v>
+      </c>
+      <c r="R150" s="12" t="n">
+        <v>-84319</v>
+      </c>
+      <c r="S150" s="12" t="n">
+        <v>-16770</v>
+      </c>
+      <c r="T150" s="12" t="n">
+        <v>-53929</v>
+      </c>
+      <c r="U150" s="12" t="n">
+        <v>-77998</v>
+      </c>
+      <c r="V150" s="12" t="n">
+        <v>-13563</v>
+      </c>
+      <c r="W150" s="12" t="n">
+        <v>-134084</v>
+      </c>
+      <c r="X150" s="12" t="n">
+        <v>-56437</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="D151" s="22" t="n">
+        <v>-28391</v>
+      </c>
+      <c r="F151" s="22" t="n">
+        <v>-40261</v>
+      </c>
+      <c r="H151" s="22" t="n">
+        <v>-49555</v>
+      </c>
+      <c r="J151" s="22" t="n">
+        <v>-665</v>
+      </c>
+      <c r="L151" s="22" t="n">
+        <v>-553</v>
+      </c>
+      <c r="N151" s="22" t="n">
+        <v>-50011</v>
+      </c>
+      <c r="O151" s="22" t="n">
+        <v>-13481</v>
+      </c>
+      <c r="P151" s="22" t="n">
+        <v>-442</v>
+      </c>
+      <c r="Q151" s="22" t="n">
+        <v>-183</v>
+      </c>
+      <c r="R151" s="22" t="n">
+        <v>-36870</v>
+      </c>
+      <c r="S151" s="22" t="n">
+        <v>-283</v>
+      </c>
+      <c r="T151" s="22" t="n">
+        <v>-234</v>
+      </c>
+      <c r="U151" s="22" t="n">
+        <v>-24436</v>
+      </c>
+      <c r="V151" s="22" t="n">
+        <v>-28391</v>
+      </c>
+      <c r="W151" s="22" t="n">
+        <v>-49555</v>
+      </c>
+      <c r="X151" s="22" t="n">
+        <v>-553</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="20" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="D152" s="22" t="n">
+        <v>-90096</v>
+      </c>
+      <c r="F152" s="22" t="n">
+        <v>-41493</v>
+      </c>
+      <c r="H152" s="22" t="n">
+        <v>-83133</v>
+      </c>
+      <c r="J152" s="22" t="n">
+        <v>-46554</v>
+      </c>
+      <c r="L152" s="22" t="n">
+        <v>-94459</v>
+      </c>
+      <c r="N152" s="22" t="n">
+        <v>-52018</v>
+      </c>
+      <c r="O152" s="22" t="n">
+        <v>-76505</v>
+      </c>
+      <c r="P152" s="22" t="n">
+        <v>-92003</v>
+      </c>
+      <c r="Q152" s="22" t="n">
+        <v>-173571</v>
+      </c>
+      <c r="R152" s="22" t="n">
+        <v>-102546</v>
+      </c>
+      <c r="S152" s="22" t="n">
+        <v>-50484</v>
+      </c>
+      <c r="T152" s="22" t="n">
+        <v>-86799</v>
+      </c>
+      <c r="U152" s="22" t="n">
+        <v>-96485</v>
+      </c>
+      <c r="V152" s="22" t="n">
+        <v>-90096</v>
+      </c>
+      <c r="W152" s="22" t="n">
+        <v>-83133</v>
+      </c>
+      <c r="X152" s="22" t="n">
+        <v>-94459</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득 예탁금 증감</t>
+        </is>
+      </c>
+      <c r="F153" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="22" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="N153" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="D154" s="22" t="n">
+        <v>-4027</v>
+      </c>
+      <c r="F154" s="22" t="n">
+        <v>-2737</v>
+      </c>
+      <c r="H154" s="22" t="n">
+        <v>-3930</v>
+      </c>
+      <c r="J154" s="22" t="n">
+        <v>-2528</v>
+      </c>
+      <c r="L154" s="22" t="n">
+        <v>-3586</v>
+      </c>
+      <c r="N154" s="22" t="n">
+        <v>-3683</v>
+      </c>
+      <c r="O154" s="22" t="n">
+        <v>-281</v>
+      </c>
+      <c r="P154" s="22" t="n">
+        <v>-652</v>
+      </c>
+      <c r="Q154" s="22" t="n">
+        <v>886</v>
+      </c>
+      <c r="R154" s="22" t="n">
+        <v>-1310</v>
+      </c>
+      <c r="S154" s="22" t="n">
+        <v>-2365</v>
+      </c>
+      <c r="T154" s="22" t="n">
+        <v>-2121</v>
+      </c>
+      <c r="U154" s="22" t="n">
+        <v>-7003</v>
+      </c>
+      <c r="V154" s="22" t="n">
+        <v>-4027</v>
+      </c>
+      <c r="W154" s="22" t="n">
+        <v>-3930</v>
+      </c>
+      <c r="X154" s="22" t="n">
+        <v>-3586</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="D155" s="12" t="n">
+        <v>-122514</v>
+      </c>
+      <c r="F155" s="12" t="n">
+        <v>-84491</v>
+      </c>
+      <c r="H155" s="12" t="n">
+        <v>-136618</v>
+      </c>
+      <c r="J155" s="12" t="n">
+        <v>-59747</v>
+      </c>
+      <c r="L155" s="12" t="n">
+        <v>-98598</v>
+      </c>
+      <c r="N155" s="12" t="n">
+        <v>-105712</v>
+      </c>
+      <c r="O155" s="12" t="n">
+        <v>-90267</v>
+      </c>
+      <c r="P155" s="12" t="n">
+        <v>-93097</v>
+      </c>
+      <c r="Q155" s="12" t="n">
+        <v>-172868</v>
+      </c>
+      <c r="R155" s="12" t="n">
+        <v>-140726</v>
+      </c>
+      <c r="S155" s="12" t="n">
+        <v>-53132</v>
+      </c>
+      <c r="T155" s="12" t="n">
+        <v>-89154</v>
+      </c>
+      <c r="U155" s="12" t="n">
+        <v>-127924</v>
+      </c>
+      <c r="V155" s="12" t="n">
+        <v>-122514</v>
+      </c>
+      <c r="W155" s="12" t="n">
+        <v>-136618</v>
+      </c>
+      <c r="X155" s="12" t="n">
+        <v>-98598</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="D156" s="22" t="n">
+        <v>14241</v>
+      </c>
+      <c r="F156" s="22" t="n">
+        <v>-9489</v>
+      </c>
+      <c r="H156" s="22" t="n">
+        <v>-9361</v>
+      </c>
+      <c r="J156" s="22" t="n">
+        <v>5835</v>
+      </c>
+      <c r="L156" s="22" t="n">
+        <v>17123</v>
+      </c>
+      <c r="N156" s="22" t="n">
+        <v>1687</v>
+      </c>
+      <c r="O156" s="22" t="n">
+        <v>215</v>
+      </c>
+      <c r="P156" s="22" t="n">
+        <v>-2283</v>
+      </c>
+      <c r="Q156" s="22" t="n">
+        <v>-580</v>
+      </c>
+      <c r="R156" s="22" t="n">
+        <v>-12533</v>
+      </c>
+      <c r="S156" s="22" t="n">
+        <v>14465</v>
+      </c>
+      <c r="T156" s="22" t="n">
+        <v>14238</v>
+      </c>
+      <c r="U156" s="22" t="n">
+        <v>8715</v>
+      </c>
+      <c r="V156" s="22" t="n">
+        <v>14241</v>
+      </c>
+      <c r="W156" s="22" t="n">
+        <v>-9361</v>
+      </c>
+      <c r="X156" s="22" t="n">
+        <v>17123</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 증감</t>
+        </is>
+      </c>
+      <c r="D157" s="22" t="n">
+        <v>49928</v>
+      </c>
+      <c r="F157" s="22" t="n">
+        <v>-45742</v>
+      </c>
+      <c r="H157" s="22" t="n">
+        <v>-24790</v>
+      </c>
+      <c r="J157" s="22" t="n">
+        <v>27283</v>
+      </c>
+      <c r="L157" s="22" t="n">
+        <v>112984</v>
+      </c>
+      <c r="N157" s="22" t="n">
+        <v>-63890</v>
+      </c>
+      <c r="O157" s="22" t="n">
+        <v>-56901</v>
+      </c>
+      <c r="P157" s="22" t="n">
+        <v>-49647</v>
+      </c>
+      <c r="Q157" s="22" t="n">
+        <v>-119053</v>
+      </c>
+      <c r="R157" s="22" t="n">
+        <v>-92706</v>
+      </c>
+      <c r="S157" s="22" t="n">
+        <v>62559</v>
+      </c>
+      <c r="T157" s="22" t="n">
+        <v>-3264</v>
+      </c>
+      <c r="U157" s="22" t="n">
+        <v>-97702</v>
+      </c>
+      <c r="V157" s="22" t="n">
+        <v>49928</v>
+      </c>
+      <c r="W157" s="22" t="n">
+        <v>-24790</v>
+      </c>
+      <c r="X157" s="22" t="n">
+        <v>112984</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="20" t="inlineStr">
+        <is>
           <t>비연결 자회사 합병에 따른 현금성자산 증가</t>
         </is>
       </c>
-      <c r="O151" s="22" t="n">
+      <c r="O158" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="P151" s="22" t="n">
+      <c r="P158" s="22" t="n">
         <v>789</v>
       </c>
-      <c r="Q151" s="22" t="n">
+      <c r="Q158" s="22" t="n">
         <v>864</v>
       </c>
-      <c r="R151" s="22" t="n">
+      <c r="R158" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="S151" s="22" t="n">
+      <c r="S158" s="22" t="n">
         <v>352</v>
       </c>
-      <c r="T151" s="22" t="n">
+      <c r="T158" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9571,7 +10038,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -11005,7 +11472,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -11057,7 +11524,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -11109,7 +11576,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -11161,7 +11628,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -11213,7 +11680,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -11265,7 +11732,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -11317,7 +11784,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -11327,43 +11794,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -11387,7 +11854,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -11439,7 +11906,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -11491,7 +11958,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -11543,7 +12010,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -11595,7 +12062,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -11647,7 +12114,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -11717,7 +12184,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -11769,7 +12236,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -11779,49 +12246,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -11831,49 +12298,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -11883,49 +12350,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -11935,43 +12402,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -11995,7 +12462,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -12047,7 +12514,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -12099,7 +12566,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -12151,7 +12618,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -14073,2104 +14540,2104 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>화낙 섹터·사업 데이터</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="53" t="inlineStr">
         <is>
           <t>2단계 보고서를 만들 때 모은 자료 · 월차 · 출처는 맨 오른쪽</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="54" t="inlineStr">
         <is>
           <t>상반기 가이던스 직전</t>
         </is>
       </c>
-      <c r="B4" s="53" t="n"/>
-      <c r="C4" s="53" t="n"/>
-      <c r="D4" s="53" t="n"/>
-      <c r="E4" s="53" t="n"/>
-      <c r="F4" s="53" t="n"/>
-      <c r="G4" s="53" t="n"/>
-      <c r="H4" s="53" t="n"/>
-      <c r="I4" s="53" t="n"/>
-      <c r="J4" s="53" t="n"/>
-      <c r="K4" s="53" t="n"/>
+      <c r="B4" s="54" t="n"/>
+      <c r="C4" s="54" t="n"/>
+      <c r="D4" s="54" t="n"/>
+      <c r="E4" s="54" t="n"/>
+      <c r="F4" s="54" t="n"/>
+      <c r="G4" s="54" t="n"/>
+      <c r="H4" s="54" t="n"/>
+      <c r="I4" s="54" t="n"/>
+      <c r="J4" s="54" t="n"/>
+      <c r="K4" s="54" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="54" t="inlineStr">
+      <c r="A5" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K5" s="54" t="inlineStr">
+      <c r="K5" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="55" t="inlineStr">
+      <c r="A6" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B6" s="56" t="n">
+      <c r="B6" s="57" t="n">
         <v>4660</v>
       </c>
-      <c r="K6" s="57" t="inlineStr">
+      <c r="K6" s="58" t="inlineStr">
         <is>
           <t>7/31 상반기 예상. Q2 함의치 = 상반기 예상 − 1Q 실적 → 매출 2349.7·영업이익 509.1·순이익 493.2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="55" t="inlineStr">
+      <c r="A7" s="56" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="B7" s="56" t="n">
+      <c r="B7" s="57" t="n">
         <v>1044</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="55" t="inlineStr">
+      <c r="A8" s="56" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="B8" s="56" t="n">
+      <c r="B8" s="57" t="n">
         <v>1003</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="53" t="inlineStr">
+      <c r="A10" s="54" t="inlineStr">
         <is>
           <t>컨센서스 · 3Q</t>
         </is>
       </c>
-      <c r="B10" s="53" t="n"/>
-      <c r="C10" s="53" t="n"/>
-      <c r="D10" s="53" t="n"/>
-      <c r="E10" s="53" t="n"/>
-      <c r="F10" s="53" t="n"/>
-      <c r="G10" s="53" t="n"/>
-      <c r="H10" s="53" t="n"/>
-      <c r="I10" s="53" t="n"/>
-      <c r="J10" s="53" t="n"/>
-      <c r="K10" s="53" t="n"/>
+      <c r="B10" s="54" t="n"/>
+      <c r="C10" s="54" t="n"/>
+      <c r="D10" s="54" t="n"/>
+      <c r="E10" s="54" t="n"/>
+      <c r="F10" s="54" t="n"/>
+      <c r="G10" s="54" t="n"/>
+      <c r="H10" s="54" t="n"/>
+      <c r="I10" s="54" t="n"/>
+      <c r="J10" s="54" t="n"/>
+      <c r="K10" s="54" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="54" t="inlineStr">
+      <c r="A11" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B11" s="54" t="inlineStr">
+      <c r="B11" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K11" s="54" t="inlineStr">
+      <c r="K11" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="55" t="inlineStr">
+      <c r="A12" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B12" s="58" t="n">
+      <c r="B12" s="59" t="n">
         <v>2509.3</v>
       </c>
-      <c r="K12" s="57" t="inlineStr">
+      <c r="K12" s="58" t="inlineStr">
         <is>
           <t>야후 파이낸스(jp_consensus) 2026-10-23 · 컨센 FY27은 10/23 가이던스 상향 전 숫자가 대부분 — 가이던스(EPS 246)가 컨센(231)보다 높음</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="55" t="inlineStr">
+      <c r="A13" s="56" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="B13" s="58" t="n">
+      <c r="B13" s="59" t="n">
         <v>61.17</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="55" t="inlineStr">
+      <c r="A14" s="56" t="inlineStr">
         <is>
           <t>EPS 애널리스트 수</t>
         </is>
       </c>
-      <c r="B14" s="56" t="n">
+      <c r="B14" s="57" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="55" t="inlineStr">
+      <c r="A15" s="56" t="inlineStr">
         <is>
           <t>매출 애널리스트 수</t>
         </is>
       </c>
-      <c r="B15" s="56" t="n">
+      <c r="B15" s="57" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="53" t="inlineStr">
+      <c r="A17" s="54" t="inlineStr">
         <is>
           <t>컨센서스 · 4Q</t>
         </is>
       </c>
-      <c r="B17" s="53" t="n"/>
-      <c r="C17" s="53" t="n"/>
-      <c r="D17" s="53" t="n"/>
-      <c r="E17" s="53" t="n"/>
-      <c r="F17" s="53" t="n"/>
-      <c r="G17" s="53" t="n"/>
-      <c r="H17" s="53" t="n"/>
-      <c r="I17" s="53" t="n"/>
-      <c r="J17" s="53" t="n"/>
-      <c r="K17" s="53" t="n"/>
+      <c r="B17" s="54" t="n"/>
+      <c r="C17" s="54" t="n"/>
+      <c r="D17" s="54" t="n"/>
+      <c r="E17" s="54" t="n"/>
+      <c r="F17" s="54" t="n"/>
+      <c r="G17" s="54" t="n"/>
+      <c r="H17" s="54" t="n"/>
+      <c r="I17" s="54" t="n"/>
+      <c r="J17" s="54" t="n"/>
+      <c r="K17" s="54" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="54" t="inlineStr">
+      <c r="A18" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B18" s="54" t="inlineStr">
+      <c r="B18" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K18" s="54" t="inlineStr">
+      <c r="K18" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="55" t="inlineStr">
+      <c r="A19" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B19" s="58" t="n">
+      <c r="B19" s="59" t="n">
         <v>2672.4</v>
       </c>
-      <c r="K19" s="57" t="inlineStr">
+      <c r="K19" s="58" t="inlineStr">
         <is>
           <t>야후 파이낸스(jp_consensus) 2026-10-23 · 컨센 FY27은 10/23 가이던스 상향 전 숫자가 대부분 — 가이던스(EPS 246)가 컨센(231)보다 높음</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="55" t="inlineStr">
+      <c r="A20" s="56" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="B20" s="58" t="n">
+      <c r="B20" s="59" t="n">
         <v>62.87</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="53" t="inlineStr">
+      <c r="A22" s="54" t="inlineStr">
         <is>
           <t>컨센서스 · fy27</t>
         </is>
       </c>
-      <c r="B22" s="53" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="53" t="n"/>
-      <c r="E22" s="53" t="n"/>
-      <c r="F22" s="53" t="n"/>
-      <c r="G22" s="53" t="n"/>
-      <c r="H22" s="53" t="n"/>
-      <c r="I22" s="53" t="n"/>
-      <c r="J22" s="53" t="n"/>
-      <c r="K22" s="53" t="n"/>
+      <c r="B22" s="54" t="n"/>
+      <c r="C22" s="54" t="n"/>
+      <c r="D22" s="54" t="n"/>
+      <c r="E22" s="54" t="n"/>
+      <c r="F22" s="54" t="n"/>
+      <c r="G22" s="54" t="n"/>
+      <c r="H22" s="54" t="n"/>
+      <c r="I22" s="54" t="n"/>
+      <c r="J22" s="54" t="n"/>
+      <c r="K22" s="54" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="54" t="inlineStr">
+      <c r="A23" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B23" s="54" t="inlineStr">
+      <c r="B23" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K23" s="54" t="inlineStr">
+      <c r="K23" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="55" t="inlineStr">
+      <c r="A24" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B24" s="58" t="n">
+      <c r="B24" s="59" t="n">
         <v>9860.700000000001</v>
       </c>
-      <c r="K24" s="57" t="inlineStr">
+      <c r="K24" s="58" t="inlineStr">
         <is>
           <t>야후 파이낸스(jp_consensus) 2026-10-23 · 컨센 FY27은 10/23 가이던스 상향 전 숫자가 대부분 — 가이던스(EPS 246)가 컨센(231)보다 높음</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="55" t="inlineStr">
+      <c r="A25" s="56" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="B25" s="58" t="n">
+      <c r="B25" s="59" t="n">
         <v>230.86</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="55" t="inlineStr">
+      <c r="A26" s="56" t="inlineStr">
         <is>
           <t>애널리스트 수</t>
         </is>
       </c>
-      <c r="B26" s="56" t="n">
+      <c r="B26" s="57" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="55" t="inlineStr">
+      <c r="A27" s="56" t="inlineStr">
         <is>
           <t>90일 전 EPS</t>
         </is>
       </c>
-      <c r="B27" s="58" t="n">
+      <c r="B27" s="59" t="n">
         <v>213.95</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="53" t="inlineStr">
+      <c r="A29" s="54" t="inlineStr">
         <is>
           <t>컨센서스 · fy28</t>
         </is>
       </c>
-      <c r="B29" s="53" t="n"/>
-      <c r="C29" s="53" t="n"/>
-      <c r="D29" s="53" t="n"/>
-      <c r="E29" s="53" t="n"/>
-      <c r="F29" s="53" t="n"/>
-      <c r="G29" s="53" t="n"/>
-      <c r="H29" s="53" t="n"/>
-      <c r="I29" s="53" t="n"/>
-      <c r="J29" s="53" t="n"/>
-      <c r="K29" s="53" t="n"/>
+      <c r="B29" s="54" t="n"/>
+      <c r="C29" s="54" t="n"/>
+      <c r="D29" s="54" t="n"/>
+      <c r="E29" s="54" t="n"/>
+      <c r="F29" s="54" t="n"/>
+      <c r="G29" s="54" t="n"/>
+      <c r="H29" s="54" t="n"/>
+      <c r="I29" s="54" t="n"/>
+      <c r="J29" s="54" t="n"/>
+      <c r="K29" s="54" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="54" t="inlineStr">
+      <c r="A30" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B30" s="54" t="inlineStr">
+      <c r="B30" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K30" s="54" t="inlineStr">
+      <c r="K30" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="55" t="inlineStr">
+      <c r="A31" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B31" s="58" t="n">
+      <c r="B31" s="59" t="n">
         <v>10418.9</v>
       </c>
-      <c r="K31" s="57" t="inlineStr">
+      <c r="K31" s="58" t="inlineStr">
         <is>
           <t>야후 파이낸스(jp_consensus) 2026-10-23 · 컨센 FY27은 10/23 가이던스 상향 전 숫자가 대부분 — 가이던스(EPS 246)가 컨센(231)보다 높음</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="55" t="inlineStr">
+      <c r="A32" s="56" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="B32" s="58" t="n">
+      <c r="B32" s="59" t="n">
         <v>241.13</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="55" t="inlineStr">
+      <c r="A33" s="56" t="inlineStr">
         <is>
           <t>애널리스트 수</t>
         </is>
       </c>
-      <c r="B33" s="56" t="n">
+      <c r="B33" s="57" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="55" t="inlineStr">
+      <c r="A34" s="56" t="inlineStr">
         <is>
           <t>90일 전 EPS</t>
         </is>
       </c>
-      <c r="B34" s="58" t="n">
+      <c r="B34" s="59" t="n">
         <v>228.81</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="53" t="inlineStr">
+      <c r="A36" s="54" t="inlineStr">
         <is>
           <t>컨센서스 · 목표주가</t>
         </is>
       </c>
-      <c r="B36" s="53" t="n"/>
-      <c r="C36" s="53" t="n"/>
-      <c r="D36" s="53" t="n"/>
-      <c r="E36" s="53" t="n"/>
-      <c r="F36" s="53" t="n"/>
-      <c r="G36" s="53" t="n"/>
-      <c r="H36" s="53" t="n"/>
-      <c r="I36" s="53" t="n"/>
-      <c r="J36" s="53" t="n"/>
-      <c r="K36" s="53" t="n"/>
+      <c r="B36" s="54" t="n"/>
+      <c r="C36" s="54" t="n"/>
+      <c r="D36" s="54" t="n"/>
+      <c r="E36" s="54" t="n"/>
+      <c r="F36" s="54" t="n"/>
+      <c r="G36" s="54" t="n"/>
+      <c r="H36" s="54" t="n"/>
+      <c r="I36" s="54" t="n"/>
+      <c r="J36" s="54" t="n"/>
+      <c r="K36" s="54" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="54" t="inlineStr">
+      <c r="A37" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B37" s="54" t="inlineStr">
+      <c r="B37" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K37" s="54" t="inlineStr">
+      <c r="K37" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="55" t="inlineStr">
+      <c r="A38" s="56" t="inlineStr">
         <is>
           <t>평균</t>
         </is>
       </c>
-      <c r="B38" s="56" t="n">
+      <c r="B38" s="57" t="n">
         <v>7296</v>
       </c>
-      <c r="K38" s="57" t="inlineStr">
+      <c r="K38" s="58" t="inlineStr">
         <is>
           <t>야후 파이낸스(jp_consensus) 2026-10-23 · 컨센 FY27은 10/23 가이던스 상향 전 숫자가 대부분 — 가이던스(EPS 246)가 컨센(231)보다 높음</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="55" t="inlineStr">
+      <c r="A39" s="56" t="inlineStr">
         <is>
           <t>중앙값</t>
         </is>
       </c>
-      <c r="B39" s="56" t="n">
+      <c r="B39" s="57" t="n">
         <v>7300</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="55" t="inlineStr">
+      <c r="A40" s="56" t="inlineStr">
         <is>
           <t>최고</t>
         </is>
       </c>
-      <c r="B40" s="56" t="n">
+      <c r="B40" s="57" t="n">
         <v>8700</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="55" t="inlineStr">
+      <c r="A41" s="56" t="inlineStr">
         <is>
           <t>최저</t>
         </is>
       </c>
-      <c r="B41" s="56" t="n">
+      <c r="B41" s="57" t="n">
         <v>4900</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="55" t="inlineStr">
+      <c r="A42" s="56" t="inlineStr">
         <is>
           <t>애널리스트 수</t>
         </is>
       </c>
-      <c r="B42" s="56" t="n">
+      <c r="B42" s="57" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="53" t="inlineStr">
+      <c r="A44" s="54" t="inlineStr">
         <is>
           <t>부문별 매출</t>
         </is>
       </c>
-      <c r="B44" s="53" t="n"/>
-      <c r="C44" s="53" t="n"/>
-      <c r="D44" s="53" t="n"/>
-      <c r="E44" s="53" t="n"/>
-      <c r="F44" s="53" t="n"/>
-      <c r="G44" s="53" t="n"/>
-      <c r="H44" s="53" t="n"/>
-      <c r="I44" s="53" t="n"/>
-      <c r="J44" s="53" t="n"/>
-      <c r="K44" s="53" t="n"/>
+      <c r="B44" s="54" t="n"/>
+      <c r="C44" s="54" t="n"/>
+      <c r="D44" s="54" t="n"/>
+      <c r="E44" s="54" t="n"/>
+      <c r="F44" s="54" t="n"/>
+      <c r="G44" s="54" t="n"/>
+      <c r="H44" s="54" t="n"/>
+      <c r="I44" s="54" t="n"/>
+      <c r="J44" s="54" t="n"/>
+      <c r="K44" s="54" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="54" t="inlineStr">
+      <c r="A45" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B45" s="54" t="inlineStr">
+      <c r="B45" s="55" t="inlineStr">
         <is>
           <t>24.7~9</t>
         </is>
       </c>
-      <c r="C45" s="54" t="inlineStr">
+      <c r="C45" s="55" t="inlineStr">
         <is>
           <t>24.10~12</t>
         </is>
       </c>
-      <c r="D45" s="54" t="inlineStr">
+      <c r="D45" s="55" t="inlineStr">
         <is>
           <t>25.1~3</t>
         </is>
       </c>
-      <c r="E45" s="54" t="inlineStr">
+      <c r="E45" s="55" t="inlineStr">
         <is>
           <t>25.4~6</t>
         </is>
       </c>
-      <c r="F45" s="54" t="inlineStr">
+      <c r="F45" s="55" t="inlineStr">
         <is>
           <t>25.7~9</t>
         </is>
       </c>
-      <c r="G45" s="54" t="inlineStr">
+      <c r="G45" s="55" t="inlineStr">
         <is>
           <t>25.10~12</t>
         </is>
       </c>
-      <c r="H45" s="54" t="inlineStr">
+      <c r="H45" s="55" t="inlineStr">
         <is>
           <t>26.1~3</t>
         </is>
       </c>
-      <c r="I45" s="54" t="inlineStr">
+      <c r="I45" s="55" t="inlineStr">
         <is>
           <t>26.4~6</t>
         </is>
       </c>
-      <c r="J45" s="54" t="inlineStr">
+      <c r="J45" s="55" t="inlineStr">
         <is>
           <t>26.7~9</t>
         </is>
       </c>
-      <c r="K45" s="54" t="inlineStr">
+      <c r="K45" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="55" t="inlineStr">
+      <c r="A46" s="56" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
       </c>
-      <c r="B46" s="56" t="n">
+      <c r="B46" s="57" t="n">
         <v>514</v>
       </c>
-      <c r="C46" s="56" t="n">
+      <c r="C46" s="57" t="n">
         <v>480</v>
       </c>
-      <c r="D46" s="56" t="n">
+      <c r="D46" s="57" t="n">
         <v>474</v>
       </c>
-      <c r="E46" s="56" t="n">
+      <c r="E46" s="57" t="n">
         <v>497</v>
       </c>
-      <c r="F46" s="56" t="n">
+      <c r="F46" s="57" t="n">
         <v>542</v>
       </c>
-      <c r="G46" s="56" t="n">
+      <c r="G46" s="57" t="n">
         <v>498</v>
       </c>
-      <c r="H46" s="56" t="n">
+      <c r="H46" s="57" t="n">
         <v>548</v>
       </c>
-      <c r="I46" s="56" t="n">
+      <c r="I46" s="57" t="n">
         <v>574</v>
       </c>
-      <c r="J46" s="56" t="n">
+      <c r="J46" s="57" t="n">
         <v>625</v>
       </c>
-      <c r="K46" s="57" t="inlineStr">
+      <c r="K46" s="58" t="inlineStr">
         <is>
           <t>설명회 자료 부문별 매출(억 엔)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="55" t="inlineStr">
+      <c r="A47" s="56" t="inlineStr">
         <is>
           <t>로봇</t>
         </is>
       </c>
-      <c r="B47" s="56" t="n">
+      <c r="B47" s="57" t="n">
         <v>790</v>
       </c>
-      <c r="C47" s="56" t="n">
+      <c r="C47" s="57" t="n">
         <v>793</v>
       </c>
-      <c r="D47" s="56" t="n">
+      <c r="D47" s="57" t="n">
         <v>872</v>
       </c>
-      <c r="E47" s="56" t="n">
+      <c r="E47" s="57" t="n">
         <v>810</v>
       </c>
-      <c r="F47" s="56" t="n">
+      <c r="F47" s="57" t="n">
         <v>916</v>
       </c>
-      <c r="G47" s="56" t="n">
+      <c r="G47" s="57" t="n">
         <v>966</v>
       </c>
-      <c r="H47" s="56" t="n">
+      <c r="H47" s="57" t="n">
         <v>1094</v>
       </c>
-      <c r="I47" s="56" t="n">
+      <c r="I47" s="57" t="n">
         <v>961</v>
       </c>
-      <c r="J47" s="56" t="n">
+      <c r="J47" s="57" t="n">
         <v>982</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="55" t="inlineStr">
+      <c r="A48" s="56" t="inlineStr">
         <is>
           <t>로보머신</t>
         </is>
       </c>
-      <c r="B48" s="56" t="n">
+      <c r="B48" s="57" t="n">
         <v>278</v>
       </c>
-      <c r="C48" s="56" t="n">
+      <c r="C48" s="57" t="n">
         <v>359</v>
       </c>
-      <c r="D48" s="56" t="n">
+      <c r="D48" s="57" t="n">
         <v>448</v>
       </c>
-      <c r="E48" s="56" t="n">
+      <c r="E48" s="57" t="n">
         <v>339</v>
       </c>
-      <c r="F48" s="56" t="n">
+      <c r="F48" s="57" t="n">
         <v>296</v>
       </c>
-      <c r="G48" s="56" t="n">
+      <c r="G48" s="57" t="n">
         <v>330</v>
       </c>
-      <c r="H48" s="56" t="n">
+      <c r="H48" s="57" t="n">
         <v>331</v>
       </c>
-      <c r="I48" s="56" t="n">
+      <c r="I48" s="57" t="n">
         <v>417</v>
       </c>
-      <c r="J48" s="56" t="n">
+      <c r="J48" s="57" t="n">
         <v>416</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="55" t="inlineStr">
+      <c r="A49" s="56" t="inlineStr">
         <is>
           <t>서비스</t>
         </is>
       </c>
-      <c r="B49" s="56" t="n">
+      <c r="B49" s="57" t="n">
         <v>347</v>
       </c>
-      <c r="C49" s="56" t="n">
+      <c r="C49" s="57" t="n">
         <v>339</v>
       </c>
-      <c r="D49" s="56" t="n">
+      <c r="D49" s="57" t="n">
         <v>328</v>
       </c>
-      <c r="E49" s="56" t="n">
+      <c r="E49" s="57" t="n">
         <v>318</v>
       </c>
-      <c r="F49" s="56" t="n">
+      <c r="F49" s="57" t="n">
         <v>358</v>
       </c>
-      <c r="G49" s="56" t="n">
+      <c r="G49" s="57" t="n">
         <v>363</v>
       </c>
-      <c r="H49" s="56" t="n">
+      <c r="H49" s="57" t="n">
         <v>372</v>
       </c>
-      <c r="I49" s="56" t="n">
+      <c r="I49" s="57" t="n">
         <v>359</v>
       </c>
-      <c r="J49" s="56" t="n">
+      <c r="J49" s="57" t="n">
         <v>403</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="53" t="inlineStr">
+      <c r="A51" s="54" t="inlineStr">
         <is>
           <t>수주</t>
         </is>
       </c>
-      <c r="B51" s="53" t="n"/>
-      <c r="C51" s="53" t="n"/>
-      <c r="D51" s="53" t="n"/>
-      <c r="E51" s="53" t="n"/>
-      <c r="F51" s="53" t="n"/>
-      <c r="G51" s="53" t="n"/>
-      <c r="H51" s="53" t="n"/>
-      <c r="I51" s="53" t="n"/>
-      <c r="J51" s="53" t="n"/>
-      <c r="K51" s="53" t="n"/>
+      <c r="B51" s="54" t="n"/>
+      <c r="C51" s="54" t="n"/>
+      <c r="D51" s="54" t="n"/>
+      <c r="E51" s="54" t="n"/>
+      <c r="F51" s="54" t="n"/>
+      <c r="G51" s="54" t="n"/>
+      <c r="H51" s="54" t="n"/>
+      <c r="I51" s="54" t="n"/>
+      <c r="J51" s="54" t="n"/>
+      <c r="K51" s="54" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="54" t="inlineStr">
+      <c r="A52" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B52" s="54" t="inlineStr">
+      <c r="B52" s="55" t="inlineStr">
         <is>
           <t>24.7~9</t>
         </is>
       </c>
-      <c r="C52" s="54" t="inlineStr">
+      <c r="C52" s="55" t="inlineStr">
         <is>
           <t>24.10~12</t>
         </is>
       </c>
-      <c r="D52" s="54" t="inlineStr">
+      <c r="D52" s="55" t="inlineStr">
         <is>
           <t>25.1~3</t>
         </is>
       </c>
-      <c r="E52" s="54" t="inlineStr">
+      <c r="E52" s="55" t="inlineStr">
         <is>
           <t>25.4~6</t>
         </is>
       </c>
-      <c r="F52" s="54" t="inlineStr">
+      <c r="F52" s="55" t="inlineStr">
         <is>
           <t>25.7~9</t>
         </is>
       </c>
-      <c r="G52" s="54" t="inlineStr">
+      <c r="G52" s="55" t="inlineStr">
         <is>
           <t>25.10~12</t>
         </is>
       </c>
-      <c r="H52" s="54" t="inlineStr">
+      <c r="H52" s="55" t="inlineStr">
         <is>
           <t>26.1~3</t>
         </is>
       </c>
-      <c r="I52" s="54" t="inlineStr">
+      <c r="I52" s="55" t="inlineStr">
         <is>
           <t>26.4~6</t>
         </is>
       </c>
-      <c r="J52" s="54" t="inlineStr">
+      <c r="J52" s="55" t="inlineStr">
         <is>
           <t>26.7~9</t>
         </is>
       </c>
-      <c r="K52" s="54" t="inlineStr">
+      <c r="K52" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="55" t="inlineStr">
+      <c r="A53" s="56" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B53" s="56" t="n">
+      <c r="B53" s="57" t="n">
         <v>1857</v>
       </c>
-      <c r="C53" s="56" t="n">
+      <c r="C53" s="57" t="n">
         <v>2011</v>
       </c>
-      <c r="D53" s="56" t="n">
+      <c r="D53" s="57" t="n">
         <v>2114</v>
       </c>
-      <c r="E53" s="56" t="n">
+      <c r="E53" s="57" t="n">
         <v>2059</v>
       </c>
-      <c r="F53" s="56" t="n">
+      <c r="F53" s="57" t="n">
         <v>2053</v>
       </c>
-      <c r="G53" s="56" t="n">
+      <c r="G53" s="57" t="n">
         <v>2202</v>
       </c>
-      <c r="H53" s="56" t="n">
+      <c r="H53" s="57" t="n">
         <v>2520</v>
       </c>
-      <c r="I53" s="56" t="n">
+      <c r="I53" s="57" t="n">
         <v>2819</v>
       </c>
-      <c r="J53" s="56" t="n">
+      <c r="J53" s="57" t="n">
         <v>3060</v>
       </c>
-      <c r="K53" s="57" t="inlineStr">
+      <c r="K53" s="58" t="inlineStr">
         <is>
           <t>설명회 자료 부문별 수주고(억 엔)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="55" t="inlineStr">
+      <c r="A54" s="56" t="inlineStr">
         <is>
           <t>FA</t>
         </is>
       </c>
-      <c r="B54" s="56" t="n">
+      <c r="B54" s="57" t="n">
         <v>494</v>
       </c>
-      <c r="C54" s="56" t="n">
+      <c r="C54" s="57" t="n">
         <v>473</v>
       </c>
-      <c r="D54" s="56" t="n">
+      <c r="D54" s="57" t="n">
         <v>507</v>
       </c>
-      <c r="E54" s="56" t="n">
+      <c r="E54" s="57" t="n">
         <v>550</v>
       </c>
-      <c r="F54" s="56" t="n">
+      <c r="F54" s="57" t="n">
         <v>488</v>
       </c>
-      <c r="G54" s="56" t="n">
+      <c r="G54" s="57" t="n">
         <v>547</v>
       </c>
-      <c r="H54" s="56" t="n">
+      <c r="H54" s="57" t="n">
         <v>711</v>
       </c>
-      <c r="I54" s="56" t="n">
+      <c r="I54" s="57" t="n">
         <v>902</v>
       </c>
-      <c r="J54" s="56" t="n">
+      <c r="J54" s="57" t="n">
         <v>1122</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="55" t="inlineStr">
+      <c r="A55" s="56" t="inlineStr">
         <is>
           <t>로봇</t>
         </is>
       </c>
-      <c r="B55" s="56" t="n">
+      <c r="B55" s="57" t="n">
         <v>663</v>
       </c>
-      <c r="C55" s="56" t="n">
+      <c r="C55" s="57" t="n">
         <v>817</v>
       </c>
-      <c r="D55" s="56" t="n">
+      <c r="D55" s="57" t="n">
         <v>909</v>
       </c>
-      <c r="E55" s="56" t="n">
+      <c r="E55" s="57" t="n">
         <v>906</v>
       </c>
-      <c r="F55" s="56" t="n">
+      <c r="F55" s="57" t="n">
         <v>918</v>
       </c>
-      <c r="G55" s="56" t="n">
+      <c r="G55" s="57" t="n">
         <v>988</v>
       </c>
-      <c r="H55" s="56" t="n">
+      <c r="H55" s="57" t="n">
         <v>1006</v>
       </c>
-      <c r="I55" s="56" t="n">
+      <c r="I55" s="57" t="n">
         <v>979</v>
       </c>
-      <c r="J55" s="56" t="n">
+      <c r="J55" s="57" t="n">
         <v>1034</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="55" t="inlineStr">
+      <c r="A56" s="56" t="inlineStr">
         <is>
           <t>로보머신</t>
         </is>
       </c>
-      <c r="B56" s="56" t="n">
+      <c r="B56" s="57" t="n">
         <v>361</v>
       </c>
-      <c r="C56" s="56" t="n">
+      <c r="C56" s="57" t="n">
         <v>388</v>
       </c>
-      <c r="D56" s="56" t="n">
+      <c r="D56" s="57" t="n">
         <v>375</v>
       </c>
-      <c r="E56" s="56" t="n">
+      <c r="E56" s="57" t="n">
         <v>290</v>
       </c>
-      <c r="F56" s="56" t="n">
+      <c r="F56" s="57" t="n">
         <v>297</v>
       </c>
-      <c r="G56" s="56" t="n">
+      <c r="G56" s="57" t="n">
         <v>308</v>
       </c>
-      <c r="H56" s="56" t="n">
+      <c r="H56" s="57" t="n">
         <v>438</v>
       </c>
-      <c r="I56" s="56" t="n">
+      <c r="I56" s="57" t="n">
         <v>576</v>
       </c>
-      <c r="J56" s="56" t="n">
+      <c r="J56" s="57" t="n">
         <v>512</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="55" t="inlineStr">
+      <c r="A57" s="56" t="inlineStr">
         <is>
           <t>서비스</t>
         </is>
       </c>
-      <c r="B57" s="56" t="n">
+      <c r="B57" s="57" t="n">
         <v>340</v>
       </c>
-      <c r="C57" s="56" t="n">
+      <c r="C57" s="57" t="n">
         <v>333</v>
       </c>
-      <c r="D57" s="56" t="n">
+      <c r="D57" s="57" t="n">
         <v>323</v>
       </c>
-      <c r="E57" s="56" t="n">
+      <c r="E57" s="57" t="n">
         <v>312</v>
       </c>
-      <c r="F57" s="56" t="n">
+      <c r="F57" s="57" t="n">
         <v>351</v>
       </c>
-      <c r="G57" s="56" t="n">
+      <c r="G57" s="57" t="n">
         <v>359</v>
       </c>
-      <c r="H57" s="56" t="n">
+      <c r="H57" s="57" t="n">
         <v>365</v>
       </c>
-      <c r="I57" s="56" t="n">
+      <c r="I57" s="57" t="n">
         <v>363</v>
       </c>
-      <c r="J57" s="56" t="n">
+      <c r="J57" s="57" t="n">
         <v>393</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="53" t="inlineStr">
+      <c r="A59" s="54" t="inlineStr">
         <is>
           <t>수주 지역별 26Q2 YoY</t>
         </is>
       </c>
-      <c r="B59" s="53" t="n"/>
-      <c r="C59" s="53" t="n"/>
-      <c r="D59" s="53" t="n"/>
-      <c r="E59" s="53" t="n"/>
-      <c r="F59" s="53" t="n"/>
-      <c r="G59" s="53" t="n"/>
-      <c r="H59" s="53" t="n"/>
-      <c r="I59" s="53" t="n"/>
-      <c r="J59" s="53" t="n"/>
-      <c r="K59" s="53" t="n"/>
+      <c r="B59" s="54" t="n"/>
+      <c r="C59" s="54" t="n"/>
+      <c r="D59" s="54" t="n"/>
+      <c r="E59" s="54" t="n"/>
+      <c r="F59" s="54" t="n"/>
+      <c r="G59" s="54" t="n"/>
+      <c r="H59" s="54" t="n"/>
+      <c r="I59" s="54" t="n"/>
+      <c r="J59" s="54" t="n"/>
+      <c r="K59" s="54" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="54" t="inlineStr">
+      <c r="A60" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B60" s="54" t="inlineStr">
+      <c r="B60" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K60" s="54" t="inlineStr">
+      <c r="K60" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="55" t="inlineStr">
+      <c r="A61" s="56" t="inlineStr">
         <is>
           <t>전체</t>
         </is>
       </c>
-      <c r="B61" s="58" t="n">
+      <c r="B61" s="59" t="n">
         <v>49</v>
       </c>
-      <c r="K61" s="57" t="inlineStr">
+      <c r="K61" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="55" t="inlineStr">
+      <c r="A62" s="56" t="inlineStr">
         <is>
           <t>아시아(중국 외)</t>
         </is>
       </c>
-      <c r="B62" s="58" t="n">
+      <c r="B62" s="59" t="n">
         <v>111.9</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="55" t="inlineStr">
+      <c r="A63" s="56" t="inlineStr">
         <is>
           <t>중국</t>
         </is>
       </c>
-      <c r="B63" s="58" t="n">
+      <c r="B63" s="59" t="n">
         <v>79.8</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="55" t="inlineStr">
+      <c r="A64" s="56" t="inlineStr">
         <is>
           <t>일본</t>
         </is>
       </c>
-      <c r="B64" s="58" t="n">
+      <c r="B64" s="59" t="n">
         <v>54.3</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="55" t="inlineStr">
+      <c r="A65" s="56" t="inlineStr">
         <is>
           <t>미주</t>
         </is>
       </c>
-      <c r="B65" s="58" t="n">
+      <c r="B65" s="59" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="55" t="inlineStr">
+      <c r="A66" s="56" t="inlineStr">
         <is>
           <t>유럽</t>
         </is>
       </c>
-      <c r="B66" s="58" t="n">
+      <c r="B66" s="59" t="n">
         <v>5.3</v>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="53" t="inlineStr">
+      <c r="A68" s="54" t="inlineStr">
         <is>
           <t>매출 지역별 26Q2 · 비중</t>
         </is>
       </c>
-      <c r="B68" s="53" t="n"/>
-      <c r="C68" s="53" t="n"/>
-      <c r="D68" s="53" t="n"/>
-      <c r="E68" s="53" t="n"/>
-      <c r="F68" s="53" t="n"/>
-      <c r="G68" s="53" t="n"/>
-      <c r="H68" s="53" t="n"/>
-      <c r="I68" s="53" t="n"/>
-      <c r="J68" s="53" t="n"/>
-      <c r="K68" s="53" t="n"/>
+      <c r="B68" s="54" t="n"/>
+      <c r="C68" s="54" t="n"/>
+      <c r="D68" s="54" t="n"/>
+      <c r="E68" s="54" t="n"/>
+      <c r="F68" s="54" t="n"/>
+      <c r="G68" s="54" t="n"/>
+      <c r="H68" s="54" t="n"/>
+      <c r="I68" s="54" t="n"/>
+      <c r="J68" s="54" t="n"/>
+      <c r="K68" s="54" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="54" t="inlineStr">
+      <c r="A69" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B69" s="54" t="inlineStr">
+      <c r="B69" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K69" s="54" t="inlineStr">
+      <c r="K69" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="55" t="inlineStr">
+      <c r="A70" s="56" t="inlineStr">
         <is>
           <t>미주</t>
         </is>
       </c>
-      <c r="B70" s="58" t="n">
+      <c r="B70" s="59" t="n">
         <v>27.8</v>
       </c>
-      <c r="K70" s="57" t="inlineStr">
+      <c r="K70" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="55" t="inlineStr">
+      <c r="A71" s="56" t="inlineStr">
         <is>
           <t>중국</t>
         </is>
       </c>
-      <c r="B71" s="58" t="n">
+      <c r="B71" s="59" t="n">
         <v>27.4</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="55" t="inlineStr">
+      <c r="A72" s="56" t="inlineStr">
         <is>
           <t>유럽</t>
         </is>
       </c>
-      <c r="B72" s="58" t="n">
+      <c r="B72" s="59" t="n">
         <v>15.9</v>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="55" t="inlineStr">
+      <c r="A73" s="56" t="inlineStr">
         <is>
           <t>아시아(중국 외)</t>
         </is>
       </c>
-      <c r="B73" s="58" t="n">
+      <c r="B73" s="59" t="n">
         <v>14.7</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="55" t="inlineStr">
+      <c r="A74" s="56" t="inlineStr">
         <is>
           <t>일본</t>
         </is>
       </c>
-      <c r="B74" s="58" t="n">
+      <c r="B74" s="59" t="n">
         <v>13.1</v>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="55" t="inlineStr">
+      <c r="A75" s="56" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="B75" s="58" t="n">
+      <c r="B75" s="59" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="53" t="inlineStr">
+      <c r="A77" s="54" t="inlineStr">
         <is>
           <t>매출 지역별 26Q2 · YoY</t>
         </is>
       </c>
-      <c r="B77" s="53" t="n"/>
-      <c r="C77" s="53" t="n"/>
-      <c r="D77" s="53" t="n"/>
-      <c r="E77" s="53" t="n"/>
-      <c r="F77" s="53" t="n"/>
-      <c r="G77" s="53" t="n"/>
-      <c r="H77" s="53" t="n"/>
-      <c r="I77" s="53" t="n"/>
-      <c r="J77" s="53" t="n"/>
-      <c r="K77" s="53" t="n"/>
+      <c r="B77" s="54" t="n"/>
+      <c r="C77" s="54" t="n"/>
+      <c r="D77" s="54" t="n"/>
+      <c r="E77" s="54" t="n"/>
+      <c r="F77" s="54" t="n"/>
+      <c r="G77" s="54" t="n"/>
+      <c r="H77" s="54" t="n"/>
+      <c r="I77" s="54" t="n"/>
+      <c r="J77" s="54" t="n"/>
+      <c r="K77" s="54" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="54" t="inlineStr">
+      <c r="A78" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B78" s="54" t="inlineStr">
+      <c r="B78" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K78" s="54" t="inlineStr">
+      <c r="K78" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="55" t="inlineStr">
+      <c r="A79" s="56" t="inlineStr">
         <is>
           <t>미주</t>
         </is>
       </c>
-      <c r="B79" s="58" t="n">
+      <c r="B79" s="59" t="n">
         <v>12.9</v>
       </c>
-      <c r="K79" s="57" t="inlineStr">
+      <c r="K79" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="55" t="inlineStr">
+      <c r="A80" s="56" t="inlineStr">
         <is>
           <t>중국</t>
         </is>
       </c>
-      <c r="B80" s="58" t="n">
+      <c r="B80" s="59" t="n">
         <v>20.8</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="55" t="inlineStr">
+      <c r="A81" s="56" t="inlineStr">
         <is>
           <t>유럽</t>
         </is>
       </c>
-      <c r="B81" s="58" t="n">
+      <c r="B81" s="59" t="n">
         <v>5.7</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="55" t="inlineStr">
+      <c r="A82" s="56" t="inlineStr">
         <is>
           <t>아시아(중국 외)</t>
         </is>
       </c>
-      <c r="B82" s="58" t="n">
+      <c r="B82" s="59" t="n">
         <v>17.2</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="55" t="inlineStr">
+      <c r="A83" s="56" t="inlineStr">
         <is>
           <t>일본</t>
         </is>
       </c>
-      <c r="B83" s="58" t="n">
+      <c r="B83" s="59" t="n">
         <v>17.1</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="53" t="inlineStr">
+      <c r="A85" s="54" t="inlineStr">
         <is>
           <t>영업이익 증감 요인 상반기 YoY</t>
         </is>
       </c>
-      <c r="B85" s="53" t="n"/>
-      <c r="C85" s="53" t="n"/>
-      <c r="D85" s="53" t="n"/>
-      <c r="E85" s="53" t="n"/>
-      <c r="F85" s="53" t="n"/>
-      <c r="G85" s="53" t="n"/>
-      <c r="H85" s="53" t="n"/>
-      <c r="I85" s="53" t="n"/>
-      <c r="J85" s="53" t="n"/>
-      <c r="K85" s="53" t="n"/>
+      <c r="B85" s="54" t="n"/>
+      <c r="C85" s="54" t="n"/>
+      <c r="D85" s="54" t="n"/>
+      <c r="E85" s="54" t="n"/>
+      <c r="F85" s="54" t="n"/>
+      <c r="G85" s="54" t="n"/>
+      <c r="H85" s="54" t="n"/>
+      <c r="I85" s="54" t="n"/>
+      <c r="J85" s="54" t="n"/>
+      <c r="K85" s="54" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="54" t="inlineStr">
+      <c r="A86" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B86" s="54" t="inlineStr">
+      <c r="B86" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K86" s="54" t="inlineStr">
+      <c r="K86" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="55" t="inlineStr">
+      <c r="A87" s="56" t="inlineStr">
         <is>
           <t>전년 상반기</t>
         </is>
       </c>
-      <c r="B87" s="56" t="n">
+      <c r="B87" s="57" t="n">
         <v>860</v>
       </c>
-      <c r="K87" s="57" t="inlineStr">
+      <c r="K87" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="55" t="inlineStr">
+      <c r="A88" s="56" t="inlineStr">
         <is>
           <t>매출 증가</t>
         </is>
       </c>
-      <c r="B88" s="56" t="n">
+      <c r="B88" s="57" t="n">
         <v>235</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="55" t="inlineStr">
+      <c r="A89" s="56" t="inlineStr">
         <is>
           <t>원가 차이</t>
         </is>
       </c>
-      <c r="B89" s="56" t="n">
+      <c r="B89" s="57" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="55" t="inlineStr">
+      <c r="A90" s="56" t="inlineStr">
         <is>
           <t>미실현이익</t>
         </is>
       </c>
-      <c r="B90" s="56" t="n">
+      <c r="B90" s="57" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="55" t="inlineStr">
+      <c r="A91" s="56" t="inlineStr">
         <is>
           <t>판관비</t>
         </is>
       </c>
-      <c r="B91" s="56" t="n">
+      <c r="B91" s="57" t="n">
         <v>-37</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="55" t="inlineStr">
+      <c r="A92" s="56" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="B92" s="56" t="n">
+      <c r="B92" s="57" t="n">
         <v>65</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="55" t="inlineStr">
+      <c r="A93" s="56" t="inlineStr">
         <is>
           <t>당기 상반기</t>
         </is>
       </c>
-      <c r="B93" s="56" t="n">
+      <c r="B93" s="57" t="n">
         <v>1167</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="53" t="inlineStr">
+      <c r="A95" s="54" t="inlineStr">
         <is>
           <t>영업이익 증감 요인 QoQ</t>
         </is>
       </c>
-      <c r="B95" s="53" t="n"/>
-      <c r="C95" s="53" t="n"/>
-      <c r="D95" s="53" t="n"/>
-      <c r="E95" s="53" t="n"/>
-      <c r="F95" s="53" t="n"/>
-      <c r="G95" s="53" t="n"/>
-      <c r="H95" s="53" t="n"/>
-      <c r="I95" s="53" t="n"/>
-      <c r="J95" s="53" t="n"/>
-      <c r="K95" s="53" t="n"/>
+      <c r="B95" s="54" t="n"/>
+      <c r="C95" s="54" t="n"/>
+      <c r="D95" s="54" t="n"/>
+      <c r="E95" s="54" t="n"/>
+      <c r="F95" s="54" t="n"/>
+      <c r="G95" s="54" t="n"/>
+      <c r="H95" s="54" t="n"/>
+      <c r="I95" s="54" t="n"/>
+      <c r="J95" s="54" t="n"/>
+      <c r="K95" s="54" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="54" t="inlineStr">
+      <c r="A96" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B96" s="54" t="inlineStr">
+      <c r="B96" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K96" s="54" t="inlineStr">
+      <c r="K96" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="55" t="inlineStr">
+      <c r="A97" s="56" t="inlineStr">
         <is>
           <t>1Q</t>
         </is>
       </c>
-      <c r="B97" s="56" t="n">
+      <c r="B97" s="57" t="n">
         <v>535</v>
       </c>
-      <c r="K97" s="57" t="inlineStr">
+      <c r="K97" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="55" t="inlineStr">
+      <c r="A98" s="56" t="inlineStr">
         <is>
           <t>매출 증가</t>
         </is>
       </c>
-      <c r="B98" s="56" t="n">
+      <c r="B98" s="57" t="n">
         <v>105</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="55" t="inlineStr">
+      <c r="A99" s="56" t="inlineStr">
         <is>
           <t>원가 차이</t>
         </is>
       </c>
-      <c r="B99" s="56" t="n">
+      <c r="B99" s="57" t="n">
         <v>-18</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="55" t="inlineStr">
+      <c r="A100" s="56" t="inlineStr">
         <is>
           <t>미실현이익</t>
         </is>
       </c>
-      <c r="B100" s="56" t="n">
+      <c r="B100" s="57" t="n">
         <v>28</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="55" t="inlineStr">
+      <c r="A101" s="56" t="inlineStr">
         <is>
           <t>판관비</t>
         </is>
       </c>
-      <c r="B101" s="56" t="n">
+      <c r="B101" s="57" t="n">
         <v>-19</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="55" t="inlineStr">
+      <c r="A102" s="56" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="B102" s="56" t="n">
+      <c r="B102" s="57" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="55" t="inlineStr">
+      <c r="A103" s="56" t="inlineStr">
         <is>
           <t>2Q</t>
         </is>
       </c>
-      <c r="B103" s="56" t="n">
+      <c r="B103" s="57" t="n">
         <v>632</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="53" t="inlineStr">
+      <c r="A105" s="54" t="inlineStr">
         <is>
           <t>환율 · 2Q 26</t>
         </is>
       </c>
-      <c r="B105" s="53" t="n"/>
-      <c r="C105" s="53" t="n"/>
-      <c r="D105" s="53" t="n"/>
-      <c r="E105" s="53" t="n"/>
-      <c r="F105" s="53" t="n"/>
-      <c r="G105" s="53" t="n"/>
-      <c r="H105" s="53" t="n"/>
-      <c r="I105" s="53" t="n"/>
-      <c r="J105" s="53" t="n"/>
-      <c r="K105" s="53" t="n"/>
+      <c r="B105" s="54" t="n"/>
+      <c r="C105" s="54" t="n"/>
+      <c r="D105" s="54" t="n"/>
+      <c r="E105" s="54" t="n"/>
+      <c r="F105" s="54" t="n"/>
+      <c r="G105" s="54" t="n"/>
+      <c r="H105" s="54" t="n"/>
+      <c r="I105" s="54" t="n"/>
+      <c r="J105" s="54" t="n"/>
+      <c r="K105" s="54" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="54" t="inlineStr">
+      <c r="A106" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B106" s="54" t="inlineStr">
+      <c r="B106" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K106" s="54" t="inlineStr">
+      <c r="K106" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="55" t="inlineStr">
+      <c r="A107" s="56" t="inlineStr">
         <is>
           <t>달러</t>
         </is>
       </c>
-      <c r="B107" s="58" t="n">
+      <c r="B107" s="59" t="n">
         <v>159.25</v>
       </c>
-      <c r="K107" s="57" t="inlineStr">
+      <c r="K107" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="55" t="inlineStr">
+      <c r="A108" s="56" t="inlineStr">
         <is>
           <t>유로</t>
         </is>
       </c>
-      <c r="B108" s="58" t="n">
+      <c r="B108" s="59" t="n">
         <v>183.32</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="53" t="inlineStr">
+      <c r="A110" s="54" t="inlineStr">
         <is>
           <t>환율 · 2Q 25</t>
         </is>
       </c>
-      <c r="B110" s="53" t="n"/>
-      <c r="C110" s="53" t="n"/>
-      <c r="D110" s="53" t="n"/>
-      <c r="E110" s="53" t="n"/>
-      <c r="F110" s="53" t="n"/>
-      <c r="G110" s="53" t="n"/>
-      <c r="H110" s="53" t="n"/>
-      <c r="I110" s="53" t="n"/>
-      <c r="J110" s="53" t="n"/>
-      <c r="K110" s="53" t="n"/>
+      <c r="B110" s="54" t="n"/>
+      <c r="C110" s="54" t="n"/>
+      <c r="D110" s="54" t="n"/>
+      <c r="E110" s="54" t="n"/>
+      <c r="F110" s="54" t="n"/>
+      <c r="G110" s="54" t="n"/>
+      <c r="H110" s="54" t="n"/>
+      <c r="I110" s="54" t="n"/>
+      <c r="J110" s="54" t="n"/>
+      <c r="K110" s="54" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="54" t="inlineStr">
+      <c r="A111" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B111" s="54" t="inlineStr">
+      <c r="B111" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K111" s="54" t="inlineStr">
+      <c r="K111" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="55" t="inlineStr">
+      <c r="A112" s="56" t="inlineStr">
         <is>
           <t>달러</t>
         </is>
       </c>
-      <c r="B112" s="58" t="n">
+      <c r="B112" s="59" t="n">
         <v>147.48</v>
       </c>
-      <c r="K112" s="57" t="inlineStr">
+      <c r="K112" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="55" t="inlineStr">
+      <c r="A113" s="56" t="inlineStr">
         <is>
           <t>유로</t>
         </is>
       </c>
-      <c r="B113" s="58" t="n">
+      <c r="B113" s="59" t="n">
         <v>172.32</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="53" t="inlineStr">
+      <c r="A115" s="54" t="inlineStr">
         <is>
           <t>환율 · 하반기 assume</t>
         </is>
       </c>
-      <c r="B115" s="53" t="n"/>
-      <c r="C115" s="53" t="n"/>
-      <c r="D115" s="53" t="n"/>
-      <c r="E115" s="53" t="n"/>
-      <c r="F115" s="53" t="n"/>
-      <c r="G115" s="53" t="n"/>
-      <c r="H115" s="53" t="n"/>
-      <c r="I115" s="53" t="n"/>
-      <c r="J115" s="53" t="n"/>
-      <c r="K115" s="53" t="n"/>
+      <c r="B115" s="54" t="n"/>
+      <c r="C115" s="54" t="n"/>
+      <c r="D115" s="54" t="n"/>
+      <c r="E115" s="54" t="n"/>
+      <c r="F115" s="54" t="n"/>
+      <c r="G115" s="54" t="n"/>
+      <c r="H115" s="54" t="n"/>
+      <c r="I115" s="54" t="n"/>
+      <c r="J115" s="54" t="n"/>
+      <c r="K115" s="54" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="54" t="inlineStr">
+      <c r="A116" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B116" s="54" t="inlineStr">
+      <c r="B116" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K116" s="54" t="inlineStr">
+      <c r="K116" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="55" t="inlineStr">
+      <c r="A117" s="56" t="inlineStr">
         <is>
           <t>달러</t>
         </is>
       </c>
-      <c r="B117" s="56" t="n">
+      <c r="B117" s="57" t="n">
         <v>150</v>
       </c>
-      <c r="K117" s="57" t="inlineStr">
+      <c r="K117" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="55" t="inlineStr">
+      <c r="A118" s="56" t="inlineStr">
         <is>
           <t>유로</t>
         </is>
       </c>
-      <c r="B118" s="56" t="n">
+      <c r="B118" s="57" t="n">
         <v>175</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="53" t="inlineStr">
+      <c r="A120" s="54" t="inlineStr">
         <is>
           <t>가이던스 FY3 27 · latest 2026-10-23</t>
         </is>
       </c>
-      <c r="B120" s="53" t="n"/>
-      <c r="C120" s="53" t="n"/>
-      <c r="D120" s="53" t="n"/>
-      <c r="E120" s="53" t="n"/>
-      <c r="F120" s="53" t="n"/>
-      <c r="G120" s="53" t="n"/>
-      <c r="H120" s="53" t="n"/>
-      <c r="I120" s="53" t="n"/>
-      <c r="J120" s="53" t="n"/>
-      <c r="K120" s="53" t="n"/>
+      <c r="B120" s="54" t="n"/>
+      <c r="C120" s="54" t="n"/>
+      <c r="D120" s="54" t="n"/>
+      <c r="E120" s="54" t="n"/>
+      <c r="F120" s="54" t="n"/>
+      <c r="G120" s="54" t="n"/>
+      <c r="H120" s="54" t="n"/>
+      <c r="I120" s="54" t="n"/>
+      <c r="J120" s="54" t="n"/>
+      <c r="K120" s="54" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="54" t="inlineStr">
+      <c r="A121" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B121" s="54" t="inlineStr">
+      <c r="B121" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K121" s="54" t="inlineStr">
+      <c r="K121" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="55" t="inlineStr">
+      <c r="A122" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B122" s="56" t="n">
+      <c r="B122" s="57" t="n">
         <v>10137</v>
       </c>
-      <c r="K122" s="57" t="inlineStr">
+      <c r="K122" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="55" t="inlineStr">
+      <c r="A123" s="56" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="B123" s="56" t="n">
+      <c r="B123" s="57" t="n">
         <v>2407</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="55" t="inlineStr">
+      <c r="A124" s="56" t="inlineStr">
         <is>
           <t>ordinary</t>
         </is>
       </c>
-      <c r="B124" s="56" t="n">
+      <c r="B124" s="57" t="n">
         <v>3088</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="55" t="inlineStr">
+      <c r="A125" s="56" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="B125" s="56" t="n">
+      <c r="B125" s="57" t="n">
         <v>2283</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="55" t="inlineStr">
+      <c r="A126" s="56" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="B126" s="58" t="n">
+      <c r="B126" s="59" t="n">
         <v>246.01</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="53" t="inlineStr">
+      <c r="A128" s="54" t="inlineStr">
         <is>
           <t>가이던스 FY3 27 · 하반기 implied</t>
         </is>
       </c>
-      <c r="B128" s="53" t="n"/>
-      <c r="C128" s="53" t="n"/>
-      <c r="D128" s="53" t="n"/>
-      <c r="E128" s="53" t="n"/>
-      <c r="F128" s="53" t="n"/>
-      <c r="G128" s="53" t="n"/>
-      <c r="H128" s="53" t="n"/>
-      <c r="I128" s="53" t="n"/>
-      <c r="J128" s="53" t="n"/>
-      <c r="K128" s="53" t="n"/>
+      <c r="B128" s="54" t="n"/>
+      <c r="C128" s="54" t="n"/>
+      <c r="D128" s="54" t="n"/>
+      <c r="E128" s="54" t="n"/>
+      <c r="F128" s="54" t="n"/>
+      <c r="G128" s="54" t="n"/>
+      <c r="H128" s="54" t="n"/>
+      <c r="I128" s="54" t="n"/>
+      <c r="J128" s="54" t="n"/>
+      <c r="K128" s="54" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="54" t="inlineStr">
+      <c r="A129" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B129" s="54" t="inlineStr">
+      <c r="B129" s="55" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="K129" s="54" t="inlineStr">
+      <c r="K129" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="55" t="inlineStr">
+      <c r="A130" s="56" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="B130" s="58" t="n">
+      <c r="B130" s="59" t="n">
         <v>5399.92</v>
       </c>
-      <c r="K130" s="57" t="inlineStr">
+      <c r="K130" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="55" t="inlineStr">
+      <c r="A131" s="56" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="B131" s="58" t="n">
+      <c r="B131" s="59" t="n">
         <v>1240.38</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="55" t="inlineStr">
+      <c r="A132" s="56" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="B132" s="58" t="n">
+      <c r="B132" s="59" t="n">
         <v>1157.24</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="53" t="inlineStr">
+      <c r="A134" s="54" t="inlineStr">
         <is>
           <t>가이던스 history FY3 27</t>
         </is>
       </c>
-      <c r="B134" s="53" t="n"/>
-      <c r="C134" s="53" t="n"/>
-      <c r="D134" s="53" t="n"/>
-      <c r="E134" s="53" t="n"/>
-      <c r="F134" s="53" t="n"/>
-      <c r="G134" s="53" t="n"/>
-      <c r="H134" s="53" t="n"/>
-      <c r="I134" s="53" t="n"/>
-      <c r="J134" s="53" t="n"/>
-      <c r="K134" s="53" t="n"/>
+      <c r="B134" s="54" t="n"/>
+      <c r="C134" s="54" t="n"/>
+      <c r="D134" s="54" t="n"/>
+      <c r="E134" s="54" t="n"/>
+      <c r="F134" s="54" t="n"/>
+      <c r="G134" s="54" t="n"/>
+      <c r="H134" s="54" t="n"/>
+      <c r="I134" s="54" t="n"/>
+      <c r="J134" s="54" t="n"/>
+      <c r="K134" s="54" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="54" t="inlineStr">
+      <c r="A135" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B135" s="54" t="inlineStr">
+      <c r="B135" s="55" t="inlineStr">
         <is>
           <t>매출</t>
         </is>
       </c>
-      <c r="C135" s="54" t="inlineStr">
+      <c r="C135" s="55" t="inlineStr">
         <is>
           <t>영업이익</t>
         </is>
       </c>
-      <c r="D135" s="54" t="inlineStr">
+      <c r="D135" s="55" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="E135" s="54" t="inlineStr">
+      <c r="E135" s="55" t="inlineStr">
         <is>
           <t>EPS</t>
         </is>
       </c>
-      <c r="K135" s="54" t="inlineStr">
+      <c r="K135" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="55" t="inlineStr">
+      <c r="A136" s="56" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="B136" s="56" t="n">
+      <c r="B136" s="57" t="n">
         <v>9096</v>
       </c>
-      <c r="C136" s="56" t="n">
+      <c r="C136" s="57" t="n">
         <v>2122</v>
       </c>
-      <c r="D136" s="56" t="n">
+      <c r="D136" s="57" t="n">
         <v>1849</v>
       </c>
-      <c r="E136" s="58" t="n">
+      <c r="E136" s="59" t="n">
         <v>198.14</v>
       </c>
-      <c r="K136" s="57" t="inlineStr">
+      <c r="K136" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="55" t="inlineStr">
+      <c r="A137" s="56" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="B137" s="56" t="n">
+      <c r="B137" s="57" t="n">
         <v>9481</v>
       </c>
-      <c r="C137" s="56" t="n">
+      <c r="C137" s="57" t="n">
         <v>2180</v>
       </c>
-      <c r="D137" s="56" t="n">
+      <c r="D137" s="57" t="n">
         <v>1980</v>
       </c>
-      <c r="E137" s="58" t="n">
+      <c r="E137" s="59" t="n">
         <v>212.18</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="55" t="inlineStr">
+      <c r="A138" s="56" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="B138" s="56" t="n">
+      <c r="B138" s="57" t="n">
         <v>10137</v>
       </c>
-      <c r="C138" s="56" t="n">
+      <c r="C138" s="57" t="n">
         <v>2407</v>
       </c>
-      <c r="D138" s="56" t="n">
+      <c r="D138" s="57" t="n">
         <v>2283</v>
       </c>
-      <c r="E138" s="58" t="n">
+      <c r="E138" s="59" t="n">
         <v>246.01</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="53" t="inlineStr">
+      <c r="A140" s="54" t="inlineStr">
         <is>
           <t>가이던스 history past</t>
         </is>
       </c>
-      <c r="B140" s="53" t="n"/>
-      <c r="C140" s="53" t="n"/>
-      <c r="D140" s="53" t="n"/>
-      <c r="E140" s="53" t="n"/>
-      <c r="F140" s="53" t="n"/>
-      <c r="G140" s="53" t="n"/>
-      <c r="H140" s="53" t="n"/>
-      <c r="I140" s="53" t="n"/>
-      <c r="J140" s="53" t="n"/>
-      <c r="K140" s="53" t="n"/>
+      <c r="B140" s="54" t="n"/>
+      <c r="C140" s="54" t="n"/>
+      <c r="D140" s="54" t="n"/>
+      <c r="E140" s="54" t="n"/>
+      <c r="F140" s="54" t="n"/>
+      <c r="G140" s="54" t="n"/>
+      <c r="H140" s="54" t="n"/>
+      <c r="I140" s="54" t="n"/>
+      <c r="J140" s="54" t="n"/>
+      <c r="K140" s="54" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="54" t="inlineStr">
+      <c r="A141" s="55" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B141" s="54" t="inlineStr">
+      <c r="B141" s="55" t="inlineStr">
         <is>
           <t>initial 매출</t>
         </is>
       </c>
-      <c r="C141" s="54" t="inlineStr">
+      <c r="C141" s="55" t="inlineStr">
         <is>
           <t>initial 영업이익</t>
         </is>
       </c>
-      <c r="D141" s="54" t="inlineStr">
+      <c r="D141" s="55" t="inlineStr">
         <is>
           <t>실적 매출</t>
         </is>
       </c>
-      <c r="E141" s="54" t="inlineStr">
+      <c r="E141" s="55" t="inlineStr">
         <is>
           <t>실적 영업이익</t>
         </is>
       </c>
-      <c r="K141" s="54" t="inlineStr">
+      <c r="K141" s="55" t="inlineStr">
         <is>
           <t>출처</t>
         </is>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="55" t="inlineStr">
+      <c r="A142" s="56" t="inlineStr">
         <is>
           <t>FY3/18</t>
         </is>
       </c>
-      <c r="B142" s="56" t="n">
+      <c r="B142" s="57" t="n">
         <v>5698</v>
       </c>
-      <c r="C142" s="56" t="n">
+      <c r="C142" s="57" t="n">
         <v>1555</v>
       </c>
-      <c r="D142" s="56" t="n">
+      <c r="D142" s="57" t="n">
         <v>7266</v>
       </c>
-      <c r="E142" s="56" t="n">
+      <c r="E142" s="57" t="n">
         <v>2296</v>
       </c>
-      <c r="K142" s="57" t="inlineStr">
+      <c r="K142" s="58" t="inlineStr">
         <is>
           <t>2단계 보고서 자료(회사 설명회 자료·공시)</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="55" t="inlineStr">
+      <c r="A143" s="56" t="inlineStr">
         <is>
           <t>FY3/19</t>
         </is>
       </c>
-      <c r="B143" s="56" t="n">
+      <c r="B143" s="57" t="n">
         <v>6342</v>
       </c>
-      <c r="C143" s="56" t="n">
+      <c r="C143" s="57" t="n">
         <v>1517</v>
       </c>
-      <c r="D143" s="56" t="n">
+      <c r="D143" s="57" t="n">
         <v>6356</v>
       </c>
-      <c r="E143" s="56" t="n">
+      <c r="E143" s="57" t="n">
         <v>1633</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="55" t="inlineStr">
+      <c r="A144" s="56" t="inlineStr">
         <is>
           <t>FY3/20</t>
         </is>
       </c>
-      <c r="B144" s="56" t="n">
+      <c r="B144" s="57" t="n">
         <v>5369</v>
       </c>
-      <c r="C144" s="56" t="n">
+      <c r="C144" s="57" t="n">
         <v>757</v>
       </c>
-      <c r="D144" s="56" t="n">
+      <c r="D144" s="57" t="n">
         <v>5083</v>
       </c>
-      <c r="E144" s="56" t="n">
+      <c r="E144" s="57" t="n">
         <v>884</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="55" t="inlineStr">
+      <c r="A145" s="56" t="inlineStr">
         <is>
           <t>FY3/22</t>
         </is>
       </c>
-      <c r="B145" s="56" t="n">
+      <c r="B145" s="57" t="n">
         <v>6571</v>
       </c>
-      <c r="C145" s="56" t="n">
+      <c r="C145" s="57" t="n">
         <v>1484</v>
       </c>
-      <c r="D145" s="56" t="n">
+      <c r="D145" s="57" t="n">
         <v>7330</v>
       </c>
-      <c r="E145" s="56" t="n">
+      <c r="E145" s="57" t="n">
         <v>1832</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="55" t="inlineStr">
+      <c r="A146" s="56" t="inlineStr">
         <is>
           <t>FY3/23</t>
         </is>
       </c>
-      <c r="B146" s="56" t="n">
+      <c r="B146" s="57" t="n">
         <v>8255</v>
       </c>
-      <c r="C146" s="56" t="n">
+      <c r="C146" s="57" t="n">
         <v>1973</v>
       </c>
-      <c r="D146" s="56" t="n">
+      <c r="D146" s="57" t="n">
         <v>8520</v>
       </c>
-      <c r="E146" s="56" t="n">
+      <c r="E146" s="57" t="n">
         <v>1914</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="55" t="inlineStr">
+      <c r="A147" s="56" t="inlineStr">
         <is>
           <t>FY3/24</t>
         </is>
       </c>
-      <c r="B147" s="56" t="n">
+      <c r="B147" s="57" t="n">
         <v>8195</v>
       </c>
-      <c r="C147" s="56" t="n">
+      <c r="C147" s="57" t="n">
         <v>1563</v>
       </c>
-      <c r="D147" s="56" t="n">
+      <c r="D147" s="57" t="n">
         <v>7953</v>
       </c>
-      <c r="E147" s="56" t="n">
+      <c r="E147" s="57" t="n">
         <v>1419</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="55" t="inlineStr">
+      <c r="A148" s="56" t="inlineStr">
         <is>
           <t>FY3/25</t>
         </is>
       </c>
-      <c r="B148" s="56" t="n">
+      <c r="B148" s="57" t="n">
         <v>7464</v>
       </c>
-      <c r="C148" s="56" t="n">
+      <c r="C148" s="57" t="n">
         <v>1210</v>
       </c>
-      <c r="D148" s="56" t="n">
+      <c r="D148" s="57" t="n">
         <v>7971</v>
       </c>
-      <c r="E148" s="56" t="n">
+      <c r="E148" s="57" t="n">
         <v>1588</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="55" t="inlineStr">
+      <c r="A149" s="56" t="inlineStr">
         <is>
           <t>FY3/26</t>
         </is>
       </c>
-      <c r="B149" s="59" t="n"/>
-      <c r="C149" s="59" t="n"/>
-      <c r="D149" s="56" t="n">
+      <c r="B149" s="60" t="n"/>
+      <c r="C149" s="60" t="n"/>
+      <c r="D149" s="57" t="n">
         <v>8578</v>
       </c>
-      <c r="E149" s="56" t="n">
+      <c r="E149" s="57" t="n">
         <v>1838</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="55" t="inlineStr">
+      <c r="A150" s="56" t="inlineStr">
         <is>
           <t>FY3/27</t>
         </is>
       </c>
-      <c r="B150" s="56" t="n">
+      <c r="B150" s="57" t="n">
         <v>9096</v>
       </c>
-      <c r="C150" s="56" t="n">
+      <c r="C150" s="57" t="n">
         <v>2122</v>
       </c>
-      <c r="D150" s="59" t="n"/>
-      <c r="E150" s="59" t="n"/>
+      <c r="D150" s="60" t="n"/>
+      <c r="E150" s="60" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16192,24 +16659,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="60" t="inlineStr">
+      <c r="A3" s="61" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="60" t="inlineStr">
+      <c r="B3" s="61" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="60" t="inlineStr">
+      <c r="C3" s="61" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
